--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1237</v>
+        <v>5.1259</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9496</v>
+        <v>5.9594</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1309.75</v>
+        <v>1293.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>536.75</v>
+        <v>512</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.30027</v>
+        <v>-1.257898</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.998645</v>
+        <v>-0.835574</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.705352</v>
+        <v>1.450696</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>4.223301</v>
+        <v>-0.582524</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9594</v>
+        <v>5.9606</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.835574</v>
+        <v>-0.8156099999999999</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185147</v>
+        <v>188913.453125</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>181.940002</v>
+        <v>186.029999</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.989998</v>
+        <v>112.760002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>447.350006</v>
+        <v>439.269989</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1259</v>
+        <v>5.0806</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9606</v>
+        <v>5.9044</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7718.600098</v>
+        <v>7684.339844</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26506.990234</v>
+        <v>26390.132812</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53414.25</v>
+        <v>52819.558594</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4476.600098</v>
+        <v>4442</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.480003</v>
+        <v>93.269997</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.279999</v>
+        <v>98.08000199999999</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1293.75</v>
+        <v>1307.25</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>535.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.355791</v>
+        <v>6.478705</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.096581</v>
+        <v>6.436663</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.57929</v>
+        <v>6.24706</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.445087</v>
+        <v>-2.243244</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.257898</v>
+        <v>-2.130529</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8156099999999999</v>
+        <v>-1.750779</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.422318</v>
+        <v>-0.023423</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5160979999999999</v>
+        <v>0.07296800000000001</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>0.429346</v>
+        <v>-0.688791</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>1.026833</v>
+        <v>0.245986</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>6.669777</v>
+        <v>8.75699</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>6.398498</v>
+        <v>8.387672</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.450696</v>
+        <v>2.509312</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.582524</v>
+        <v>3.980583</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>188913.453125</v>
+        <v>187042.90625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>186.029999</v>
+        <v>184.070007</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>112.760002</v>
+        <v>111.110001</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>439.269989</v>
+        <v>440.329987</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0806</v>
+        <v>5.0937</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9044</v>
+        <v>5.9353</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7684.339844</v>
+        <v>7653.459961</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26390.132812</v>
+        <v>26360.449219</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52819.558594</v>
+        <v>52381.640625</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4442</v>
+        <v>4456.600098</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>93.269997</v>
+        <v>95.75</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>98.08000199999999</v>
+        <v>100.669998</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1307.25</v>
+        <v>1308.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>535.5</v>
+        <v>527.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>6.478705</v>
+        <v>5.424394</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>6.436663</v>
+        <v>5.315258</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>6.24706</v>
+        <v>4.692362</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.243244</v>
+        <v>-2.007348</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.130529</v>
+        <v>-1.878176</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.750779</v>
+        <v>-1.236603</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.023423</v>
+        <v>-0.425183</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.07296800000000001</v>
+        <v>-0.039594</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.688791</v>
+        <v>-1.512164</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>0.245986</v>
+        <v>0.575478</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>8.75699</v>
+        <v>11.648785</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>8.387672</v>
+        <v>11.249862</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.509312</v>
+        <v>2.626936</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>3.980583</v>
+        <v>2.378641</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1253</v>
+        <v>5.0856</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1247</v>
+        <v>5.085</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1592,19 +1592,19 @@
         <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
         <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>369742</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.086537</v>
+        <v>-1.85271</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.086663</v>
+        <v>-1.852924</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1792,19 +1792,19 @@
         <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
         <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187042.90625</v>
+        <v>185144.859375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.070007</v>
+        <v>182.330002</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.110001</v>
+        <v>109.870003</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.329987</v>
+        <v>440.929993</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0937</v>
+        <v>5.1422</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9353</v>
+        <v>5.9703</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7653.459961</v>
+        <v>7583.859863</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26360.449219</v>
+        <v>26037.785156</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52381.640625</v>
+        <v>52079.46875</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4456.600098</v>
+        <v>4409.5</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.75</v>
+        <v>99.300003</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.669998</v>
+        <v>104.540001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1308.75</v>
+        <v>1316</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>527.25</v>
+        <v>528</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>5.424394</v>
+        <v>4.354584</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.315258</v>
+        <v>4.319718</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.692362</v>
+        <v>3.523985</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.007348</v>
+        <v>-1.873821</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.878176</v>
+        <v>-0.943901</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.236603</v>
+        <v>-0.654197</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.425183</v>
+        <v>-1.33071</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.039594</v>
+        <v>-1.263156</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.512164</v>
+        <v>-2.080306</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>0.575478</v>
+        <v>-0.487466</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>11.648785</v>
+        <v>15.788247</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>11.249862</v>
+        <v>15.526581</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.626936</v>
+        <v>3.195452</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.378641</v>
+        <v>2.524272</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0856</v>
+        <v>5.0979</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.085</v>
+        <v>5.0973</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.85271</v>
+        <v>-1.615331</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.852924</v>
+        <v>-1.615518</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185144.859375</v>
+        <v>187021.609375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.330002</v>
+        <v>184.119995</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.870003</v>
+        <v>111.400002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.929993</v>
+        <v>440.160004</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1422</v>
+        <v>5.083</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9703</v>
+        <v>5.9061</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7583.859863</v>
+        <v>7675.77002</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26037.785156</v>
+        <v>26405.673828</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52079.46875</v>
+        <v>52662.679688</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4409.5</v>
+        <v>4432.399902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>99.300003</v>
+        <v>98.75</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.540001</v>
+        <v>104.110001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1316</v>
+        <v>1311.5</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528</v>
+        <v>525.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.354584</v>
+        <v>5.412391</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.319718</v>
+        <v>5.343859</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.523985</v>
+        <v>4.965612</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.873821</v>
+        <v>-2.045177</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.943901</v>
+        <v>-2.084289</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.654197</v>
+        <v>-1.722492</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.33071</v>
+        <v>-0.13492</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.263156</v>
+        <v>0.1319</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.080306</v>
+        <v>-0.983755</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.487466</v>
+        <v>0.029334</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>15.788247</v>
+        <v>15.146919</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>15.526581</v>
+        <v>15.05139</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.195452</v>
+        <v>2.84258</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.524272</v>
+        <v>2.038835</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1242,19 +1242,19 @@
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
         <v>1.16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="G33" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="34">
@@ -1292,19 +1292,19 @@
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
         <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="36">
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0979</v>
+        <v>5.1149</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0973</v>
+        <v>5.1143</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.615331</v>
+        <v>-1.287247</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.615518</v>
+        <v>-1.287396</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1817,19 +1817,19 @@
         <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
         <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>4.443025</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
-        <v>59.259259</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="57">
@@ -1867,19 +1867,19 @@
         <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
         <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>4.098046</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>59.259259</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187021.609375</v>
+        <v>187039.734375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.119995</v>
+        <v>184.139999</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.400002</v>
+        <v>111.370003</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.160004</v>
+        <v>440.209991</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.083</v>
+        <v>5.0901</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9061</v>
+        <v>5.9107</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7675.77002</v>
+        <v>7664.779785</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26405.673828</v>
+        <v>26356.910156</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52662.679688</v>
+        <v>52650.328125</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4432.399902</v>
+        <v>4430.5</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>98.75</v>
+        <v>99.050003</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.110001</v>
+        <v>104.43</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1311.5</v>
+        <v>1310.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>525.5</v>
+        <v>525.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>5.412391</v>
+        <v>5.422607</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.343859</v>
+        <v>5.355304</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.965612</v>
+        <v>4.937346</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.045177</v>
+        <v>-2.034052</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.084289</v>
+        <v>-1.947526</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.722492</v>
+        <v>-1.645947</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.13492</v>
+        <v>-0.277907</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1319</v>
+        <v>-0.053015</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.983755</v>
+        <v>-1.006978</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>0.029334</v>
+        <v>-0.013543</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>15.146919</v>
+        <v>15.496736</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>15.05139</v>
+        <v>15.40502</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.84258</v>
+        <v>2.783768</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.038835</v>
+        <v>1.990291</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>109.89427</v>
+        <v>5.1149</v>
       </c>
       <c r="G37" t="n">
-        <v>71.604938</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1149</v>
+        <v>5.1143</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1143</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>5.81</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>21.42</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>32.08</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,73 +1535,73 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>368886</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>372616</v>
       </c>
       <c r="G45" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>0.541272</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
         <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>3.74306</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-1.287247</v>
       </c>
       <c r="G47" t="n">
         <v>74.074074</v>
@@ -1610,457 +1610,457 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>0.541272</v>
+        <v>3.743473</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>-1.287396</v>
       </c>
       <c r="G48" t="n">
-        <v>70.37036999999999</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.59426</v>
+        <v>1.596467</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>0.257708</v>
       </c>
       <c r="G49" t="n">
-        <v>70.37036999999999</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>0.888065</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.287247</v>
+        <v>-0.694824</v>
       </c>
       <c r="G50" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>2.123375</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.287396</v>
+        <v>0.826955</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>-0.259972</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>0.777299</v>
       </c>
       <c r="G52" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>4.223453</v>
       </c>
       <c r="G53" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>8.58755</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>2.178243</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.825751</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>3.983297</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>1.5</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>0.002704</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-0.000124</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.002704</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000124</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G59" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002704</v>
+        <v>-0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000124</v>
+        <v>0.39</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002704</v>
+        <v>1.47</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000124</v>
+        <v>-1.25</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>14429715267</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>33157804370</v>
       </c>
       <c r="G62" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>17190165488</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>25763862100</v>
       </c>
       <c r="G63" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>-2760450221</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>7393942270</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>31619880755</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>58921666470</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>46718273016</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>77119199389</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>12206525099</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>14073182023</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>641249369</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>1548184686</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>11309879</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>19241881</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>17842724736</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>27331288667</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>395907378</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>753147930</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>1403790404</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>2221291720</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2245,22 +2245,22 @@
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>42579</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>170442</v>
       </c>
       <c r="G73" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2270,22 +2270,22 @@
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>41657</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>143344</v>
       </c>
       <c r="G74" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>357877575</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>1094109253</v>
       </c>
       <c r="G75" t="n">
         <v>98.765432</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>163332129</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>206264157</v>
       </c>
       <c r="G76" t="n">
         <v>98.765432</v>
@@ -2335,57 +2335,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>31418</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>6294</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>20000</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>1560</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2398,10 +2398,10 @@
         <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>500185177</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>967242706</v>
       </c>
       <c r="G79" t="n">
         <v>98.765432</v>
@@ -2410,7 +2410,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2423,10 +2423,10 @@
         <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>103909023</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>162300453</v>
       </c>
       <c r="G80" t="n">
         <v>98.765432</v>
@@ -2435,57 +2435,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>9788257</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>9868969</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>1182973</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>942383</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>488810441</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>748163251</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1351894846</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>1412673002</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2545,22 +2545,22 @@
         <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>23393</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>1381516</v>
       </c>
       <c r="G85" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2570,22 +2570,22 @@
         <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>40720</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1452782</v>
       </c>
       <c r="G86" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2598,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>401663716</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>893582419</v>
       </c>
       <c r="G87" t="n">
         <v>98.765432</v>
@@ -2610,7 +2610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2623,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>955961547</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1438094595</v>
       </c>
       <c r="G88" t="n">
         <v>98.765432</v>
@@ -2635,57 +2635,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>13124930</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>60</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>40054409</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>24</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2698,10 +2698,10 @@
         <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>349915062</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>1002656682</v>
       </c>
       <c r="G91" t="n">
         <v>98.765432</v>
@@ -2710,7 +2710,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2723,10 +2723,10 @@
         <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>2083530104</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>4653100189</v>
       </c>
       <c r="G92" t="n">
         <v>98.765432</v>
@@ -2735,57 +2735,57 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>26216991</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>33273820</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>196178640</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>199281400</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>1627139024</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>2051566400</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>25418986258</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>34406447895</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2845,22 +2845,22 @@
         <v>46265</v>
       </c>
       <c r="D97" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>6207</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>6950029</v>
       </c>
       <c r="G97" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2870,22 +2870,22 @@
         <v>46265</v>
       </c>
       <c r="D98" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>7200</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>78331372</v>
       </c>
       <c r="G98" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2898,10 +2898,10 @@
         <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>1707992437</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>4828191084</v>
       </c>
       <c r="G99" t="n">
         <v>98.765432</v>
@@ -2910,7 +2910,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2923,10 +2923,10 @@
         <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>4221906804</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>8379911835</v>
       </c>
       <c r="G100" t="n">
         <v>98.765432</v>
@@ -2935,7 +2935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>207990371</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>547298813</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>432290309</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>797225701</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>281324952</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>646488066</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>831821378</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>1790486389</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,57 +3035,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>2282</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>360</v>
       </c>
       <c r="G105" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>2500</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
@@ -3098,10 +3098,10 @@
         <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>504774218</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>4410039153</v>
       </c>
       <c r="G107" t="n">
         <v>98.765432</v>
@@ -3110,7 +3110,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
@@ -3123,10 +3123,10 @@
         <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>1397018249</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>9808807495</v>
       </c>
       <c r="G108" t="n">
         <v>98.765432</v>
@@ -3135,150 +3135,50 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>6305340</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>44621019</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>19690000</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>109088024</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D111" t="n">
-        <v>80</v>
-      </c>
-      <c r="E111" t="n">
-        <v>504774218</v>
-      </c>
-      <c r="F111" t="n">
-        <v>4410039153</v>
-      </c>
-      <c r="G111" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
-        <v>80</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1397018249</v>
-      </c>
-      <c r="F112" t="n">
-        <v>9808807495</v>
-      </c>
-      <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187039.734375</v>
+        <v>187207</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.139999</v>
+        <v>185.210007</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.370003</v>
+        <v>112.300003</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.209991</v>
+        <v>437.649994</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0901</v>
+        <v>5.1262</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9107</v>
+        <v>5.9463</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7664.779785</v>
+        <v>7656.97998</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26356.910156</v>
+        <v>26333.039062</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52650.328125</v>
+        <v>52573.289062</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4430.5</v>
+        <v>4366.200195</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>99.050003</v>
+        <v>100.050003</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.43</v>
+        <v>104.610001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1310.75</v>
+        <v>1280.25</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>525.25</v>
+        <v>510.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>5.422607</v>
+        <v>5.516884</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.355304</v>
+        <v>5.967507</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.937346</v>
+        <v>5.81363</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.034052</v>
+        <v>-2.603764</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.947526</v>
+        <v>-1.252111</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.645947</v>
+        <v>-1.05356</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.277907</v>
+        <v>-0.379386</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.053015</v>
+        <v>-0.143535</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.006978</v>
+        <v>-1.151827</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.013543</v>
+        <v>-1.464645</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>15.496736</v>
+        <v>16.662781</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>15.40502</v>
+        <v>15.603938</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.783768</v>
+        <v>0.39208</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>1.990291</v>
+        <v>-0.92233</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10569</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1149</v>
+        <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1143</v>
+        <v>5.0918</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.0912</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>5.81</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>21.42</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>32.08</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,73 +1535,73 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>368886</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>372616</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>0.541272</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6395690000000001</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>70.37036999999999</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
         <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>3.74306</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.287247</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
         <v>74.074074</v>
@@ -1610,457 +1610,457 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>3.743473</v>
+        <v>0.541272</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.287396</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>74.074074</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>1.596467</v>
+        <v>-0.59426</v>
       </c>
       <c r="F49" t="n">
-        <v>0.257708</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.888065</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.694824</v>
+        <v>-1.733055</v>
       </c>
       <c r="G50" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>2.123375</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.826955</v>
+        <v>-1.733256</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.259972</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>0.777299</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>8.727061000000001</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>4.223453</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>8.58755</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>2.178243</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.825751</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>3.983297</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>1.5</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>0.002704</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.000124</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002704</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000124</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.01</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.02</v>
+        <v>0.002704</v>
       </c>
       <c r="F60" t="n">
-        <v>0.39</v>
+        <v>-0.000124</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>1.47</v>
+        <v>0.002704</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.25</v>
+        <v>-0.000124</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>14429715267</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>33157804370</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D63" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>17190165488</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>25763862100</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>-2760450221</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>7393942270</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>31619880755</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>58921666470</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>46718273016</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>77119199389</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>12206525099</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>14073182023</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>641249369</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>1548184686</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>11309879</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>19241881</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>17842724736</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>27331288667</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>395907378</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>753147930</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>1403790404</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>2221291720</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2245,22 +2245,22 @@
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>42579</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>170442</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2270,22 +2270,22 @@
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>41657</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>143344</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>357877575</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>1094109253</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
         <v>98.765432</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>163332129</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>206264157</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
         <v>98.765432</v>
@@ -2335,57 +2335,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>31418</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>6294</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>27.160494</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>20000</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>1560</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>27.160494</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2398,10 +2398,10 @@
         <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>500185177</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>967242706</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
         <v>98.765432</v>
@@ -2410,7 +2410,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2423,10 +2423,10 @@
         <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>103909023</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>162300453</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
         <v>98.765432</v>
@@ -2435,57 +2435,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>9788257</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>9868969</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>1182973</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>942383</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>488810441</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>748163251</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1351894846</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>1412673002</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2545,22 +2545,22 @@
         <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>23393</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>1381516</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2570,22 +2570,22 @@
         <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>40720</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1452782</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2598,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>401663716</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>893582419</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
         <v>98.765432</v>
@@ -2610,7 +2610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2623,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>955961547</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1438094595</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
         <v>98.765432</v>
@@ -2635,57 +2635,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>13124930</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>60</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>53.08642</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>40054409</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>53.08642</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2698,10 +2698,10 @@
         <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>349915062</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>1002656682</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
         <v>98.765432</v>
@@ -2710,7 +2710,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2723,10 +2723,10 @@
         <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>2083530104</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>4653100189</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
         <v>98.765432</v>
@@ -2735,57 +2735,57 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>26216991</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>33273820</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>196178640</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>199281400</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>1627139024</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>2051566400</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>25418986258</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>34406447895</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2845,22 +2845,22 @@
         <v>46265</v>
       </c>
       <c r="D97" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>6207</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>6950029</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2870,22 +2870,22 @@
         <v>46265</v>
       </c>
       <c r="D98" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>7200</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>78331372</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2898,10 +2898,10 @@
         <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>1707992437</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>4828191084</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
         <v>98.765432</v>
@@ -2910,7 +2910,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2923,10 +2923,10 @@
         <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>4221906804</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>8379911835</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
         <v>98.765432</v>
@@ -2935,7 +2935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>207990371</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>547298813</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>432290309</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>797225701</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>281324952</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>646488066</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>831821378</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>1790486389</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,57 +3035,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>2282</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>360</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>2500</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
@@ -3098,10 +3098,10 @@
         <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>504774218</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>4410039153</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
         <v>98.765432</v>
@@ -3110,7 +3110,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
@@ -3123,10 +3123,10 @@
         <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>1397018249</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>9808807495</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
         <v>98.765432</v>
@@ -3135,50 +3135,150 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>6305340</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>44621019</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>93.82716000000001</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6.17284</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D111" t="n">
+        <v>80</v>
+      </c>
+      <c r="E111" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="F111" t="n">
+        <v>4410039153</v>
+      </c>
+      <c r="G111" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D110" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>185.210007</v>
+        <v>183.850006</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>112.300003</v>
+        <v>110.830002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>437.649994</v>
+        <v>443.149994</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4366.200195</v>
+        <v>4408.899902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1280.25</v>
+        <v>1299</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>510.25</v>
+        <v>532</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.967507</v>
+        <v>5.189385</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>5.81363</v>
+        <v>4.428535</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.603764</v>
+        <v>-1.379773</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.464645</v>
+        <v>-0.501009</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>0.39208</v>
+        <v>1.86238</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.92233</v>
+        <v>3.300971</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,7 +1235,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="G33" t="n">
         <v>74.074074</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="G34" t="n">
         <v>74.074074</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>96.95313</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>110.22154</v>
       </c>
       <c r="G35" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>96.95313</v>
+        <v>97.10569</v>
       </c>
       <c r="F36" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
       <c r="G36" t="n">
         <v>71.604938</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>109.89427</v>
+        <v>5.0918</v>
       </c>
       <c r="G37" t="n">
-        <v>71.604938</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0918</v>
+        <v>5.0912</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0912</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.541272</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>0.541272</v>
+        <v>-0.59426</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
       <c r="G48" t="n">
         <v>70.37036999999999</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.59426</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>-1.733055</v>
       </c>
       <c r="G49" t="n">
-        <v>70.37036999999999</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.733055</v>
+        <v>-1.733256</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.733256</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>0.777299</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.002704</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000124</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.002704</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000124</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002704</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000124</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002704</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000124</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187207</v>
+        <v>185371.140625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.850006</v>
+        <v>182.369995</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.830002</v>
+        <v>109.68</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>443.149994</v>
+        <v>443.630005</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1262</v>
+        <v>5.1539</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9463</v>
+        <v>5.9512</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7656.97998</v>
+        <v>7626.77002</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26333.039062</v>
+        <v>26209.451172</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52573.289062</v>
+        <v>52482.101562</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4408.899902</v>
+        <v>4331.600098</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.050003</v>
+        <v>102.970001</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.610001</v>
+        <v>107.419998</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1299</v>
+        <v>1306.5</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>532</v>
+        <v>530.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>5.516884</v>
+        <v>4.482125</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.189385</v>
+        <v>4.3426</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.428535</v>
+        <v>3.344957</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.379773</v>
+        <v>-1.27295</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.252111</v>
+        <v>-0.718517</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.05356</v>
+        <v>-0.972025</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.379386</v>
+        <v>-0.772431</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.143535</v>
+        <v>-0.612188</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.151827</v>
+        <v>-1.323277</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.501009</v>
+        <v>-2.245492</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>16.662781</v>
+        <v>20.067629</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>15.603938</v>
+        <v>18.70925</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.86238</v>
+        <v>2.4505</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>3.300971</v>
+        <v>3.009709</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02154</v>
+        <v>0.021664</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02154</v>
+        <v>0.021664</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1235,7 +1235,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="G33" t="n">
         <v>74.074074</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="G34" t="n">
         <v>74.074074</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>96.95313</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>110.22154</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.10569</v>
+        <v>96.95313</v>
       </c>
       <c r="F36" t="n">
-        <v>109.89427</v>
+        <v>110.22154</v>
       </c>
       <c r="G36" t="n">
         <v>71.604938</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10569</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0918</v>
+        <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0912</v>
+        <v>5.0918</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.0912</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.541272</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6395690000000001</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>70.37036999999999</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.59426</v>
+        <v>0.541272</v>
       </c>
       <c r="F48" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
         <v>70.37036999999999</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.59426</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.733055</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.733256</v>
+        <v>-1.733055</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>-1.733256</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>0.777299</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002704</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000124</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.002704</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000124</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.00258</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000124</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.00258</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000124</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185371.140625</v>
+        <v>185959.625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.369995</v>
+        <v>183.039993</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.68</v>
+        <v>109.540001</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>443.630005</v>
+        <v>440.839996</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1539</v>
+        <v>5.1456</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9512</v>
+        <v>5.9456</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7626.77002</v>
+        <v>7585.890137</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26209.451172</v>
+        <v>26026.601562</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52482.101562</v>
+        <v>51923.578125</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -698,10 +698,10 @@
         <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1755.300049</v>
+        <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4331.600098</v>
+        <v>4329.299805</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>102.970001</v>
+        <v>103.730003</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>107.419998</v>
+        <v>102.610001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>530.5</v>
+        <v>531.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.482125</v>
+        <v>4.813816</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3426</v>
+        <v>4.725938</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.344957</v>
+        <v>3.213044</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.27295</v>
+        <v>-1.893849</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.718517</v>
+        <v>-0.878408</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.972025</v>
+        <v>-1.065208</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.772431</v>
+        <v>-1.304296</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.612188</v>
+        <v>-1.305565</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.323277</v>
+        <v>-2.373412</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1048,10 +1048,10 @@
         <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>1.578075</v>
+        <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.245492</v>
+        <v>-3.396189</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>20.067629</v>
+        <v>20.953826</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>18.70925</v>
+        <v>13.393749</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>3.009709</v>
+        <v>3.15534</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0918</v>
+        <v>5.1696</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0912</v>
+        <v>5.169</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.733055</v>
+        <v>-0.231589</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.733256</v>
+        <v>-0.231616</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185959.625</v>
+        <v>185399.484375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.039993</v>
+        <v>182.539993</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.839996</v>
+        <v>442.51001</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1456</v>
+        <v>5.1546</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9456</v>
+        <v>5.9476</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7585.890137</v>
+        <v>7600.680176</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26026.601562</v>
+        <v>26133.207031</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51923.578125</v>
+        <v>51940.390625</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4329.299805</v>
+        <v>4376.899902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>103.730003</v>
+        <v>103.169998</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>102.610001</v>
+        <v>106.949997</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1306.5</v>
+        <v>1320.25</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>531.25</v>
+        <v>535</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.813816</v>
+        <v>4.4981</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.725938</v>
+        <v>4.439864</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.893849</v>
+        <v>-1.522198</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.878408</v>
+        <v>-0.705032</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.065208</v>
+        <v>-1.031931</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.304296</v>
+        <v>-1.111871</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.305565</v>
+        <v>-0.9013099999999999</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.373412</v>
+        <v>-2.341801</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.396189</v>
+        <v>-2.334042</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>20.953826</v>
+        <v>20.300834</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>13.393749</v>
+        <v>18.189855</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4505</v>
+        <v>3.52872</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>3.15534</v>
+        <v>3.883495</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1317,19 +1317,19 @@
         <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.95313</v>
+        <v>96.96513</v>
       </c>
       <c r="F36" t="n">
-        <v>110.22154</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="37">
@@ -1342,19 +1342,19 @@
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10569</v>
+        <v>97.10777</v>
       </c>
       <c r="F37" t="n">
-        <v>109.89427</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="38">
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1696</v>
+        <v>5.149</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.169</v>
+        <v>5.1484</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1617,19 +1617,19 @@
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.541272</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
-        <v>70.37036999999999</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="49">
@@ -1642,19 +1642,19 @@
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.59426</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>70.37036999999999</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.231589</v>
+        <v>-0.629149</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.231616</v>
+        <v>-0.6292219999999999</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185399.484375</v>
+        <v>184544.75</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.539993</v>
+        <v>181.610001</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.540001</v>
+        <v>109.209999</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>442.51001</v>
+        <v>444.839996</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1546</v>
+        <v>5.1599</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9476</v>
+        <v>5.9317</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7600.680176</v>
+        <v>7630.069824</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26133.207031</v>
+        <v>26407.919922</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51940.390625</v>
+        <v>51741.929688</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4376.899902</v>
+        <v>4410.5</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>103.169998</v>
+        <v>100.389999</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>106.949997</v>
+        <v>102.959999</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1320.25</v>
+        <v>1312.5</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4981</v>
+        <v>4.01634</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.439864</v>
+        <v>3.907771</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.213044</v>
+        <v>2.902103</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.522198</v>
+        <v>-1.003674</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.705032</v>
+        <v>-0.602936</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.031931</v>
+        <v>-1.296501</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.111871</v>
+        <v>-0.729499</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9013099999999999</v>
+        <v>0.140417</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.341801</v>
+        <v>-2.714947</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.334042</v>
+        <v>-1.584291</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>20.300834</v>
+        <v>17.059231</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>18.189855</v>
+        <v>13.78053</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.52872</v>
+        <v>2.920996</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>3.883495</v>
+        <v>2.524272</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1176,7 +1176,7 @@
         <v>6.25</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="G30" t="n">
         <v>75.30864200000001</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.149</v>
+        <v>5.1527</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1484</v>
+        <v>5.152</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.629149</v>
+        <v>-0.557743</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.6292219999999999</v>
+        <v>-0.559738</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1901,7 +1901,7 @@
         <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>184544.75</v>
+        <v>184955.578125</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>181.610001</v>
+        <v>182.089996</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.209999</v>
+        <v>108.889999</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.839996</v>
+        <v>444.149994</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1599</v>
+        <v>5.1563</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9317</v>
+        <v>5.9081</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7630.069824</v>
+        <v>7623.669922</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26407.919922</v>
+        <v>26423.677734</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51741.929688</v>
+        <v>51562.378906</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4410.5</v>
+        <v>4391</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.389999</v>
+        <v>97.860001</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>102.959999</v>
+        <v>100.040001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -763,23 +763,15 @@
           <t>yahoo_soja</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>61</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1256</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1312.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>75.30864200000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +793,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528</v>
+        <v>526.75</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +818,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.01634</v>
+        <v>4.247898</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +843,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.907771</v>
+        <v>4.182399</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +868,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>2.902103</v>
+        <v>2.600586</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +893,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.003674</v>
+        <v>-1.15723</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +918,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.602936</v>
+        <v>-0.6722860000000001</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +943,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.296501</v>
+        <v>-1.689207</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +968,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.729499</v>
+        <v>-0.812764</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +993,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.140417</v>
+        <v>0.200172</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1018,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.714947</v>
+        <v>-3.052538</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1043,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.584291</v>
+        <v>-2.019413</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1068,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>17.059231</v>
+        <v>14.10914</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1093,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>13.78053</v>
+        <v>10.553656</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1113,23 +1105,15 @@
           <t>yahoo_ret_soja</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>60</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-1.612261</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.920996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>74.074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1151,7 +1135,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.524272</v>
+        <v>2.281553</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1185,7 +1169,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1198,10 +1182,10 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.022184</v>
+        <v>0.022435</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05166</v>
+        <v>0.051587</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1210,32 +1194,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.022184</v>
+        <v>-0.64</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05166</v>
+        <v>-0.22</v>
       </c>
       <c r="G32" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,7 +1232,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="F33" t="n">
         <v>-0.32</v>
@@ -1260,157 +1244,157 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.64</v>
+        <v>96.96513</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.22</v>
+        <v>109.91611</v>
       </c>
       <c r="G34" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>97.10777</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>114.40189</v>
       </c>
       <c r="G35" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E36" t="n">
-        <v>96.96513</v>
+        <v>5.4394</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>5.1521</v>
       </c>
       <c r="G36" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10777</v>
+        <v>5.4388</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.1515</v>
       </c>
       <c r="G37" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>1894119</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1527</v>
+        <v>2731513</v>
       </c>
       <c r="G38" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>2546936</v>
       </c>
       <c r="F39" t="n">
-        <v>5.152</v>
+        <v>4640730</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1407,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>2.34</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>4.88</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1419,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1432,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>1.43</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>3.31</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1444,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1457,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>21.42</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>32.08</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,123 +1469,123 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>368886</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>372616</v>
       </c>
       <c r="G43" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>0.537905</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>-0.219358</v>
       </c>
       <c r="G44" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>-0.594556</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>4.057001</v>
       </c>
       <c r="G45" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>3.74306</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>-0.569322</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
         <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>3.743473</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.569388</v>
       </c>
       <c r="G47" t="n">
         <v>74.074074</v>
@@ -1610,7 +1594,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1607,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>0.888065</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>-0.694824</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,7 +1619,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -1648,10 +1632,10 @@
         <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>2.123375</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.826955</v>
       </c>
       <c r="G49" t="n">
         <v>71.604938</v>
@@ -1660,407 +1644,407 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>-0.259972</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.557743</v>
+        <v>0.777299</v>
       </c>
       <c r="G50" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>8.58755</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.559738</v>
+        <v>2.178243</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>8.825751</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>3.983297</v>
       </c>
       <c r="G52" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>1.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>-0.25</v>
       </c>
       <c r="G53" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>0.001809</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>-0.000197</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>-0.01</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>0.3</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>0.13</v>
       </c>
       <c r="G56" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.47</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-1.25</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>43861</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>14429715267</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>33157804370</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>17190165488</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G59" t="n">
-        <v>74.074074</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00206</v>
+        <v>-2760450221</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000124</v>
+        <v>7393942270</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00206</v>
+        <v>31619880755</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000124</v>
+        <v>58921666470</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>46718273016</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>77119199389</v>
       </c>
       <c r="G62" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>12206525099</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>14073182023</v>
       </c>
       <c r="G63" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>641249369</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>1548184686</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>11309879</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>19241881</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2057,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>17842724736</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>27331288667</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2069,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2082,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>395907378</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>753147930</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2094,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2107,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>1403790404</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>2221291720</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2119,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2145,22 +2129,22 @@
         <v>46265</v>
       </c>
       <c r="D69" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>42579</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>170442</v>
       </c>
       <c r="G69" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2170,22 +2154,22 @@
         <v>46265</v>
       </c>
       <c r="D70" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>41657</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>143344</v>
       </c>
       <c r="G70" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2182,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>357877575</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>1094109253</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2194,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2207,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>163332129</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>206264157</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,57 +2219,57 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>31418</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>6294</v>
       </c>
       <c r="G73" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>20000</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>1560</v>
       </c>
       <c r="G74" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2282,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>500185177</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>967242706</v>
       </c>
       <c r="G75" t="n">
         <v>98.765432</v>
@@ -2310,7 +2294,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2307,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>103909023</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>162300453</v>
       </c>
       <c r="G76" t="n">
         <v>98.765432</v>
@@ -2335,7 +2319,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2329,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>9788257</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>9868969</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,22 +2354,22 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>1182973</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>942383</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2398,10 +2382,10 @@
         <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>488810441</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>748163251</v>
       </c>
       <c r="G79" t="n">
         <v>98.765432</v>
@@ -2410,7 +2394,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2423,10 +2407,10 @@
         <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>1351894846</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1412673002</v>
       </c>
       <c r="G80" t="n">
         <v>98.765432</v>
@@ -2435,57 +2419,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>23393</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>1381516</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>40720</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>1452782</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2482,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>401663716</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>893582419</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2494,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2507,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>955961547</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>1438094595</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,57 +2519,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>13124930</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>60</v>
       </c>
       <c r="G85" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>40054409</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>24</v>
       </c>
       <c r="G86" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2582,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>349915062</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1002656682</v>
       </c>
       <c r="G87" t="n">
         <v>98.765432</v>
@@ -2610,7 +2594,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2607,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>2083530104</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>4653100189</v>
       </c>
       <c r="G88" t="n">
         <v>98.765432</v>
@@ -2635,7 +2619,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2629,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>26216991</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>33273820</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,22 +2654,22 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>196178640</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>199281400</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2698,10 +2682,10 @@
         <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>1627139024</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>2051566400</v>
       </c>
       <c r="G91" t="n">
         <v>98.765432</v>
@@ -2710,7 +2694,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2723,10 +2707,10 @@
         <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>25418986258</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>34406447895</v>
       </c>
       <c r="G92" t="n">
         <v>98.765432</v>
@@ -2735,57 +2719,57 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>6207</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>6950029</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>7200</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>78331372</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2782,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>1707992437</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>4828191084</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2794,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2807,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>4221906804</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>8379911835</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2819,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2832,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>207990371</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>547298813</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2844,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2857,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>432290309</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>797225701</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2869,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2898,10 +2882,10 @@
         <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>281324952</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>646488066</v>
       </c>
       <c r="G99" t="n">
         <v>98.765432</v>
@@ -2910,7 +2894,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2923,10 +2907,10 @@
         <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>831821378</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>1790486389</v>
       </c>
       <c r="G100" t="n">
         <v>98.765432</v>
@@ -2935,57 +2919,57 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>2282</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>360</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>2500</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2982,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>504774218</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>4410039153</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +2994,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3007,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>1397018249</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>9808807495</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3019,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3045,22 +3029,22 @@
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>6305340</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>44621019</v>
       </c>
       <c r="G105" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3070,215 +3054,15 @@
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>19690000</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>109088024</v>
       </c>
       <c r="G106" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D107" t="n">
-        <v>80</v>
-      </c>
-      <c r="E107" t="n">
-        <v>281324952</v>
-      </c>
-      <c r="F107" t="n">
-        <v>646488066</v>
-      </c>
-      <c r="G107" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C108" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D108" t="n">
-        <v>80</v>
-      </c>
-      <c r="E108" t="n">
-        <v>831821378</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1790486389</v>
-      </c>
-      <c r="G108" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>43890</v>
-      </c>
-      <c r="C109" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>2282</v>
-      </c>
-      <c r="F109" t="n">
-        <v>360</v>
-      </c>
-      <c r="G109" t="n">
-        <v>6.17284</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>43890</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D110" t="n">
-        <v>5</v>
-      </c>
-      <c r="E110" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>6.17284</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D111" t="n">
-        <v>80</v>
-      </c>
-      <c r="E111" t="n">
-        <v>504774218</v>
-      </c>
-      <c r="F111" t="n">
-        <v>4410039153</v>
-      </c>
-      <c r="G111" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
-        <v>80</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1397018249</v>
-      </c>
-      <c r="F112" t="n">
-        <v>9808807495</v>
-      </c>
-      <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>184955.578125</v>
+        <v>185229</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.089996</v>
+        <v>183.279999</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.889999</v>
+        <v>109.690002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.149994</v>
+        <v>442.600006</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1563</v>
+        <v>5.1421</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9081</v>
+        <v>5.9057</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7623.669922</v>
+        <v>7650.5</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26423.677734</v>
+        <v>26522.539062</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51562.378906</v>
+        <v>51682.640625</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4391</v>
+        <v>4424.899902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>97.860001</v>
+        <v>100.300003</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.040001</v>
+        <v>103.870003</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -763,15 +763,23 @@
           <t>yahoo_soja</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1256</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1303.5</v>
+      </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="15">
@@ -793,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>526.75</v>
+        <v>527.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -818,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.247898</v>
+        <v>4.402009</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -843,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.182399</v>
+        <v>4.863257</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -868,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>2.600586</v>
+        <v>3.354382</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -893,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.15723</v>
+        <v>-1.50217</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -918,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6722860000000001</v>
+        <v>-0.9458299999999999</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -943,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.689207</v>
+        <v>-1.729141</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -968,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.812764</v>
+        <v>-0.463694</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -993,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.200172</v>
+        <v>0.57506</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1018,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.052538</v>
+        <v>-2.826422</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1043,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.019413</v>
+        <v>-1.262972</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1068,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>14.10914</v>
+        <v>16.954292</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1093,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>10.553656</v>
+        <v>14.78617</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1105,15 +1113,23 @@
           <t>yahoo_ret_soja</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.612261</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.215252</v>
+      </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="29">
@@ -1135,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.281553</v>
+        <v>2.427184</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1169,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1185,7 +1201,7 @@
         <v>0.022435</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051587</v>
+        <v>0.051526</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1194,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.64</v>
+        <v>0.022435</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.22</v>
+        <v>0.051587</v>
       </c>
       <c r="G32" t="n">
-        <v>74.074074</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1232,7 +1248,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
         <v>-0.32</v>
@@ -1244,82 +1260,82 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>96.96513</v>
+        <v>-0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>109.91611</v>
+        <v>-0.22</v>
       </c>
       <c r="G34" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>97.10777</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>114.40189</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>5.4394</v>
+        <v>96.96513</v>
       </c>
       <c r="F36" t="n">
-        <v>5.1521</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -1332,10 +1348,10 @@
         <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1515</v>
+        <v>5.1575</v>
       </c>
       <c r="G37" t="n">
         <v>75.30864200000001</v>
@@ -1344,32 +1360,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>1894119</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>2731513</v>
+        <v>5.1569</v>
       </c>
       <c r="G38" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -1382,10 +1398,10 @@
         <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>2546936</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>4640730</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
         <v>72.839506</v>
@@ -1394,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1407,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>2.34</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>4.88</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1419,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1432,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1.43</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>3.31</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1444,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1457,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>21.42</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>32.08</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1469,98 +1485,98 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>368886</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>372616</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>0.537905</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.219358</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.594556</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>4.057001</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>3.74306</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.569322</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
         <v>74.074074</v>
@@ -1569,432 +1585,432 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>3.743473</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.569388</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>0.888065</v>
+        <v>3.74306</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.694824</v>
+        <v>-0.465107</v>
       </c>
       <c r="G48" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>2.123375</v>
+        <v>3.743473</v>
       </c>
       <c r="F49" t="n">
-        <v>0.826955</v>
+        <v>-0.465161</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.259972</v>
+        <v>1.596467</v>
       </c>
       <c r="F50" t="n">
-        <v>0.777299</v>
+        <v>0.257708</v>
       </c>
       <c r="G50" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>8.58755</v>
+        <v>0.888065</v>
       </c>
       <c r="F51" t="n">
-        <v>2.178243</v>
+        <v>-0.694824</v>
       </c>
       <c r="G51" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>8.825751</v>
+        <v>2.123375</v>
       </c>
       <c r="F52" t="n">
-        <v>3.983297</v>
+        <v>0.826955</v>
       </c>
       <c r="G52" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>1.5</v>
+        <v>-0.259972</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.25</v>
+        <v>0.777299</v>
       </c>
       <c r="G53" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>0.001809</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.000197</v>
+        <v>4.223453</v>
       </c>
       <c r="G54" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.01</v>
+        <v>8.58755</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3</v>
+        <v>2.178243</v>
       </c>
       <c r="G55" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>8.825751</v>
       </c>
       <c r="F56" t="n">
-        <v>0.13</v>
+        <v>3.983297</v>
       </c>
       <c r="G56" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.25</v>
+        <v>-0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>14429715267</v>
+        <v>0.001809</v>
       </c>
       <c r="F58" t="n">
-        <v>33157804370</v>
+        <v>-0.000259</v>
       </c>
       <c r="G58" t="n">
-        <v>98.765432</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D59" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>17190165488</v>
+        <v>0.001809</v>
       </c>
       <c r="F59" t="n">
-        <v>25763862100</v>
+        <v>-0.000197</v>
       </c>
       <c r="G59" t="n">
-        <v>98.765432</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>-2760450221</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>7393942270</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>31619880755</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>58921666470</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>46718273016</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>77119199389</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D63" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>12206525099</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>14073182023</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -2007,10 +2023,10 @@
         <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>641249369</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>1548184686</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
         <v>98.765432</v>
@@ -2019,7 +2035,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -2032,10 +2048,10 @@
         <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>11309879</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>19241881</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
         <v>98.765432</v>
@@ -2044,7 +2060,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2057,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>17842724736</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>27331288667</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2069,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2082,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>395907378</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>753147930</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2094,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2107,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>1403790404</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>2221291720</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2119,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2129,22 +2145,22 @@
         <v>46265</v>
       </c>
       <c r="D69" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>42579</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>170442</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2154,22 +2170,22 @@
         <v>46265</v>
       </c>
       <c r="D70" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>41657</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>143344</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2182,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>357877575</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>1094109253</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2194,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2207,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>163332129</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>206264157</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2219,57 +2235,57 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>31418</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>6294</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>20000</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>1560</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2279,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>500185177</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>967242706</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2304,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>103909023</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>162300453</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2332,10 +2348,10 @@
         <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>9788257</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>9868969</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
         <v>98.765432</v>
@@ -2344,7 +2360,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2357,10 +2373,10 @@
         <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>1182973</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>942383</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
         <v>98.765432</v>
@@ -2369,57 +2385,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>488810441</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>748163251</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>1351894846</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>1412673002</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
@@ -2429,22 +2445,22 @@
         <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>23393</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>1381516</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
@@ -2454,22 +2470,22 @@
         <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>40720</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1452782</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2482,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>401663716</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>893582419</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2494,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2507,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>955961547</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>1438094595</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2519,57 +2535,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>13124930</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>60</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>40054409</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>24</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2579,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>349915062</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>1002656682</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2604,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>2083530104</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>4653100189</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2632,10 +2648,10 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>26216991</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>33273820</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
         <v>98.765432</v>
@@ -2644,7 +2660,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2657,10 +2673,10 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>196178640</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>199281400</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
         <v>98.765432</v>
@@ -2669,57 +2685,57 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>1627139024</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>2051566400</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>25418986258</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>34406447895</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
@@ -2729,22 +2745,22 @@
         <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>6207</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>6950029</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -2754,22 +2770,22 @@
         <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>7200</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>78331372</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2782,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>1707992437</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>4828191084</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2794,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2807,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>4221906804</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>8379911835</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2819,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2832,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>207990371</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>547298813</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2844,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2857,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>432290309</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>797225701</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2869,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2879,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>281324952</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>646488066</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2904,72 +2920,72 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>831821378</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>1790486389</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>2282</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>360</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>2500</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2982,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>504774218</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4410039153</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -2994,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3007,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>1397018249</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>9808807495</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3019,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3029,40 +3045,190 @@
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>6305340</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>44621019</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D106" t="n">
+        <v>80</v>
+      </c>
+      <c r="E106" t="n">
+        <v>831821378</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1790486389</v>
+      </c>
+      <c r="G106" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D107" t="n">
+        <v>5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2282</v>
+      </c>
+      <c r="F107" t="n">
+        <v>360</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.17284</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6.17284</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D109" t="n">
+        <v>80</v>
+      </c>
+      <c r="E109" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4410039153</v>
+      </c>
+      <c r="G109" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D110" t="n">
+        <v>80</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G110" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D111" t="n">
+        <v>76</v>
+      </c>
+      <c r="E111" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F111" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G111" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D106" t="n">
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
         <v>76</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E112" t="n">
         <v>19690000</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F112" t="n">
         <v>109088024</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G112" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.279999</v>
+        <v>182.470001</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>442.600006</v>
+        <v>443.5</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1421</v>
+        <v>5.1442</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.300003</v>
+        <v>96.08000199999999</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.870003</v>
+        <v>99.290001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.863257</v>
+        <v>4.399818</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.50217</v>
+        <v>-1.301882</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9458299999999999</v>
+        <v>-0.905377</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>16.954292</v>
+        <v>12.033581</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>14.78617</v>
+        <v>9.724835000000001</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1575</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1569</v>
+        <v>5.1575</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.1569</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,157 +1560,157 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>3.74306</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.465107</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.743473</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.465161</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>1.596467</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>0.257708</v>
+        <v>-0.465107</v>
       </c>
       <c r="G50" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>0.888065</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.694824</v>
+        <v>-0.465161</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>0.826955</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.259972</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.777299</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001809</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000259</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001809</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000197</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.001809</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000259</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.001809</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000197</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185229</v>
+        <v>186247.09375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.470001</v>
+        <v>183.380005</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.690002</v>
+        <v>111.540001</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>443.5</v>
+        <v>446.429993</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1442</v>
+        <v>5.1019</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9057</v>
+        <v>5.8593</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7650.5</v>
+        <v>7743.27002</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26522.539062</v>
+        <v>27005.107422</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51682.640625</v>
+        <v>51959.019531</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4424.899902</v>
+        <v>4386.200195</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>96.08000199999999</v>
+        <v>92.339996</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.290001</v>
+        <v>96.199997</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1303.5</v>
+        <v>1325.25</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>527.5</v>
+        <v>542.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.402009</v>
+        <v>4.975845</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.399818</v>
+        <v>4.920475</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.354382</v>
+        <v>5.097525</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.301882</v>
+        <v>-0.649831</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.905377</v>
+        <v>-1.720213</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.729141</v>
+        <v>-2.501239</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.463694</v>
+        <v>0.7432839999999999</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.57506</v>
+        <v>2.404988</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.826422</v>
+        <v>-2.306775</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.262972</v>
+        <v>-2.126516</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>12.033581</v>
+        <v>7.672568</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>9.724835000000001</v>
+        <v>6.310089</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.215252</v>
+        <v>3.9208</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.427184</v>
+        <v>5.339806</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.022435</v>
+        <v>0.022748</v>
       </c>
       <c r="F31" t="n">
         <v>0.051526</v>
@@ -1223,10 +1223,10 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.022435</v>
+        <v>0.022748</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051587</v>
+        <v>0.051526</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.1575</v>
       </c>
       <c r="G37" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1575</v>
+        <v>5.1569</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1569</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>-0.465107</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.465107</v>
+        <v>-0.465161</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.465161</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>0.777299</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>2.178243</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.001496</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000259</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.001496</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000259</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.001809</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000259</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001809</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000197</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>186247.09375</v>
+        <v>185986.109375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.380005</v>
+        <v>183.190002</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.540001</v>
+        <v>111.32</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>446.429993</v>
+        <v>449.369995</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1019</v>
+        <v>5.1202</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8593</v>
+        <v>5.8591</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7743.27002</v>
+        <v>7770.220215</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27005.107422</v>
+        <v>27251.701172</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51959.019531</v>
+        <v>51857.640625</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4386.200195</v>
+        <v>4367.5</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.339996</v>
+        <v>90.910004</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.199997</v>
+        <v>99.470001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1325.25</v>
+        <v>1327.25</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>542.5</v>
+        <v>538.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.975845</v>
+        <v>4.828744</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.920475</v>
+        <v>4.811765</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>5.097525</v>
+        <v>4.890231</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.649831</v>
+        <v>0.004448</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.720213</v>
+        <v>-1.367692</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.501239</v>
+        <v>-2.504571</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7432839999999999</v>
+        <v>1.093918</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.404988</v>
+        <v>3.340086</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.306775</v>
+        <v>-2.497387</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.126516</v>
+        <v>-2.543791</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>7.672568</v>
+        <v>6.005132</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>6.310089</v>
+        <v>9.923752</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.9208</v>
+        <v>4.077632</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>5.339806</v>
+        <v>4.514563</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,10 +1198,10 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.022748</v>
+        <v>0.02315</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051526</v>
+        <v>0.051473</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1223,10 +1223,10 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.022748</v>
+        <v>0.02315</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051526</v>
+        <v>0.051473</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>96.96513</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>97.10777</v>
+        <v>96.96513</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1575</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1569</v>
+        <v>5.1117</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.1111</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.465107</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.465161</v>
+        <v>-1.349004</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>-1.34916</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>0.777299</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>4.223453</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.58755</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>2.178243</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001496</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000259</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001496</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000259</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.001094</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000311</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.001094</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000311</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185986.109375</v>
+        <v>185576.765625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.190002</v>
+        <v>182.740005</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.32</v>
+        <v>111.169998</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.369995</v>
+        <v>449.450012</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1202</v>
+        <v>5.1167</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8591</v>
+        <v>5.858</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7770.220215</v>
+        <v>7768.72998</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27251.701172</v>
+        <v>27249.957031</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51857.640625</v>
+        <v>51828.691406</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4367.5</v>
+        <v>4366</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.910004</v>
+        <v>90.699997</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.470001</v>
+        <v>99.25</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1327.25</v>
+        <v>1327.5</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>538.25</v>
+        <v>538</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.828744</v>
+        <v>4.598023</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.811765</v>
+        <v>4.554301</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.890231</v>
+        <v>4.748894</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004448</v>
+        <v>0.022256</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.367692</v>
+        <v>-1.435113</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.504571</v>
+        <v>-2.522876</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>1.093918</v>
+        <v>1.07453</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>3.340086</v>
+        <v>3.333473</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.497387</v>
+        <v>-2.551817</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.543791</v>
+        <v>-2.577262</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>6.005132</v>
+        <v>5.760255</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>9.923752</v>
+        <v>9.680630000000001</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>4.077632</v>
+        <v>4.097236</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>4.514563</v>
+        <v>4.466019</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>-1.349004</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.349004</v>
+        <v>-1.34916</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.34916</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>-0.259972</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.777299</v>
       </c>
       <c r="G53" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>4.223453</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.001094</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000311</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.001094</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000311</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.001094</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000311</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001094</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000311</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185576.765625</v>
+        <v>187575.046875</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.740005</v>
+        <v>184.679993</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.169998</v>
+        <v>111.980003</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.450012</v>
+        <v>448.869995</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1167</v>
+        <v>5.1471</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.858</v>
+        <v>5.8651</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7768.72998</v>
+        <v>7725.299805</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27249.957031</v>
+        <v>26969.003906</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51828.691406</v>
+        <v>51787.929688</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4366</v>
+        <v>4315.5</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.699997</v>
+        <v>92.099998</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.25</v>
+        <v>97.620003</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1327.5</v>
+        <v>1315.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>538</v>
+        <v>528.75</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.598023</v>
+        <v>5.724329</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.554301</v>
+        <v>5.66426</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.748894</v>
+        <v>5.512114</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.022256</v>
+        <v>-0.106823</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.435113</v>
+        <v>-0.849511</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.522876</v>
+        <v>-2.40473</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>1.07453</v>
+        <v>0.509484</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>3.333473</v>
+        <v>2.268081</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.551817</v>
+        <v>-2.628458</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.577262</v>
+        <v>-3.704117</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>5.760255</v>
+        <v>7.392719</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>9.680630000000001</v>
+        <v>7.879329</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>4.097236</v>
+        <v>3.175848</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>4.466019</v>
+        <v>2.669903</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1198,10 +1198,10 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02315</v>
+        <v>0.023687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051473</v>
+        <v>0.051427</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1223,10 +1223,10 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02315</v>
+        <v>0.023687</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051473</v>
+        <v>0.051427</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1117</v>
+        <v>5.1161</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1111</v>
+        <v>5.1155</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.349004</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.34916</v>
+        <v>-1.264088</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>-1.264235</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>0.826955</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.259972</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.777299</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001094</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000311</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001094</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000311</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000357</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000357</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187575.046875</v>
+        <v>185430.703125</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.679993</v>
+        <v>182.5</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.980003</v>
+        <v>110.760002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>448.869995</v>
+        <v>449.720001</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1471</v>
+        <v>5.1764</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8651</v>
+        <v>5.8909</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7725.299805</v>
+        <v>7687.310059</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26969.003906</v>
+        <v>26805.265625</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51787.929688</v>
+        <v>51308.679688</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4315.5</v>
+        <v>4298.899902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.099998</v>
+        <v>94.66999800000001</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.620003</v>
+        <v>100.309998</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1315.75</v>
+        <v>1316</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528.75</v>
+        <v>527.75</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>5.724329</v>
+        <v>4.515696</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.66426</v>
+        <v>4.416982</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>5.512114</v>
+        <v>4.362579</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.106823</v>
+        <v>0.08234</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.849511</v>
+        <v>-0.28509</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.40473</v>
+        <v>-1.975415</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.509484</v>
+        <v>0.015221</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.268081</v>
+        <v>1.647176</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.628458</v>
+        <v>-3.529542</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.704117</v>
+        <v>-4.074531</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>7.392719</v>
+        <v>10.389454</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>7.879329</v>
+        <v>10.852028</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.175848</v>
+        <v>3.195452</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.669903</v>
+        <v>2.475728</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1201,7 +1201,7 @@
         <v>0.023687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1226,7 +1226,7 @@
         <v>0.023687</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1161</v>
+        <v>5.1414</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1155</v>
+        <v>5.1408</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.264088</v>
+        <v>-0.775822</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.264235</v>
+        <v>-0.775912</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1926,7 +1926,7 @@
         <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
       <c r="G60" t="n">
         <v>74.074074</v>
@@ -1951,7 +1951,7 @@
         <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
       <c r="G61" t="n">
         <v>74.074074</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185430.703125</v>
+        <v>185707.59375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.5</v>
+        <v>182.770004</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.760002</v>
+        <v>110.959999</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.720001</v>
+        <v>449.549988</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1764</v>
+        <v>5.1808</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8909</v>
+        <v>5.8912</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7687.310059</v>
+        <v>7687.410156</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26805.265625</v>
+        <v>26794.8125</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51308.679688</v>
+        <v>51309.371094</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4298.899902</v>
+        <v>4296.299805</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.66999800000001</v>
+        <v>94.720001</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.309998</v>
+        <v>100.32</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1316</v>
+        <v>1317.5</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>527.75</v>
+        <v>530</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.515696</v>
+        <v>4.671762</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.416982</v>
+        <v>4.571464</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.362579</v>
+        <v>4.551024</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08234</v>
+        <v>0.044505</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.28509</v>
+        <v>-0.200336</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.975415</v>
+        <v>-1.970424</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.015221</v>
+        <v>0.016524</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>1.647176</v>
+        <v>1.607537</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.529542</v>
+        <v>-3.528242</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.074531</v>
+        <v>-4.132549</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>10.389454</v>
+        <v>10.44776</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>10.852028</v>
+        <v>10.863081</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.195452</v>
+        <v>3.313076</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.475728</v>
+        <v>2.912621</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185707.59375</v>
+        <v>182428.5</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.770004</v>
+        <v>179.610001</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.959999</v>
+        <v>109.449997</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.549988</v>
+        <v>453.279999</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1808</v>
+        <v>5.204</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8912</v>
+        <v>5.9357</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7687.410156</v>
+        <v>7712.609863</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26794.8125</v>
+        <v>26965.560547</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51309.371094</v>
+        <v>51492.351562</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4296.299805</v>
+        <v>4306.899902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.720001</v>
+        <v>94.099998</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.32</v>
+        <v>99.589996</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1317.5</v>
+        <v>1305</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>530</v>
+        <v>521.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.671762</v>
+        <v>2.823542</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.571464</v>
+        <v>2.763475</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.551024</v>
+        <v>3.128239</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.044505</v>
+        <v>0.874595</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.200336</v>
+        <v>0.246575</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.970424</v>
+        <v>-1.229946</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.016524</v>
+        <v>0.344383</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>1.607537</v>
+        <v>2.255024</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.528242</v>
+        <v>-3.184203</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.132549</v>
+        <v>-3.896019</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>10.44776</v>
+        <v>9.724809</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>10.863081</v>
+        <v>10.056358</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.313076</v>
+        <v>2.332876</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.912621</v>
+        <v>1.213592</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1201,7 +1201,7 @@
         <v>0.023687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1226,7 +1226,7 @@
         <v>0.023687</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1414</v>
+        <v>5.1795</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1408</v>
+        <v>5.1789</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.775822</v>
+        <v>-0.040528</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.775912</v>
+        <v>-0.040533</v>
       </c>
       <c r="G51" t="n">
         <v>74.074074</v>
@@ -1926,7 +1926,7 @@
         <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
       <c r="G60" t="n">
         <v>74.074074</v>
@@ -1951,7 +1951,7 @@
         <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
       <c r="G61" t="n">
         <v>74.074074</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>182428.5</v>
+        <v>183477</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>179.610001</v>
+        <v>180.869995</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.449997</v>
+        <v>109.949997</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>453.279999</v>
+        <v>451.149994</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.204</v>
+        <v>5.1866</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9357</v>
+        <v>5.9081</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7712.609863</v>
+        <v>7743.410156</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26965.560547</v>
+        <v>27068.720703</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51492.351562</v>
+        <v>51828.621094</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4306.899902</v>
+        <v>4321.200195</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.099998</v>
+        <v>92.410004</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.589996</v>
+        <v>104.32</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1305</v>
+        <v>1319</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>521.25</v>
+        <v>528.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>2.823542</v>
+        <v>3.414516</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>2.763475</v>
+        <v>3.484378</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.128239</v>
+        <v>3.599359</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.874595</v>
+        <v>0.400576</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.246575</v>
+        <v>-0.088603</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.229946</v>
+        <v>-1.689207</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.344383</v>
+        <v>0.745108</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.255024</v>
+        <v>2.646214</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.184203</v>
+        <v>-2.55195</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.896019</v>
+        <v>-3.576923</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>9.724809</v>
+        <v>7.754199</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>10.056358</v>
+        <v>15.283459</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.332876</v>
+        <v>3.4307</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>1.213592</v>
+        <v>2.572816</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1201,7 +1201,7 @@
         <v>0.023687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051352</v>
+        <v>0.051321</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1795</v>
+        <v>5.1991</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1789</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,82 +1635,82 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.337734</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.040528</v>
+        <v>0.257708</v>
       </c>
       <c r="G50" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.040533</v>
+        <v>-0.694824</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>-0.259972</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.777299</v>
       </c>
       <c r="G53" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>4.223453</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000464</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000432</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000432</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000432</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.1985</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,82 +1635,82 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>0.337734</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>1.596467</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>0.257708</v>
+        <v>0.337734</v>
       </c>
       <c r="G50" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>0.888065</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.694824</v>
+        <v>0.337773</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>0.826955</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.259972</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.777299</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000557</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000464</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000557</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000432</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000464</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000432</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.869995</v>
+        <v>180.820007</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.949997</v>
+        <v>110.449997</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>451.149994</v>
+        <v>453</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.32</v>
+        <v>97.44000200000001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.484378</v>
+        <v>3.455778</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.599359</v>
+        <v>4.070479</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.400576</v>
+        <v>0.812283</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>15.283459</v>
+        <v>7.680412</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.337734</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>0.337734</v>
+        <v>0.337773</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>0.337773</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>4.223453</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000464</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000432</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000464</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000432</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183477</v>
+        <v>183439.546875</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.820007</v>
+        <v>180.580002</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.449997</v>
+        <v>109.720001</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>453</v>
+        <v>453.25</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1866</v>
+        <v>5.2176</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9081</v>
+        <v>5.9337</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7743.410156</v>
+        <v>7702.799805</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27068.720703</v>
+        <v>26903.330078</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51828.621094</v>
+        <v>51612.378906</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4321.200195</v>
+        <v>4170.799805</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.410004</v>
+        <v>92.589996</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.44000200000001</v>
+        <v>97.69000200000001</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528.25</v>
+        <v>522</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.414516</v>
+        <v>3.393406</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.455778</v>
+        <v>3.318459</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.070479</v>
+        <v>3.382648</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.812283</v>
+        <v>0.867919</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.088603</v>
+        <v>0.508555</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.689207</v>
+        <v>-1.263223</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.745108</v>
+        <v>0.216749</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.646214</v>
+        <v>2.019042</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.55195</v>
+        <v>-2.958528</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.576923</v>
+        <v>-6.932951</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>7.754199</v>
+        <v>7.964079</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>7.680412</v>
+        <v>7.956686</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>3.4307</v>
+        <v>0.921388</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>2.572816</v>
+        <v>1.359223</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1226,7 +1226,7 @@
         <v>0.023687</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051352</v>
+        <v>0.051321</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1985</v>
+        <v>5.2126</v>
       </c>
       <c r="G39" t="n">
         <v>75.30864200000001</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>0.337734</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>0.337773</v>
+        <v>0.337734</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>0.609921</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000557</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000464</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000557</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000432</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000464</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000464</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183439.546875</v>
+        <v>183466.265625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.580002</v>
+        <v>180.649994</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.720001</v>
+        <v>109.889999</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>453.25</v>
+        <v>452.769989</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2176</v>
+        <v>5.2163</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9337</v>
+        <v>5.9327</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7702.799805</v>
+        <v>7702.350098</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26903.330078</v>
+        <v>26899.5</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51612.378906</v>
+        <v>51614.789062</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4170.799805</v>
+        <v>4170.399902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.589996</v>
+        <v>92.55999799999999</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.69000200000001</v>
+        <v>97.769997</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1287</v>
+        <v>1288.25</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.393406</v>
+        <v>3.408466</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.318459</v>
+        <v>3.358505</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.382648</v>
+        <v>3.542827</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.867919</v>
+        <v>0.761096</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.508555</v>
+        <v>0.483515</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.263223</v>
+        <v>-1.279862</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.216749</v>
+        <v>0.210899</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.019042</v>
+        <v>2.004518</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.958528</v>
+        <v>-2.953996</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.932951</v>
+        <v>-6.941874</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>7.964079</v>
+        <v>7.929099</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>7.956686</v>
+        <v>8.045087000000001</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>0.921388</v>
+        <v>1.019408</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>1.359223</v>
+        <v>1.553398</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.1991</v>
       </c>
       <c r="G37" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1991</v>
+        <v>5.2126</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2126</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,157 +1560,157 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>0.537905</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>-0.219358</v>
       </c>
       <c r="G46" t="n">
-        <v>72.839506</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>-0.594556</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>4.057001</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>3.74306</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>0.337734</v>
       </c>
       <c r="G48" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.743473</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.609921</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="F50" t="n">
-        <v>0.337734</v>
+        <v>0.257708</v>
       </c>
       <c r="G50" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="F51" t="n">
-        <v>0.609921</v>
+        <v>-0.694824</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,332 +1735,332 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>4.223453</v>
       </c>
       <c r="G53" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>8.58755</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>2.178243</v>
       </c>
       <c r="G54" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>1.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>-0.25</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>0.000557</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>-0.000464</v>
       </c>
       <c r="G56" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>0.000557</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>-0.000464</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>-0.01</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>0.3</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>0.13</v>
       </c>
       <c r="G59" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000557</v>
+        <v>-0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000464</v>
+        <v>0.39</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000557</v>
+        <v>1.47</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000464</v>
+        <v>-1.25</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>14429715267</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>33157804370</v>
       </c>
       <c r="G62" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>17190165488</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>25763862100</v>
       </c>
       <c r="G63" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>-2760450221</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>7393942270</v>
       </c>
       <c r="G64" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>31619880755</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>58921666470</v>
       </c>
       <c r="G65" t="n">
-        <v>71.604938</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>46718273016</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>77119199389</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>12206525099</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>14073182023</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>641249369</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>1548184686</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>11309879</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>19241881</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>17842724736</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>27331288667</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>395907378</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>753147930</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>1403790404</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>2221291720</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2245,22 +2245,22 @@
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>42579</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>170442</v>
       </c>
       <c r="G73" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2270,22 +2270,22 @@
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>41657</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>143344</v>
       </c>
       <c r="G74" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>357877575</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>1094109253</v>
       </c>
       <c r="G75" t="n">
         <v>98.765432</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>163332129</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>206264157</v>
       </c>
       <c r="G76" t="n">
         <v>98.765432</v>
@@ -2335,57 +2335,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>31418</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>6294</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>20000</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>1560</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2398,10 +2398,10 @@
         <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>500185177</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>967242706</v>
       </c>
       <c r="G79" t="n">
         <v>98.765432</v>
@@ -2410,7 +2410,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2423,10 +2423,10 @@
         <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>103909023</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>162300453</v>
       </c>
       <c r="G80" t="n">
         <v>98.765432</v>
@@ -2435,57 +2435,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>9788257</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>9868969</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>1182973</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>942383</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>488810441</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>748163251</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1351894846</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>1412673002</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2545,22 +2545,22 @@
         <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>23393</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>1381516</v>
       </c>
       <c r="G85" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2570,22 +2570,22 @@
         <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>40720</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1452782</v>
       </c>
       <c r="G86" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2598,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>401663716</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>893582419</v>
       </c>
       <c r="G87" t="n">
         <v>98.765432</v>
@@ -2610,7 +2610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2623,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>955961547</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1438094595</v>
       </c>
       <c r="G88" t="n">
         <v>98.765432</v>
@@ -2635,57 +2635,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>13124930</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>60</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>40054409</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>24</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2698,10 +2698,10 @@
         <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>349915062</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>1002656682</v>
       </c>
       <c r="G91" t="n">
         <v>98.765432</v>
@@ -2710,7 +2710,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2723,10 +2723,10 @@
         <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>2083530104</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>4653100189</v>
       </c>
       <c r="G92" t="n">
         <v>98.765432</v>
@@ -2735,57 +2735,57 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>26216991</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>33273820</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>196178640</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>199281400</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>1627139024</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>2051566400</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>25418986258</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>34406447895</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2845,22 +2845,22 @@
         <v>46265</v>
       </c>
       <c r="D97" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>6207</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>6950029</v>
       </c>
       <c r="G97" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2870,22 +2870,22 @@
         <v>46265</v>
       </c>
       <c r="D98" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>7200</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>78331372</v>
       </c>
       <c r="G98" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2898,10 +2898,10 @@
         <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>1707992437</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>4828191084</v>
       </c>
       <c r="G99" t="n">
         <v>98.765432</v>
@@ -2910,7 +2910,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2923,10 +2923,10 @@
         <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>4221906804</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>8379911835</v>
       </c>
       <c r="G100" t="n">
         <v>98.765432</v>
@@ -2935,7 +2935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>207990371</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>547298813</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>432290309</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>797225701</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>281324952</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>646488066</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>831821378</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>1790486389</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,57 +3035,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>2282</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>360</v>
       </c>
       <c r="G105" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>2500</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
@@ -3098,10 +3098,10 @@
         <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>504774218</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>4410039153</v>
       </c>
       <c r="G107" t="n">
         <v>98.765432</v>
@@ -3110,7 +3110,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
@@ -3123,10 +3123,10 @@
         <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>1397018249</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>9808807495</v>
       </c>
       <c r="G108" t="n">
         <v>98.765432</v>
@@ -3135,150 +3135,50 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>6305340</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>44621019</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>19690000</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>109088024</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D111" t="n">
-        <v>80</v>
-      </c>
-      <c r="E111" t="n">
-        <v>504774218</v>
-      </c>
-      <c r="F111" t="n">
-        <v>4410039153</v>
-      </c>
-      <c r="G111" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
-        <v>80</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1397018249</v>
-      </c>
-      <c r="F112" t="n">
-        <v>9808807495</v>
-      </c>
-      <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183466.265625</v>
+        <v>182477.703125</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.649994</v>
+        <v>179.699997</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.889999</v>
+        <v>108.629997</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>452.769989</v>
+        <v>452.440002</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2163</v>
+        <v>5.2304</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9327</v>
+        <v>5.9299</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7702.350098</v>
+        <v>7660.640137</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26899.5</v>
+        <v>26774.152344</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51614.789062</v>
+        <v>51159.171875</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4170.399902</v>
+        <v>4183.600098</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.55999799999999</v>
+        <v>90.720001</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.769997</v>
+        <v>96.80999799999999</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1288.25</v>
+        <v>1297</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>523</v>
+        <v>521.25</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.408466</v>
+        <v>2.851275</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.358505</v>
+        <v>2.814966</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.542827</v>
+        <v>2.355602</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.761096</v>
+        <v>0.687659</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.483515</v>
+        <v>0.75513</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.279862</v>
+        <v>-1.326454</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.210899</v>
+        <v>-0.331766</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.004518</v>
+        <v>1.529193</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.953996</v>
+        <v>-3.810646</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.941874</v>
+        <v>-6.647326</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>7.929099</v>
+        <v>5.783581</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>8.045087000000001</v>
+        <v>6.984197</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.019408</v>
+        <v>1.705548</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>1.553398</v>
+        <v>1.213592</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1201,7 +1201,7 @@
         <v>0.023687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051321</v>
+        <v>0.051293</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1226,7 +1226,7 @@
         <v>0.023687</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051321</v>
+        <v>0.051293</v>
       </c>
       <c r="G32" t="n">
         <v>75.30864200000001</v>
@@ -1267,50 +1267,50 @@
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
         <v>-0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.22</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>74.074074</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>96.96513</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>97.10777</v>
+        <v>96.96513</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1991</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2126</v>
+        <v>5.2132</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,682 +1385,682 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.2126</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>0.537905</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.219358</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.594556</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>4.057001</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>3.74306</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>0.337734</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.743473</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>0.609921</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>1.596467</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>0.257708</v>
+        <v>0.60985</v>
       </c>
       <c r="G50" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>0.888065</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.694824</v>
+        <v>0.609921</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>0.826955</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>8.727061000000001</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>4.223453</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>8.58755</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>2.178243</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>1.5</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.25</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>0.000557</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.000464</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>0.000557</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.000464</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>61.728395</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.01</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>71.604938</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>0.13</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.02</v>
+        <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>0.39</v>
+        <v>-0.000492</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>1.47</v>
+        <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.25</v>
+        <v>-0.000492</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>14429715267</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>33157804370</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
-        <v>98.765432</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E63" t="n">
-        <v>17190165488</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>25763862100</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>98.765432</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E64" t="n">
-        <v>-2760450221</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>7393942270</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E65" t="n">
-        <v>31619880755</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>58921666470</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>46718273016</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>77119199389</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>12206525099</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>14073182023</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>641249369</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>1548184686</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>11309879</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>19241881</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>17842724736</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>27331288667</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>395907378</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>753147930</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>1403790404</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>2221291720</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2245,22 +2245,22 @@
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>42579</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>170442</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2270,22 +2270,22 @@
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>41657</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>143344</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>357877575</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>1094109253</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
         <v>98.765432</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>163332129</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>206264157</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
         <v>98.765432</v>
@@ -2335,57 +2335,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>31418</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>6294</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>27.160494</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>20000</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>1560</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>27.160494</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2398,10 +2398,10 @@
         <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>500185177</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>967242706</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
         <v>98.765432</v>
@@ -2410,7 +2410,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2423,10 +2423,10 @@
         <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>103909023</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>162300453</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
         <v>98.765432</v>
@@ -2435,57 +2435,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>9788257</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>9868969</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>1182973</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>942383</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>488810441</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>748163251</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1351894846</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>1412673002</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2545,22 +2545,22 @@
         <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>23393</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>1381516</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2570,22 +2570,22 @@
         <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>40720</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1452782</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2598,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>401663716</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>893582419</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
         <v>98.765432</v>
@@ -2610,7 +2610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2623,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>955961547</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1438094595</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
         <v>98.765432</v>
@@ -2635,57 +2635,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>13124930</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>60</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>53.08642</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>40054409</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>53.08642</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2698,10 +2698,10 @@
         <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>349915062</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>1002656682</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
         <v>98.765432</v>
@@ -2710,7 +2710,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2723,10 +2723,10 @@
         <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>2083530104</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>4653100189</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
         <v>98.765432</v>
@@ -2735,57 +2735,57 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>26216991</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>33273820</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>196178640</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>199281400</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>1627139024</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>2051566400</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>25418986258</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>34406447895</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2845,22 +2845,22 @@
         <v>46265</v>
       </c>
       <c r="D97" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>6207</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>6950029</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2870,22 +2870,22 @@
         <v>46265</v>
       </c>
       <c r="D98" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>7200</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>78331372</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2898,10 +2898,10 @@
         <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>1707992437</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>4828191084</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
         <v>98.765432</v>
@@ -2910,7 +2910,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2923,10 +2923,10 @@
         <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>4221906804</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>8379911835</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
         <v>98.765432</v>
@@ -2935,7 +2935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>207990371</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>547298813</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>432290309</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>797225701</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>281324952</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>646488066</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>831821378</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>1790486389</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,57 +3035,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>2282</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>360</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>2500</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
@@ -3098,10 +3098,10 @@
         <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>504774218</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>4410039153</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
         <v>98.765432</v>
@@ -3110,7 +3110,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
@@ -3123,10 +3123,10 @@
         <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>1397018249</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>9808807495</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
         <v>98.765432</v>
@@ -3135,50 +3135,150 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>6305340</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>44621019</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>93.82716000000001</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6.17284</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D111" t="n">
+        <v>80</v>
+      </c>
+      <c r="E111" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="F111" t="n">
+        <v>4410039153</v>
+      </c>
+      <c r="G111" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D110" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>182477.703125</v>
+        <v>182503.359375</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>179.699997</v>
+        <v>179.679993</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.629997</v>
+        <v>108.690002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>452.440002</v>
+        <v>452.390015</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2304</v>
+        <v>5.2357</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9299</v>
+        <v>5.9313</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7660.640137</v>
+        <v>7660.899902</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26774.152344</v>
+        <v>26779.210938</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51159.171875</v>
+        <v>51162.320312</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4183.600098</v>
+        <v>4185.399902</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.720001</v>
+        <v>90.44000200000001</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.80999799999999</v>
+        <v>96.769997</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1297</v>
+        <v>1298.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>521.25</v>
+        <v>522</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>2.851275</v>
+        <v>2.865736</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>2.814966</v>
+        <v>2.803521</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>2.355602</v>
+        <v>2.412141</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.687659</v>
+        <v>0.676535</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.75513</v>
+        <v>0.857227</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.326454</v>
+        <v>-1.303158</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.331766</v>
+        <v>-0.328386</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>1.529193</v>
+        <v>1.548375</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.810646</v>
+        <v>-3.804727</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.647326</v>
+        <v>-6.607165</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>5.783581</v>
+        <v>5.45709</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>6.984197</v>
+        <v>6.939992</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.705548</v>
+        <v>1.842776</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>1.213592</v>
+        <v>1.359223</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>6.25</v>
+        <v>0.023687</v>
       </c>
       <c r="F30" t="n">
-        <v>13.75</v>
+        <v>0.051293</v>
       </c>
       <c r="G30" t="n">
         <v>75.30864200000001</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1210,107 +1210,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.023687</v>
+        <v>1.16</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051293</v>
+        <v>-0.32</v>
       </c>
       <c r="G32" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
-        <v>74.074074</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.2204</v>
       </c>
       <c r="G37" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2132</v>
+        <v>5.2126</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2126</v>
+        <v>7397669</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
       <c r="G40" t="n">
         <v>74.074074</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
       <c r="G41" t="n">
         <v>74.074074</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
       <c r="G42" t="n">
         <v>74.074074</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
         <v>74.074074</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
         <v>74.074074</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
         <v>74.074074</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
         <v>74.074074</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.748803</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>0.60985</v>
+        <v>0.609921</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>0.609921</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>72.839506</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>72.839506</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>0.777299</v>
       </c>
       <c r="G54" t="n">
         <v>72.839506</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
-        <v>60.493827</v>
+        <v>61.728395</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>3.983297</v>
       </c>
       <c r="G57" t="n">
-        <v>61.728395</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000492</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000492</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000492</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000492</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
         <v>72.839506</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>59</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
         <v>72.839506</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>72.839506</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>72.839506</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>182503.359375</v>
+        <v>185742.0625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>179.679993</v>
+        <v>182.880005</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.690002</v>
+        <v>110.900002</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>452.390015</v>
+        <v>450.890015</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2357</v>
+        <v>5.1848</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9313</v>
+        <v>5.8759</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7660.899902</v>
+        <v>7715.97998</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26779.210938</v>
+        <v>27077.017578</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51162.320312</v>
+        <v>51323.691406</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4185.399902</v>
+        <v>4191.299805</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.44000200000001</v>
+        <v>91.379997</v>
       </c>
       <c r="G12" t="n">
         <v>75.30864200000001</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.769997</v>
+        <v>98.83000199999999</v>
       </c>
       <c r="G13" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1298.75</v>
+        <v>1309.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>522</v>
+        <v>513.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>2.865736</v>
+        <v>4.69119</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>2.803521</v>
+        <v>4.634401</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>2.412141</v>
+        <v>4.494492</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.676535</v>
+        <v>0.342719</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.857227</v>
+        <v>-0.123278</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.303158</v>
+        <v>-2.22502</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.328386</v>
+        <v>0.388229</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>1.548375</v>
+        <v>2.677676</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.804727</v>
+        <v>-3.501317</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.607165</v>
+        <v>-6.475515</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>5.45709</v>
+        <v>6.553166</v>
       </c>
       <c r="G26" t="n">
         <v>74.074074</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>6.939992</v>
+        <v>9.216493</v>
       </c>
       <c r="G27" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.842776</v>
+        <v>2.705352</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>1.359223</v>
+        <v>-0.291262</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>0.023687</v>
+        <v>6.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.051293</v>
+        <v>13.75</v>
       </c>
       <c r="G30" t="n">
         <v>75.30864200000001</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1201,7 +1201,7 @@
         <v>0.023687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051293</v>
+        <v>0.051268</v>
       </c>
       <c r="G31" t="n">
         <v>75.30864200000001</v>
@@ -1210,107 +1210,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>1.16</v>
+        <v>0.023687</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.32</v>
+        <v>0.051268</v>
       </c>
       <c r="G32" t="n">
-        <v>74.074074</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G33" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>74.074074</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>96.96513</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>97.10777</v>
+        <v>96.96513</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F37" t="n">
-        <v>5.2204</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2126</v>
+        <v>5.2204</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7397669</v>
+        <v>5.2198</v>
       </c>
       <c r="G39" t="n">
-        <v>74.074074</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
         <v>74.074074</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
         <v>74.074074</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
         <v>74.074074</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
         <v>74.074074</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
         <v>74.074074</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
         <v>74.074074</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
         <v>74.074074</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F49" t="n">
-        <v>0.748803</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>0.609921</v>
+        <v>0.748803</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>0.7488899999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
         <v>72.839506</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
         <v>72.839506</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>0.777299</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
         <v>72.839506</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>4.223453</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.58755</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>3.348378</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
-        <v>61.728395</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>8.825751</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>3.983297</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
-        <v>60.493827</v>
+        <v>61.728395</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000557</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000492</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000557</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000492</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>-0.000517</v>
       </c>
       <c r="G60" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03</v>
+        <v>-0.000517</v>
       </c>
       <c r="G61" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
         <v>72.839506</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>59</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
         <v>72.839506</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185742.0625</v>
+        <v>185892.640625</v>
       </c>
       <c r="G2" t="n">
         <v>75.30864200000001</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.880005</v>
+        <v>183.020004</v>
       </c>
       <c r="G3" t="n">
         <v>75.30864200000001</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.900002</v>
+        <v>110.860001</v>
       </c>
       <c r="G4" t="n">
         <v>75.30864200000001</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>450.890015</v>
+        <v>451.519989</v>
       </c>
       <c r="G5" t="n">
         <v>75.30864200000001</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1848</v>
+        <v>5.1838</v>
       </c>
       <c r="G6" t="n">
         <v>75.30864200000001</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8759</v>
+        <v>5.8751</v>
       </c>
       <c r="G7" t="n">
         <v>75.30864200000001</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7715.97998</v>
+        <v>7711.649902</v>
       </c>
       <c r="G8" t="n">
         <v>75.30864200000001</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27077.017578</v>
+        <v>27062.792969</v>
       </c>
       <c r="G9" t="n">
         <v>75.30864200000001</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51323.691406</v>
+        <v>51319.070312</v>
       </c>
       <c r="G10" t="n">
         <v>75.30864200000001</v>
@@ -701,7 +701,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4191.299805</v>
+        <v>4189.299805</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1309.75</v>
+        <v>1306.5</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>513.5</v>
+        <v>507.5</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>4.69119</v>
+        <v>4.776062</v>
       </c>
       <c r="G16" t="n">
         <v>74.074074</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.634401</v>
+        <v>4.714501</v>
       </c>
       <c r="G17" t="n">
         <v>74.074074</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.494492</v>
+        <v>4.456802</v>
       </c>
       <c r="G18" t="n">
         <v>74.074074</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.342719</v>
+        <v>0.482916</v>
       </c>
       <c r="G19" t="n">
         <v>74.074074</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.123278</v>
+        <v>-0.14254</v>
       </c>
       <c r="G20" t="n">
         <v>74.074074</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.22502</v>
+        <v>-2.238327</v>
       </c>
       <c r="G21" t="n">
         <v>74.074074</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.388229</v>
+        <v>0.331893</v>
       </c>
       <c r="G22" t="n">
         <v>74.074074</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>2.677676</v>
+        <v>2.623735</v>
       </c>
       <c r="G23" t="n">
         <v>74.074074</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.501317</v>
+        <v>-3.510006</v>
       </c>
       <c r="G24" t="n">
         <v>74.074074</v>
@@ -1051,7 +1051,7 @@
         <v>1.53102</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.475515</v>
+        <v>-6.520143</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.705352</v>
+        <v>2.4505</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.291262</v>
+        <v>-1.456311</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
@@ -1260,57 +1260,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>72.839506</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.2204</v>
       </c>
       <c r="G37" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2204</v>
+        <v>5.2198</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2198</v>
+        <v>7397669</v>
       </c>
       <c r="G39" t="n">
-        <v>75.30864200000001</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
       <c r="G40" t="n">
         <v>74.074074</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
       <c r="G41" t="n">
         <v>74.074074</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
       <c r="G42" t="n">
         <v>74.074074</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
         <v>74.074074</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
         <v>74.074074</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
         <v>74.074074</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
         <v>74.074074</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>74.074074</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>71.604938</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.748803</v>
       </c>
       <c r="G49" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>0.748803</v>
+        <v>0.7488899999999999</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7488899999999999</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>72.839506</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>72.839506</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>0.777299</v>
       </c>
       <c r="G54" t="n">
         <v>72.839506</v>
@@ -1785,32 +1785,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
       <c r="G55" t="n">
-        <v>72.839506</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
       <c r="G56" t="n">
         <v>60.493827</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>-0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>61.728395</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000517</v>
       </c>
       <c r="G58" t="n">
-        <v>60.493827</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000517</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000517</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000517</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
         <v>72.839506</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>59</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
         <v>72.839506</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>72.839506</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>72.839506</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>98.765432</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>98.765432</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>9808807495</v>
       </c>
       <c r="G110" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>4410039153</v>
+        <v>44621019</v>
       </c>
       <c r="G111" t="n">
-        <v>98.765432</v>
+        <v>93.82716000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>9808807495</v>
+        <v>109088024</v>
       </c>
       <c r="G112" t="n">
-        <v>98.765432</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.82716000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.82716000000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,22 +464,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>110979</v>
+        <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>185892.640625</v>
+        <v>186810.84375</v>
       </c>
       <c r="G2" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="3">
@@ -489,22 +489,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D3" t="n">
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>106.489998</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>183.020004</v>
+        <v>183.960007</v>
       </c>
       <c r="G3" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="4">
@@ -514,22 +514,22 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>127.400002</v>
+        <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>110.860001</v>
+        <v>112.709999</v>
       </c>
       <c r="G4" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="5">
@@ -539,22 +539,22 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D5" t="n">
         <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>451.519989</v>
+        <v>451.859985</v>
       </c>
       <c r="G5" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="6">
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D6" t="n">
         <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4143</v>
+        <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1838</v>
+        <v>5.2282</v>
       </c>
       <c r="G6" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="7">
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D7" t="n">
         <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2785</v>
+        <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8751</v>
+        <v>5.8715</v>
       </c>
       <c r="G7" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="8">
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D8" t="n">
         <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>4307.540039</v>
+        <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.649902</v>
+        <v>7647.740234</v>
       </c>
       <c r="G8" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="9">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
         <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>14448.580078</v>
+        <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27062.792969</v>
+        <v>26818.607422</v>
       </c>
       <c r="G9" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="10">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D10" t="n">
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>33843.921875</v>
+        <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51319.070312</v>
+        <v>50836.351562</v>
       </c>
       <c r="G10" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="11">
@@ -689,22 +689,22 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
         <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1757</v>
+        <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4189.299805</v>
+        <v>4195.399902</v>
       </c>
       <c r="G11" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="12">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D12" t="n">
         <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>75.029999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.379997</v>
+        <v>91.910004</v>
       </c>
       <c r="G12" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="13">
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>78.519997</v>
+        <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>98.83000199999999</v>
+        <v>101.080002</v>
       </c>
       <c r="G13" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="14">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>1256</v>
+        <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1306.5</v>
+        <v>1277.25</v>
       </c>
       <c r="G14" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="15">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D15" t="n">
         <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>536.75</v>
+        <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>507.5</v>
+        <v>497.75</v>
       </c>
       <c r="G15" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="16">
@@ -814,22 +814,22 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D16" t="n">
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.738212</v>
+        <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>4.776062</v>
+        <v>0.25268</v>
       </c>
       <c r="G16" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="17">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D17" t="n">
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.394964</v>
+        <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>4.714501</v>
+        <v>1.607293</v>
       </c>
       <c r="G17" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="18">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.715859</v>
+        <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>4.456802</v>
+        <v>2.790695</v>
       </c>
       <c r="G18" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="19">
@@ -889,22 +889,22 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>10.980392</v>
+        <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>0.482916</v>
+        <v>0.07308199999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="20">
@@ -914,22 +914,22 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D20" t="n">
         <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>4.259089</v>
+        <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.14254</v>
+        <v>0.486268</v>
       </c>
       <c r="G20" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="21">
@@ -939,22 +939,22 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
         <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>5.009156</v>
+        <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.238327</v>
+        <v>-0.419352</v>
       </c>
       <c r="G21" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="22">
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D22" t="n">
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>6.914384</v>
+        <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>0.331893</v>
+        <v>-0.049661</v>
       </c>
       <c r="G22" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="23">
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>7.265832</v>
+        <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>2.623735</v>
+        <v>-0.158047</v>
       </c>
       <c r="G23" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="24">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D24" t="n">
         <v>60</v>
       </c>
       <c r="E24" t="n">
-        <v>5.837493</v>
+        <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.510006</v>
+        <v>-0.136917</v>
       </c>
       <c r="G24" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="25">
@@ -1039,22 +1039,22 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D25" t="n">
         <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>1.53102</v>
+        <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.520143</v>
+        <v>0.207794</v>
       </c>
       <c r="G25" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="26">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D26" t="n">
         <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>11.382115</v>
+        <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>6.553166</v>
+        <v>1.647872</v>
       </c>
       <c r="G26" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="27">
@@ -1089,22 +1089,22 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D27" t="n">
         <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>7.463068</v>
+        <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>9.216493</v>
+        <v>-2.366461</v>
       </c>
       <c r="G27" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="28">
@@ -1114,22 +1114,22 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D28" t="n">
         <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.612261</v>
+        <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4505</v>
+        <v>-1.218097</v>
       </c>
       <c r="G28" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="29">
@@ -1139,22 +1139,22 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D29" t="n">
         <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>5.868654</v>
+        <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.456311</v>
+        <v>-0.599101</v>
       </c>
       <c r="G29" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="30">
@@ -1164,22 +1164,22 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>6.25</v>
+        <v>7.75</v>
       </c>
       <c r="F30" t="n">
         <v>13.75</v>
       </c>
       <c r="G30" t="n">
-        <v>75.30864200000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="31">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.023687</v>
+        <v>0.024244</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051268</v>
+        <v>0.051245</v>
       </c>
       <c r="G31" t="n">
-        <v>75.30864200000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="32">
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.023687</v>
+        <v>0.024244</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051268</v>
+        <v>0.051245</v>
       </c>
       <c r="G32" t="n">
-        <v>75.30864200000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="33">
@@ -1239,828 +1239,828 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
         <v>-0.32</v>
       </c>
       <c r="G33" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2</v>
+        <v>0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
         <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>96.96513</v>
+        <v>1.16</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>72.839506</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.10777</v>
+        <v>97.48671</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
-        <v>72.839506</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>96.53041</v>
       </c>
       <c r="F37" t="n">
-        <v>5.2204</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.643</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2198</v>
+        <v>5.1809</v>
       </c>
       <c r="G38" t="n">
-        <v>75.30864200000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.6424</v>
       </c>
       <c r="F39" t="n">
-        <v>7397669</v>
+        <v>5.2073</v>
       </c>
       <c r="G39" t="n">
-        <v>74.074074</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4511956</v>
       </c>
       <c r="F40" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1910940</v>
       </c>
       <c r="F41" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2601017</v>
       </c>
       <c r="F42" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>2.99</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>22.89</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47" t="n">
-        <v>0.537905</v>
+        <v>367927</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G47" t="n">
-        <v>71.604938</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.594556</v>
+        <v>1.608989</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
-        <v>71.604938</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>1.36989</v>
       </c>
       <c r="F49" t="n">
-        <v>0.748803</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>-0.409357</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7488899999999999</v>
+        <v>-0.013509</v>
       </c>
       <c r="G50" t="n">
-        <v>74.074074</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>-0.4094</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>0.521205</v>
       </c>
       <c r="G51" t="n">
-        <v>72.839506</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.888065</v>
+        <v>1.896096</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
-        <v>72.839506</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.123375</v>
+        <v>1.160214</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
-        <v>72.839506</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.259972</v>
+        <v>2.436662</v>
       </c>
       <c r="F54" t="n">
-        <v>0.777299</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
-        <v>72.839506</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F55" t="n">
-        <v>4.223453</v>
+        <v>0.777299</v>
       </c>
       <c r="G55" t="n">
-        <v>60.493827</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>8.825751</v>
+        <v>7.168596</v>
       </c>
       <c r="F56" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
-        <v>60.493827</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44500</v>
+        <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.25</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
-        <v>74.074074</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44834</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000557</v>
+        <v>7.191214</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000517</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D59" t="n">
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000517</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>74.074074</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.005012</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>-0.00054</v>
       </c>
       <c r="G60" t="n">
-        <v>72.839506</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
         <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03</v>
+        <v>-0.00054</v>
       </c>
       <c r="G61" t="n">
-        <v>72.839506</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
-        <v>72.839506</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0.03</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>72.839506</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.02</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,19 +2073,19 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,19 +2098,19 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,19 +2123,19 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,19 +2148,19 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,19 +2173,19 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,19 +2198,19 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,19 +2223,19 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,19 +2248,19 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,19 +2273,19 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
-        <v>97.53086399999999</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
-        <v>97.53086399999999</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,19 +2498,19 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,19 +2523,19 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,19 +2548,19 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,19 +2573,19 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>86.419753</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>86.419753</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>53.08642</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>53.08642</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,19 +2798,19 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,19 +2823,19 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,19 +2848,19 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,19 +2873,19 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,19 +2998,19 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,19 +3023,19 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,19 +3048,19 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,119 +3073,119 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
-        <v>98.765432</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>6.17284</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>6.17284</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,41 +3195,91 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>93.82716000000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G112" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>92.68292700000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
         <v>76</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>109088024</v>
       </c>
-      <c r="G112" t="n">
-        <v>93.82716000000001</v>
+      <c r="G114" t="n">
+        <v>92.68292700000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>186810.84375</v>
+        <v>186864.640625</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>183.960007</v>
+        <v>184.139999</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>112.709999</v>
+        <v>113.480003</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>451.859985</v>
+        <v>454.899994</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2282</v>
+        <v>5.225</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8715</v>
+        <v>5.8793</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7647.740234</v>
+        <v>7723.790039</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26818.607422</v>
+        <v>27210.888672</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>50836.351562</v>
+        <v>51103.199219</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4195.399902</v>
+        <v>4160.399902</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.910004</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>101.080002</v>
+        <v>101.379997</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1277.25</v>
+        <v>1279</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>497.75</v>
+        <v>496.25</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.25268</v>
+        <v>0.28155</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>1.607293</v>
+        <v>0.032593</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>2.790695</v>
+        <v>1.384797</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07308199999999999</v>
+        <v>1.68317</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>0.486268</v>
+        <v>0.424763</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.419352</v>
+        <v>-0.287062</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.049661</v>
+        <v>0.944254</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.158047</v>
+        <v>1.302362</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.136917</v>
+        <v>0.387279</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.207794</v>
+        <v>-0.6281870000000001</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>1.647872</v>
+        <v>0.442382</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.366461</v>
+        <v>-2.076694</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.218097</v>
+        <v>-1.082753</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.599101</v>
+        <v>-0.898652</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1192,19 +1192,19 @@
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024244</v>
+        <v>0.024273</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051245</v>
+        <v>0.050788</v>
       </c>
       <c r="G31" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="32">
@@ -1217,19 +1217,19 @@
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024244</v>
+        <v>0.024273</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051245</v>
+        <v>0.050788</v>
       </c>
       <c r="G32" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="33">
@@ -1367,19 +1367,19 @@
         <v>44500</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
         <v>5.643</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1809</v>
+        <v>5.2079</v>
       </c>
       <c r="G38" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F40" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F41" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F42" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
         <v>71.95122000000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>367927</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>372616</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,157 +1560,157 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E46" t="n">
-        <v>22.89</v>
+        <v>1.608989</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>-0.219358</v>
       </c>
       <c r="G46" t="n">
-        <v>71.95122000000001</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>367927</v>
+        <v>1.36989</v>
       </c>
       <c r="F47" t="n">
-        <v>372616</v>
+        <v>4.057001</v>
       </c>
       <c r="G47" t="n">
-        <v>71.95122000000001</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>1.608989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>0.521145</v>
       </c>
       <c r="G48" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>1.36989</v>
+        <v>-0.4094</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>0.521205</v>
       </c>
       <c r="G49" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.409357</v>
+        <v>1.160214</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.013509</v>
+        <v>-0.060934</v>
       </c>
       <c r="G50" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4094</v>
+        <v>2.436662</v>
       </c>
       <c r="F51" t="n">
-        <v>0.521205</v>
+        <v>0.799177</v>
       </c>
       <c r="G51" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.896096</v>
+        <v>-0.042128</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>0.777299</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,332 +1735,332 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E53" t="n">
-        <v>1.160214</v>
+        <v>7.168596</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>4.223453</v>
       </c>
       <c r="G53" t="n">
-        <v>70.731707</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.436662</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>3.348378</v>
       </c>
       <c r="G54" t="n">
-        <v>70.731707</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.042128</v>
+        <v>7.191214</v>
       </c>
       <c r="F55" t="n">
-        <v>0.777299</v>
+        <v>3.983297</v>
       </c>
       <c r="G55" t="n">
-        <v>70.731707</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>7.168596</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>58.536585</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>8.248760000000001</v>
+        <v>0.004983</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>-0.000457</v>
       </c>
       <c r="G57" t="n">
-        <v>59.756098</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>7.191214</v>
+        <v>0.004983</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>-0.000457</v>
       </c>
       <c r="G58" t="n">
-        <v>58.536585</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G59" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.00054</v>
+        <v>0.03</v>
       </c>
       <c r="G60" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005012</v>
+        <v>0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00054</v>
+        <v>0.23</v>
       </c>
       <c r="G61" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03</v>
+        <v>14429715267</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>33157804370</v>
       </c>
       <c r="G62" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03</v>
+        <v>17190165488</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>25763862100</v>
       </c>
       <c r="G63" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02</v>
+        <v>-2760450221</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>7393942270</v>
       </c>
       <c r="G64" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.02</v>
+        <v>31619880755</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>58921666470</v>
       </c>
       <c r="G65" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>46718273016</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>77119199389</v>
       </c>
       <c r="G66" t="n">
         <v>97.560976</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>12206525099</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>14073182023</v>
       </c>
       <c r="G67" t="n">
         <v>97.560976</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>641249369</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>1548184686</v>
       </c>
       <c r="G68" t="n">
         <v>97.560976</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>11309879</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>19241881</v>
       </c>
       <c r="G69" t="n">
         <v>97.560976</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>17842724736</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>27331288667</v>
       </c>
       <c r="G70" t="n">
         <v>97.560976</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>395907378</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>753147930</v>
       </c>
       <c r="G71" t="n">
         <v>97.560976</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>1403790404</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>2221291720</v>
       </c>
       <c r="G72" t="n">
         <v>97.560976</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2245,22 +2245,22 @@
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>42579</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>170442</v>
       </c>
       <c r="G73" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2270,22 +2270,22 @@
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>41657</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>143344</v>
       </c>
       <c r="G74" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>357877575</v>
       </c>
       <c r="F75" t="n">
-        <v>753147930</v>
+        <v>1094109253</v>
       </c>
       <c r="G75" t="n">
         <v>97.560976</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>163332129</v>
       </c>
       <c r="F76" t="n">
-        <v>2221291720</v>
+        <v>206264157</v>
       </c>
       <c r="G76" t="n">
         <v>97.560976</v>
@@ -2335,57 +2335,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>31418</v>
       </c>
       <c r="F77" t="n">
-        <v>170442</v>
+        <v>6294</v>
       </c>
       <c r="G77" t="n">
-        <v>96.341463</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>20000</v>
       </c>
       <c r="F78" t="n">
-        <v>143344</v>
+        <v>1560</v>
       </c>
       <c r="G78" t="n">
-        <v>96.341463</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2398,10 +2398,10 @@
         <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>500185177</v>
       </c>
       <c r="F79" t="n">
-        <v>1094109253</v>
+        <v>967242706</v>
       </c>
       <c r="G79" t="n">
         <v>97.560976</v>
@@ -2410,7 +2410,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2423,10 +2423,10 @@
         <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>103909023</v>
       </c>
       <c r="F80" t="n">
-        <v>206264157</v>
+        <v>162300453</v>
       </c>
       <c r="G80" t="n">
         <v>97.560976</v>
@@ -2435,57 +2435,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>9788257</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>9868969</v>
       </c>
       <c r="G81" t="n">
-        <v>26.829268</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>1182973</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>942383</v>
       </c>
       <c r="G82" t="n">
-        <v>26.829268</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>488810441</v>
       </c>
       <c r="F83" t="n">
-        <v>967242706</v>
+        <v>748163251</v>
       </c>
       <c r="G83" t="n">
         <v>97.560976</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1351894846</v>
       </c>
       <c r="F84" t="n">
-        <v>162300453</v>
+        <v>1412673002</v>
       </c>
       <c r="G84" t="n">
         <v>97.560976</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2545,22 +2545,22 @@
         <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>23393</v>
       </c>
       <c r="F85" t="n">
-        <v>9868969</v>
+        <v>1381516</v>
       </c>
       <c r="G85" t="n">
-        <v>97.560976</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2570,22 +2570,22 @@
         <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>40720</v>
       </c>
       <c r="F86" t="n">
-        <v>942383</v>
+        <v>1452782</v>
       </c>
       <c r="G86" t="n">
-        <v>97.560976</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2598,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>401663716</v>
       </c>
       <c r="F87" t="n">
-        <v>748163251</v>
+        <v>893582419</v>
       </c>
       <c r="G87" t="n">
         <v>97.560976</v>
@@ -2610,7 +2610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2623,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>955961547</v>
       </c>
       <c r="F88" t="n">
-        <v>1412673002</v>
+        <v>1438094595</v>
       </c>
       <c r="G88" t="n">
         <v>97.560976</v>
@@ -2635,57 +2635,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D89" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>13124930</v>
       </c>
       <c r="F89" t="n">
-        <v>1381516</v>
+        <v>60</v>
       </c>
       <c r="G89" t="n">
-        <v>85.365854</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D90" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>40054409</v>
       </c>
       <c r="F90" t="n">
-        <v>1452782</v>
+        <v>24</v>
       </c>
       <c r="G90" t="n">
-        <v>85.365854</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2698,10 +2698,10 @@
         <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>349915062</v>
       </c>
       <c r="F91" t="n">
-        <v>893582419</v>
+        <v>1002656682</v>
       </c>
       <c r="G91" t="n">
         <v>97.560976</v>
@@ -2710,7 +2710,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2723,10 +2723,10 @@
         <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>2083530104</v>
       </c>
       <c r="F92" t="n">
-        <v>1438094595</v>
+        <v>4653100189</v>
       </c>
       <c r="G92" t="n">
         <v>97.560976</v>
@@ -2735,57 +2735,57 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>26216991</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>33273820</v>
       </c>
       <c r="G93" t="n">
-        <v>52.439024</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>196178640</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>199281400</v>
       </c>
       <c r="G94" t="n">
-        <v>52.439024</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>1627139024</v>
       </c>
       <c r="F95" t="n">
-        <v>1002656682</v>
+        <v>2051566400</v>
       </c>
       <c r="G95" t="n">
         <v>97.560976</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>25418986258</v>
       </c>
       <c r="F96" t="n">
-        <v>4653100189</v>
+        <v>34406447895</v>
       </c>
       <c r="G96" t="n">
         <v>97.560976</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2845,22 +2845,22 @@
         <v>46265</v>
       </c>
       <c r="D97" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>6207</v>
       </c>
       <c r="F97" t="n">
-        <v>33273820</v>
+        <v>6950029</v>
       </c>
       <c r="G97" t="n">
-        <v>97.560976</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2870,22 +2870,22 @@
         <v>46265</v>
       </c>
       <c r="D98" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>7200</v>
       </c>
       <c r="F98" t="n">
-        <v>199281400</v>
+        <v>78331372</v>
       </c>
       <c r="G98" t="n">
-        <v>97.560976</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2898,10 +2898,10 @@
         <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>1707992437</v>
       </c>
       <c r="F99" t="n">
-        <v>2051566400</v>
+        <v>4828191084</v>
       </c>
       <c r="G99" t="n">
         <v>97.560976</v>
@@ -2910,7 +2910,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2923,10 +2923,10 @@
         <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>4221906804</v>
       </c>
       <c r="F100" t="n">
-        <v>34406447895</v>
+        <v>8379911835</v>
       </c>
       <c r="G100" t="n">
         <v>97.560976</v>
@@ -2935,7 +2935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>207990371</v>
       </c>
       <c r="F101" t="n">
-        <v>6950029</v>
+        <v>547298813</v>
       </c>
       <c r="G101" t="n">
-        <v>80.48780499999999</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>432290309</v>
       </c>
       <c r="F102" t="n">
-        <v>78331372</v>
+        <v>797225701</v>
       </c>
       <c r="G102" t="n">
-        <v>80.48780499999999</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>281324952</v>
       </c>
       <c r="F103" t="n">
-        <v>4828191084</v>
+        <v>646488066</v>
       </c>
       <c r="G103" t="n">
         <v>97.560976</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>831821378</v>
       </c>
       <c r="F104" t="n">
-        <v>8379911835</v>
+        <v>1790486389</v>
       </c>
       <c r="G104" t="n">
         <v>97.560976</v>
@@ -3035,57 +3035,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>2282</v>
       </c>
       <c r="F105" t="n">
-        <v>547298813</v>
+        <v>360</v>
       </c>
       <c r="G105" t="n">
-        <v>97.560976</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>2500</v>
       </c>
       <c r="F106" t="n">
-        <v>797225701</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>97.560976</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
@@ -3098,10 +3098,10 @@
         <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>504774218</v>
       </c>
       <c r="F107" t="n">
-        <v>646488066</v>
+        <v>4410039153</v>
       </c>
       <c r="G107" t="n">
         <v>97.560976</v>
@@ -3110,7 +3110,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
@@ -3123,10 +3123,10 @@
         <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>1397018249</v>
       </c>
       <c r="F108" t="n">
-        <v>1790486389</v>
+        <v>9808807495</v>
       </c>
       <c r="G108" t="n">
         <v>97.560976</v>
@@ -3135,150 +3135,50 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>6305340</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>44621019</v>
       </c>
       <c r="G109" t="n">
-        <v>6.097561</v>
+        <v>92.68292700000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>19690000</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>109088024</v>
       </c>
       <c r="G110" t="n">
-        <v>6.097561</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D111" t="n">
-        <v>80</v>
-      </c>
-      <c r="E111" t="n">
-        <v>504774218</v>
-      </c>
-      <c r="F111" t="n">
-        <v>4410039153</v>
-      </c>
-      <c r="G111" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
-        <v>80</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1397018249</v>
-      </c>
-      <c r="F112" t="n">
-        <v>9808807495</v>
-      </c>
-      <c r="G112" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" t="n">
-        <v>76</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G113" t="n">
-        <v>92.68292700000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D114" t="n">
-        <v>76</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G114" t="n">
         <v>92.68292700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>186864.640625</v>
+        <v>187130.234375</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>184.139999</v>
+        <v>184.320007</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>113.480003</v>
+        <v>113.379997</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>454.899994</v>
+        <v>454.670013</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.225</v>
+        <v>5.2234</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8793</v>
+        <v>5.8805</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7723.790039</v>
+        <v>7725.560059</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27210.888672</v>
+        <v>27222.126953</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51103.199219</v>
+        <v>51112.210938</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4160.399902</v>
+        <v>4155.200195</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.81999999999999</v>
+        <v>90.970001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>101.379997</v>
+        <v>101.400002</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1279</v>
+        <v>1279.25</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>496.25</v>
+        <v>496.75</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.28155</v>
+        <v>0.424082</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>0.032593</v>
+        <v>0.130381</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.384797</v>
+        <v>1.29545</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>1.68317</v>
+        <v>1.631763</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>0.424763</v>
+        <v>0.394015</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.287062</v>
+        <v>-0.266714</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>0.944254</v>
+        <v>0.967387</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.302362</v>
+        <v>1.3442</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.387279</v>
+        <v>0.404982</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6281870000000001</v>
+        <v>-0.752383</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>0.442382</v>
+        <v>0.608276</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.076694</v>
+        <v>-2.057372</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.082753</v>
+        <v>-1.063418</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.898652</v>
+        <v>-0.798802</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1210,107 +1210,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024273</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
       <c r="G32" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>70.731707</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.2079</v>
       </c>
       <c r="G37" t="n">
-        <v>70.731707</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2079</v>
+        <v>5.2073</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1385,26 +1385,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2073</v>
+        <v>7397669</v>
       </c>
       <c r="G39" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F45" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,32 +1560,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
-        <v>69.51219500000001</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
@@ -1598,10 +1598,10 @@
         <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F47" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
         <v>69.51219500000001</v>
@@ -1610,32 +1610,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F48" t="n">
-        <v>0.521145</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -1648,10 +1648,10 @@
         <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>0.521205</v>
+        <v>0.521145</v>
       </c>
       <c r="G49" t="n">
         <v>73.170732</v>
@@ -1660,32 +1660,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>1.160214</v>
+        <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.060934</v>
+        <v>0.521205</v>
       </c>
       <c r="G50" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -1698,10 +1698,10 @@
         <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>2.436662</v>
+        <v>1.896096</v>
       </c>
       <c r="F51" t="n">
-        <v>0.799177</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
         <v>70.731707</v>
@@ -1710,7 +1710,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.042128</v>
+        <v>1.160214</v>
       </c>
       <c r="F52" t="n">
-        <v>0.777299</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,57 +1735,57 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D53" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>7.168596</v>
+        <v>2.436662</v>
       </c>
       <c r="F53" t="n">
-        <v>4.223453</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
-        <v>58.536585</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F54" t="n">
-        <v>3.348378</v>
+        <v>0.777299</v>
       </c>
       <c r="G54" t="n">
-        <v>59.756098</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -1798,10 +1798,10 @@
         <v>48</v>
       </c>
       <c r="E55" t="n">
-        <v>7.191214</v>
+        <v>7.168596</v>
       </c>
       <c r="F55" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
       <c r="G55" t="n">
         <v>58.536585</v>
@@ -1810,57 +1810,57 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>0.004983</v>
+        <v>7.191214</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.000457</v>
+        <v>3.983297</v>
       </c>
       <c r="G57" t="n">
-        <v>73.170732</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -1873,10 +1873,10 @@
         <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>0.004983</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>73.170732</v>
@@ -1885,32 +1885,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.03</v>
+        <v>0.004983</v>
       </c>
       <c r="F59" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
       <c r="G59" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1926,7 +1926,7 @@
         <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
         <v>70.731707</v>
@@ -1935,7 +1935,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -1948,10 +1948,10 @@
         <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
         <v>70.731707</v>
@@ -1960,57 +1960,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>14429715267</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>33157804370</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
-        <v>97.560976</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>17190165488</v>
+        <v>1.02</v>
       </c>
       <c r="F63" t="n">
-        <v>25763862100</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
-        <v>97.560976</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -2023,10 +2023,10 @@
         <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
         <v>97.560976</v>
@@ -2035,7 +2035,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -2048,10 +2048,10 @@
         <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
         <v>97.560976</v>
@@ -2060,7 +2060,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>97.560976</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
         <v>97.560976</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
         <v>97.560976</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>97.560976</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>97.560976</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>753147930</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
         <v>97.560976</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>2221291720</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
         <v>97.560976</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2245,22 +2245,22 @@
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>170442</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2270,22 +2270,22 @@
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>143344</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,122 +2320,122 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
-        <v>26.829268</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
-        <v>26.829268</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>967242706</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>97.560976</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>162300453</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>97.560976</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
@@ -2448,10 +2448,10 @@
         <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>9868969</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
         <v>97.560976</v>
@@ -2460,7 +2460,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
@@ -2473,10 +2473,10 @@
         <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>942383</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
         <v>97.560976</v>
@@ -2485,7 +2485,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>748163251</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
         <v>97.560976</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>1412673002</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
         <v>97.560976</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2545,22 +2545,22 @@
         <v>46265</v>
       </c>
       <c r="D85" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>1381516</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
-        <v>85.365854</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2570,22 +2570,22 @@
         <v>46265</v>
       </c>
       <c r="D86" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>1452782</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
-        <v>85.365854</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>893582419</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>97.560976</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,122 +2620,122 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1438094595</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>97.560976</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>60</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
-        <v>52.439024</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
-        <v>52.439024</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>1002656682</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>97.560976</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>4653100189</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>97.560976</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
@@ -2748,10 +2748,10 @@
         <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>33273820</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
         <v>97.560976</v>
@@ -2760,7 +2760,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -2773,10 +2773,10 @@
         <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>199281400</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
         <v>97.560976</v>
@@ -2785,7 +2785,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>97.560976</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>97.560976</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2845,22 +2845,22 @@
         <v>46265</v>
       </c>
       <c r="D97" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
-        <v>80.48780499999999</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2870,22 +2870,22 @@
         <v>46265</v>
       </c>
       <c r="D98" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
-        <v>80.48780499999999</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>97.560976</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>97.560976</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2948,10 +2948,10 @@
         <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
         <v>97.560976</v>
@@ -2960,7 +2960,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2973,10 +2973,10 @@
         <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
         <v>97.560976</v>
@@ -2985,7 +2985,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>646488066</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
         <v>97.560976</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>1790486389</v>
+        <v>797225701</v>
       </c>
       <c r="G104" t="n">
         <v>97.560976</v>
@@ -3035,107 +3035,107 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>360</v>
+        <v>646488066</v>
       </c>
       <c r="G105" t="n">
-        <v>6.097561</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1790486389</v>
       </c>
       <c r="G106" t="n">
-        <v>6.097561</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>4410039153</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>97.560976</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>9808807495</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>97.560976</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
@@ -3145,40 +3145,90 @@
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E109" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>44621019</v>
+        <v>4410039153</v>
       </c>
       <c r="G109" t="n">
-        <v>92.68292700000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D110" t="n">
+        <v>80</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G110" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D111" t="n">
+        <v>76</v>
+      </c>
+      <c r="E111" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F111" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G111" t="n">
+        <v>92.68292700000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D110" t="n">
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
         <v>76</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E112" t="n">
         <v>19690000</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F112" t="n">
         <v>109088024</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G112" t="n">
         <v>92.68292700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>187130.234375</v>
+        <v>192115</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>184.320007</v>
+        <v>184.410004</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>113.379997</v>
+        <v>113.019997</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>454.670013</v>
+        <v>452.079987</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2234</v>
+        <v>5.2223</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8805</v>
+        <v>5.8702</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7725.560059</v>
+        <v>7722.720215</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27222.126953</v>
+        <v>27190.859375</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51112.210938</v>
+        <v>51176.960938</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4155.200195</v>
+        <v>4162.299805</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.970001</v>
+        <v>91.110001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>101.400002</v>
+        <v>102.25</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1279.25</v>
+        <v>1278.25</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>496.75</v>
+        <v>497.75</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.424082</v>
+        <v>3.099174</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>0.130381</v>
+        <v>0.179271</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.29545</v>
+        <v>0.97382</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>1.631763</v>
+        <v>1.052818</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>0.394015</v>
+        <v>0.372871</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.266714</v>
+        <v>-0.441397</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>0.967387</v>
+        <v>0.930273</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3442</v>
+        <v>1.227795</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.404982</v>
+        <v>0.532177</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.752383</v>
+        <v>-0.582807</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>0.608276</v>
+        <v>0.763108</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.057372</v>
+        <v>-1.236355</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.063418</v>
+        <v>-1.140758</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.798802</v>
+        <v>-0.599101</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>184.410004</v>
+        <v>190</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>113.019997</v>
+        <v>116.339996</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>452.079987</v>
+        <v>454.700012</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>0.179271</v>
+        <v>3.215992</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>0.97382</v>
+        <v>3.939959</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>1.052818</v>
+        <v>1.638469</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>192115</v>
+        <v>208982.96875</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>190</v>
+        <v>205.960007</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>116.339996</v>
+        <v>128.25</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>454.700012</v>
+        <v>439.059998</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2223</v>
+        <v>4.9902</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8702</v>
+        <v>5.6059</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7722.720215</v>
+        <v>7785.040039</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27190.859375</v>
+        <v>27504.978516</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51176.960938</v>
+        <v>51352.410156</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4162.299805</v>
+        <v>4167</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.110001</v>
+        <v>88.980003</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>102.25</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1278.25</v>
+        <v>1281</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>497.75</v>
+        <v>497.5</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>3.099174</v>
+        <v>12.151427</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>3.215992</v>
+        <v>11.886139</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>3.939959</v>
+        <v>14.580541</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>1.638469</v>
+        <v>-1.857522</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>0.372871</v>
+        <v>-4.088103</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.441397</v>
+        <v>-4.923931</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>0.930273</v>
+        <v>1.744747</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.227795</v>
+        <v>2.397217</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.532177</v>
+        <v>0.87683</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.582807</v>
+        <v>-0.470542</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>0.763108</v>
+        <v>-1.592562</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.236355</v>
+        <v>-3.409639</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.140758</v>
+        <v>-0.928074</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.599101</v>
+        <v>-0.649026</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>7.75</v>
+        <v>0.024306</v>
       </c>
       <c r="F30" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="G30" t="n">
         <v>74.390244</v>
@@ -1185,207 +1185,207 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024273</v>
+        <v>1.25</v>
       </c>
       <c r="F31" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
       <c r="G31" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G32" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G33" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>1.16</v>
+        <v>96.53041</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.32</v>
+        <v>114.40189</v>
       </c>
       <c r="G34" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>97.48671</v>
+        <v>5.643</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>4.9859</v>
       </c>
       <c r="G35" t="n">
-        <v>70.731707</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E36" t="n">
-        <v>96.53041</v>
+        <v>5.6424</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>4.9853</v>
       </c>
       <c r="G36" t="n">
-        <v>70.731707</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.643</v>
+        <v>1910940</v>
       </c>
       <c r="F37" t="n">
-        <v>5.2079</v>
+        <v>2727499</v>
       </c>
       <c r="G37" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6424</v>
+        <v>2.33</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2073</v>
+        <v>5.04</v>
       </c>
       <c r="G38" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -1398,10 +1398,10 @@
         <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>4511956</v>
+        <v>1.43</v>
       </c>
       <c r="F39" t="n">
-        <v>7397669</v>
+        <v>3.35</v>
       </c>
       <c r="G39" t="n">
         <v>71.95122000000001</v>
@@ -1410,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1910940</v>
+        <v>2.99</v>
       </c>
       <c r="F40" t="n">
-        <v>2727499</v>
+        <v>6.03</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2601017</v>
+        <v>22.89</v>
       </c>
       <c r="F41" t="n">
-        <v>4670170</v>
+        <v>32.26</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.33</v>
+        <v>367927</v>
       </c>
       <c r="F42" t="n">
-        <v>5.04</v>
+        <v>372616</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,232 +1485,232 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>1.36989</v>
       </c>
       <c r="F43" t="n">
-        <v>3.35</v>
+        <v>4.057001</v>
       </c>
       <c r="G43" t="n">
-        <v>71.95122000000001</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>-0.409357</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>-3.763825</v>
       </c>
       <c r="G44" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>22.89</v>
+        <v>-0.4094</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>-3.764261</v>
       </c>
       <c r="G45" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" t="n">
-        <v>367927</v>
+        <v>1.160214</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>-0.060934</v>
       </c>
       <c r="G46" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>1.608989</v>
+        <v>-0.042128</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>0.777299</v>
       </c>
       <c r="G47" t="n">
-        <v>69.51219500000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>1.36989</v>
+        <v>7.168596</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>4.223453</v>
       </c>
       <c r="G48" t="n">
-        <v>69.51219500000001</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.409357</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0.521145</v>
+        <v>3.348378</v>
       </c>
       <c r="G49" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4094</v>
+        <v>7.191214</v>
       </c>
       <c r="F50" t="n">
-        <v>0.521205</v>
+        <v>3.983297</v>
       </c>
       <c r="G50" t="n">
-        <v>73.170732</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.896096</v>
+        <v>0.00495</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>-0.000457</v>
       </c>
       <c r="G51" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.160214</v>
+        <v>0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.16</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.436662</v>
+        <v>0.03</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>0.03</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.042128</v>
+        <v>0.02</v>
       </c>
       <c r="F54" t="n">
-        <v>0.777299</v>
+        <v>0.23</v>
       </c>
       <c r="G54" t="n">
         <v>70.731707</v>
@@ -1785,232 +1785,232 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>7.168596</v>
+        <v>1.02</v>
       </c>
       <c r="F55" t="n">
-        <v>4.223453</v>
+        <v>0.2</v>
       </c>
       <c r="G55" t="n">
-        <v>58.536585</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44834</v>
+        <v>43861</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="E56" t="n">
-        <v>8.248760000000001</v>
+        <v>14429715267</v>
       </c>
       <c r="F56" t="n">
-        <v>3.348378</v>
+        <v>33157804370</v>
       </c>
       <c r="G56" t="n">
-        <v>59.756098</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44834</v>
+        <v>43861</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E57" t="n">
-        <v>7.191214</v>
+        <v>17190165488</v>
       </c>
       <c r="F57" t="n">
-        <v>3.983297</v>
+        <v>25763862100</v>
       </c>
       <c r="G57" t="n">
-        <v>58.536585</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-2760450221</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>7393942270</v>
       </c>
       <c r="G58" t="n">
-        <v>73.170732</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004983</v>
+        <v>31619880755</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000457</v>
+        <v>58921666470</v>
       </c>
       <c r="G59" t="n">
-        <v>73.170732</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>46718273016</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>77119199389</v>
       </c>
       <c r="G60" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03</v>
+        <v>12206525099</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03</v>
+        <v>14073182023</v>
       </c>
       <c r="G61" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>641249369</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>1548184686</v>
       </c>
       <c r="G62" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E63" t="n">
-        <v>1.02</v>
+        <v>11309879</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>19241881</v>
       </c>
       <c r="G63" t="n">
-        <v>70.731707</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -2023,10 +2023,10 @@
         <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>17842724736</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>27331288667</v>
       </c>
       <c r="G64" t="n">
         <v>97.560976</v>
@@ -2035,7 +2035,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -2048,10 +2048,10 @@
         <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>395907378</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>753147930</v>
       </c>
       <c r="G65" t="n">
         <v>97.560976</v>
@@ -2060,7 +2060,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>1403790404</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>2221291720</v>
       </c>
       <c r="G66" t="n">
         <v>97.560976</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2095,22 +2095,22 @@
         <v>46265</v>
       </c>
       <c r="D67" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>42579</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>170442</v>
       </c>
       <c r="G67" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2120,22 +2120,22 @@
         <v>46265</v>
       </c>
       <c r="D68" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>41657</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>143344</v>
       </c>
       <c r="G68" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>357877575</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>1094109253</v>
       </c>
       <c r="G69" t="n">
         <v>97.560976</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>163332129</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>206264157</v>
       </c>
       <c r="G70" t="n">
         <v>97.560976</v>
@@ -2185,57 +2185,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D71" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>31418</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>6294</v>
       </c>
       <c r="G71" t="n">
-        <v>97.560976</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D72" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>20000</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1560</v>
       </c>
       <c r="G72" t="n">
-        <v>97.560976</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>500185177</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>967242706</v>
       </c>
       <c r="G73" t="n">
         <v>97.560976</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>103909023</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>162300453</v>
       </c>
       <c r="G74" t="n">
         <v>97.560976</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>9788257</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>9868969</v>
       </c>
       <c r="G75" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1182973</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>942383</v>
       </c>
       <c r="G76" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2348,10 +2348,10 @@
         <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>488810441</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>748163251</v>
       </c>
       <c r="G77" t="n">
         <v>97.560976</v>
@@ -2360,7 +2360,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2373,10 +2373,10 @@
         <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>1351894846</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>1412673002</v>
       </c>
       <c r="G78" t="n">
         <v>97.560976</v>
@@ -2385,57 +2385,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>23393</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1381516</v>
       </c>
       <c r="G79" t="n">
-        <v>26.829268</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>40720</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>1452782</v>
       </c>
       <c r="G80" t="n">
-        <v>26.829268</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
@@ -2448,10 +2448,10 @@
         <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>401663716</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>893582419</v>
       </c>
       <c r="G81" t="n">
         <v>97.560976</v>
@@ -2460,7 +2460,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
@@ -2473,10 +2473,10 @@
         <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>955961547</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>1438094595</v>
       </c>
       <c r="G82" t="n">
         <v>97.560976</v>
@@ -2485,57 +2485,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D83" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>13124930</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>60</v>
       </c>
       <c r="G83" t="n">
-        <v>97.560976</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D84" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>40054409</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>24</v>
       </c>
       <c r="G84" t="n">
-        <v>97.560976</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>349915062</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>1002656682</v>
       </c>
       <c r="G85" t="n">
         <v>97.560976</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>2083530104</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>4653100189</v>
       </c>
       <c r="G86" t="n">
         <v>97.560976</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>26216991</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>33273820</v>
       </c>
       <c r="G87" t="n">
-        <v>85.365854</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>196178640</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>199281400</v>
       </c>
       <c r="G88" t="n">
-        <v>85.365854</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2648,10 +2648,10 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>1627139024</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>2051566400</v>
       </c>
       <c r="G89" t="n">
         <v>97.560976</v>
@@ -2660,7 +2660,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2673,10 +2673,10 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>25418986258</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>34406447895</v>
       </c>
       <c r="G90" t="n">
         <v>97.560976</v>
@@ -2685,57 +2685,57 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>6207</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>6950029</v>
       </c>
       <c r="G91" t="n">
-        <v>52.439024</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>7200</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>78331372</v>
       </c>
       <c r="G92" t="n">
-        <v>52.439024</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
@@ -2748,10 +2748,10 @@
         <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>1707992437</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>4828191084</v>
       </c>
       <c r="G93" t="n">
         <v>97.560976</v>
@@ -2760,7 +2760,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -2773,10 +2773,10 @@
         <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>4221906804</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>8379911835</v>
       </c>
       <c r="G94" t="n">
         <v>97.560976</v>
@@ -2785,7 +2785,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>207990371</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>547298813</v>
       </c>
       <c r="G95" t="n">
         <v>97.560976</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>432290309</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>797225701</v>
       </c>
       <c r="G96" t="n">
         <v>97.560976</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>281324952</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>646488066</v>
       </c>
       <c r="G97" t="n">
         <v>97.560976</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>831821378</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>1790486389</v>
       </c>
       <c r="G98" t="n">
         <v>97.560976</v>
@@ -2885,57 +2885,57 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>2282</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>360</v>
       </c>
       <c r="G99" t="n">
-        <v>80.48780499999999</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>2500</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>80.48780499999999</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2948,10 +2948,10 @@
         <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>504774218</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>4410039153</v>
       </c>
       <c r="G101" t="n">
         <v>97.560976</v>
@@ -2960,7 +2960,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2973,10 +2973,10 @@
         <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>1397018249</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>9808807495</v>
       </c>
       <c r="G102" t="n">
         <v>97.560976</v>
@@ -2985,7 +2985,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2995,22 +2995,22 @@
         <v>46265</v>
       </c>
       <c r="D103" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>6305340</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>44621019</v>
       </c>
       <c r="G103" t="n">
-        <v>97.560976</v>
+        <v>92.68292700000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3020,215 +3020,15 @@
         <v>46265</v>
       </c>
       <c r="D104" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>19690000</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>109088024</v>
       </c>
       <c r="G104" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C105" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D105" t="n">
-        <v>80</v>
-      </c>
-      <c r="E105" t="n">
-        <v>281324952</v>
-      </c>
-      <c r="F105" t="n">
-        <v>646488066</v>
-      </c>
-      <c r="G105" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D106" t="n">
-        <v>80</v>
-      </c>
-      <c r="E106" t="n">
-        <v>831821378</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1790486389</v>
-      </c>
-      <c r="G106" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>43890</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D107" t="n">
-        <v>5</v>
-      </c>
-      <c r="E107" t="n">
-        <v>2282</v>
-      </c>
-      <c r="F107" t="n">
-        <v>360</v>
-      </c>
-      <c r="G107" t="n">
-        <v>6.097561</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>43890</v>
-      </c>
-      <c r="C108" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D108" t="n">
-        <v>5</v>
-      </c>
-      <c r="E108" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>6.097561</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C109" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D109" t="n">
-        <v>80</v>
-      </c>
-      <c r="E109" t="n">
-        <v>504774218</v>
-      </c>
-      <c r="F109" t="n">
-        <v>4410039153</v>
-      </c>
-      <c r="G109" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D110" t="n">
-        <v>80</v>
-      </c>
-      <c r="E110" t="n">
-        <v>1397018249</v>
-      </c>
-      <c r="F110" t="n">
-        <v>9808807495</v>
-      </c>
-      <c r="G110" t="n">
-        <v>97.560976</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D111" t="n">
-        <v>76</v>
-      </c>
-      <c r="E111" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F111" t="n">
-        <v>44621019</v>
-      </c>
-      <c r="G111" t="n">
-        <v>92.68292700000001</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D112" t="n">
-        <v>76</v>
-      </c>
-      <c r="E112" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F112" t="n">
-        <v>109088024</v>
-      </c>
-      <c r="G112" t="n">
         <v>92.68292700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>208982.96875</v>
+        <v>205427.203125</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.960007</v>
+        <v>202.289993</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>128.25</v>
+        <v>128.529999</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.059998</v>
+        <v>440.369995</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9902</v>
+        <v>4.9748</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6059</v>
+        <v>5.601</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7785.040039</v>
+        <v>7834.240234</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27504.978516</v>
+        <v>27662.966797</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51352.410156</v>
+        <v>51601.289062</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4167</v>
+        <v>4191.299805</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>88.980003</v>
+        <v>89.220001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1281</v>
+        <v>1295.75</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>497.5</v>
+        <v>506.5</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>12.151427</v>
+        <v>10.243213</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>11.886139</v>
+        <v>9.892433</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>14.580541</v>
+        <v>14.830696</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.857522</v>
+        <v>-1.5647</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.088103</v>
+        <v>-4.38409</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.923931</v>
+        <v>-5.007035</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.744747</v>
+        <v>2.387757</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>2.397217</v>
+        <v>2.985386</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.87683</v>
+        <v>1.365728</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.470542</v>
+        <v>0.109862</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.592562</v>
+        <v>-1.327137</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.409639</v>
+        <v>-3.651114</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.928074</v>
+        <v>0.212684</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.649026</v>
+        <v>1.148278</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>0.024306</v>
+        <v>7.75</v>
       </c>
       <c r="F30" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="G30" t="n">
         <v>74.390244</v>
@@ -1185,57 +1185,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>1.25</v>
+        <v>0.024342</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.32</v>
+        <v>0.050788</v>
       </c>
       <c r="G31" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.64</v>
+        <v>0.024342</v>
       </c>
       <c r="F32" t="n">
-        <v>1.57</v>
+        <v>0.050788</v>
       </c>
       <c r="G32" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,7 +1248,7 @@
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
         <v>-0.32</v>
@@ -1260,132 +1260,132 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>96.53041</v>
+        <v>0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>114.40189</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>5.643</v>
+        <v>97.48671</v>
       </c>
       <c r="F35" t="n">
-        <v>4.9859</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>74.390244</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>5.6424</v>
+        <v>96.53041</v>
       </c>
       <c r="F36" t="n">
-        <v>4.9853</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
-        <v>74.390244</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>1910940</v>
+        <v>5.643</v>
       </c>
       <c r="F37" t="n">
-        <v>2727499</v>
+        <v>4.9698</v>
       </c>
       <c r="G37" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>2.33</v>
+        <v>5.6424</v>
       </c>
       <c r="F38" t="n">
-        <v>5.04</v>
+        <v>4.9853</v>
       </c>
       <c r="G38" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -1398,10 +1398,10 @@
         <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>1.43</v>
+        <v>4511956</v>
       </c>
       <c r="F39" t="n">
-        <v>3.35</v>
+        <v>7397669</v>
       </c>
       <c r="G39" t="n">
         <v>71.95122000000001</v>
@@ -1410,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>2.99</v>
+        <v>1910940</v>
       </c>
       <c r="F40" t="n">
-        <v>6.03</v>
+        <v>2727499</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>22.89</v>
+        <v>2601017</v>
       </c>
       <c r="F41" t="n">
-        <v>32.26</v>
+        <v>4670170</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>367927</v>
+        <v>2.33</v>
       </c>
       <c r="F42" t="n">
-        <v>372616</v>
+        <v>5.04</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,232 +1485,232 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D43" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.36989</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.057001</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
-        <v>69.51219500000001</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.409357</v>
+        <v>2.99</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.763825</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4094</v>
+        <v>22.89</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.764261</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>1.160214</v>
+        <v>367927</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.060934</v>
+        <v>372616</v>
       </c>
       <c r="G46" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.042128</v>
+        <v>1.608989</v>
       </c>
       <c r="F47" t="n">
-        <v>0.777299</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>70.731707</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>7.168596</v>
+        <v>1.36989</v>
       </c>
       <c r="F48" t="n">
-        <v>4.223453</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
-        <v>58.536585</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>3.348378</v>
+        <v>-4.074582</v>
       </c>
       <c r="G49" t="n">
-        <v>59.756098</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D50" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>7.191214</v>
+        <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>3.983297</v>
+        <v>-3.764261</v>
       </c>
       <c r="G50" t="n">
-        <v>58.536585</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0.00495</v>
+        <v>1.896096</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.000457</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.03</v>
+        <v>1.160214</v>
       </c>
       <c r="F52" t="n">
-        <v>0.16</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.03</v>
+        <v>2.436662</v>
       </c>
       <c r="F53" t="n">
-        <v>0.03</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02</v>
+        <v>-0.042128</v>
       </c>
       <c r="F54" t="n">
-        <v>0.23</v>
+        <v>0.777299</v>
       </c>
       <c r="G54" t="n">
         <v>70.731707</v>
@@ -1785,232 +1785,232 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E55" t="n">
-        <v>1.02</v>
+        <v>7.168596</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2</v>
+        <v>4.223453</v>
       </c>
       <c r="G55" t="n">
-        <v>70.731707</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>43861</v>
+        <v>44834</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>14429715267</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>33157804370</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
-        <v>97.560976</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D57" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>17190165488</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>25763862100</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>97.560976</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D58" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>-2760450221</v>
+        <v>0.004914</v>
       </c>
       <c r="F58" t="n">
-        <v>7393942270</v>
+        <v>-0.000457</v>
       </c>
       <c r="G58" t="n">
-        <v>97.560976</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D59" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>31619880755</v>
+        <v>0.004914</v>
       </c>
       <c r="F59" t="n">
-        <v>58921666470</v>
+        <v>-0.000457</v>
       </c>
       <c r="G59" t="n">
-        <v>97.560976</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>46718273016</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>77119199389</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>97.560976</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>12206525099</v>
+        <v>0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>14073182023</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
-        <v>97.560976</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>641249369</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>1548184686</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
-        <v>97.560976</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>11309879</v>
+        <v>1.02</v>
       </c>
       <c r="F63" t="n">
-        <v>19241881</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
-        <v>97.560976</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -2023,10 +2023,10 @@
         <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>17842724736</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>27331288667</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
         <v>97.560976</v>
@@ -2035,7 +2035,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -2048,10 +2048,10 @@
         <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>395907378</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>753147930</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
         <v>97.560976</v>
@@ -2060,7 +2060,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>1403790404</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>2221291720</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
         <v>97.560976</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2095,22 +2095,22 @@
         <v>46265</v>
       </c>
       <c r="D67" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>42579</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>170442</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2120,22 +2120,22 @@
         <v>46265</v>
       </c>
       <c r="D68" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>41657</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>143344</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>357877575</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>1094109253</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
         <v>97.560976</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>163332129</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>206264157</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
         <v>97.560976</v>
@@ -2185,57 +2185,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D71" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>31418</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>6294</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
-        <v>26.829268</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D72" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>20000</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1560</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
-        <v>26.829268</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>500185177</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>967242706</v>
+        <v>753147930</v>
       </c>
       <c r="G73" t="n">
         <v>97.560976</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>103909023</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>162300453</v>
+        <v>2221291720</v>
       </c>
       <c r="G74" t="n">
         <v>97.560976</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46265</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" t="n">
-        <v>9788257</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>9868969</v>
+        <v>170442</v>
       </c>
       <c r="G75" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46265</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" t="n">
-        <v>1182973</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>942383</v>
+        <v>143344</v>
       </c>
       <c r="G76" t="n">
-        <v>97.560976</v>
+        <v>96.341463</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2348,10 +2348,10 @@
         <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>488810441</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>748163251</v>
+        <v>1094109253</v>
       </c>
       <c r="G77" t="n">
         <v>97.560976</v>
@@ -2360,7 +2360,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2373,10 +2373,10 @@
         <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>1351894846</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>1412673002</v>
+        <v>206264157</v>
       </c>
       <c r="G78" t="n">
         <v>97.560976</v>
@@ -2385,57 +2385,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>23393</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1381516</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>85.365854</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>40720</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>1452782</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>85.365854</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
@@ -2448,10 +2448,10 @@
         <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>401663716</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>893582419</v>
+        <v>967242706</v>
       </c>
       <c r="G81" t="n">
         <v>97.560976</v>
@@ -2460,7 +2460,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
@@ -2473,10 +2473,10 @@
         <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>955961547</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1438094595</v>
+        <v>162300453</v>
       </c>
       <c r="G82" t="n">
         <v>97.560976</v>
@@ -2485,57 +2485,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D83" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>13124930</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>60</v>
+        <v>9868969</v>
       </c>
       <c r="G83" t="n">
-        <v>52.439024</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D84" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>40054409</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>24</v>
+        <v>942383</v>
       </c>
       <c r="G84" t="n">
-        <v>52.439024</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>349915062</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>1002656682</v>
+        <v>748163251</v>
       </c>
       <c r="G85" t="n">
         <v>97.560976</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>2083530104</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>4653100189</v>
+        <v>1412673002</v>
       </c>
       <c r="G86" t="n">
         <v>97.560976</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E87" t="n">
-        <v>26216991</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>33273820</v>
+        <v>1381516</v>
       </c>
       <c r="G87" t="n">
-        <v>97.560976</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E88" t="n">
-        <v>196178640</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>199281400</v>
+        <v>1452782</v>
       </c>
       <c r="G88" t="n">
-        <v>97.560976</v>
+        <v>85.365854</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2648,10 +2648,10 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1627139024</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>2051566400</v>
+        <v>893582419</v>
       </c>
       <c r="G89" t="n">
         <v>97.560976</v>
@@ -2660,7 +2660,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2673,10 +2673,10 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>25418986258</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>34406447895</v>
+        <v>1438094595</v>
       </c>
       <c r="G90" t="n">
         <v>97.560976</v>
@@ -2685,57 +2685,57 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>6207</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>6950029</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>80.48780499999999</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>7200</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>78331372</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>80.48780499999999</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
@@ -2748,10 +2748,10 @@
         <v>80</v>
       </c>
       <c r="E93" t="n">
-        <v>1707992437</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>4828191084</v>
+        <v>1002656682</v>
       </c>
       <c r="G93" t="n">
         <v>97.560976</v>
@@ -2760,7 +2760,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -2773,10 +2773,10 @@
         <v>80</v>
       </c>
       <c r="E94" t="n">
-        <v>4221906804</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>8379911835</v>
+        <v>4653100189</v>
       </c>
       <c r="G94" t="n">
         <v>97.560976</v>
@@ -2785,7 +2785,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>207990371</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>547298813</v>
+        <v>33273820</v>
       </c>
       <c r="G95" t="n">
         <v>97.560976</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>432290309</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>797225701</v>
+        <v>199281400</v>
       </c>
       <c r="G96" t="n">
         <v>97.560976</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>281324952</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>646488066</v>
+        <v>2051566400</v>
       </c>
       <c r="G97" t="n">
         <v>97.560976</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>831821378</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>1790486389</v>
+        <v>34406447895</v>
       </c>
       <c r="G98" t="n">
         <v>97.560976</v>
@@ -2885,57 +2885,57 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="E99" t="n">
-        <v>2282</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>360</v>
+        <v>6950029</v>
       </c>
       <c r="G99" t="n">
-        <v>6.097561</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="E100" t="n">
-        <v>2500</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>78331372</v>
       </c>
       <c r="G100" t="n">
-        <v>6.097561</v>
+        <v>80.48780499999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2948,10 +2948,10 @@
         <v>80</v>
       </c>
       <c r="E101" t="n">
-        <v>504774218</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>4410039153</v>
+        <v>4828191084</v>
       </c>
       <c r="G101" t="n">
         <v>97.560976</v>
@@ -2960,7 +2960,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2973,10 +2973,10 @@
         <v>80</v>
       </c>
       <c r="E102" t="n">
-        <v>1397018249</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>9808807495</v>
+        <v>8379911835</v>
       </c>
       <c r="G102" t="n">
         <v>97.560976</v>
@@ -2985,7 +2985,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2995,40 +2995,240 @@
         <v>46265</v>
       </c>
       <c r="D103" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>6305340</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>44621019</v>
+        <v>547298813</v>
       </c>
       <c r="G103" t="n">
-        <v>92.68292700000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D104" t="n">
+        <v>80</v>
+      </c>
+      <c r="E104" t="n">
+        <v>432290309</v>
+      </c>
+      <c r="F104" t="n">
+        <v>797225701</v>
+      </c>
+      <c r="G104" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D105" t="n">
+        <v>80</v>
+      </c>
+      <c r="E105" t="n">
+        <v>281324952</v>
+      </c>
+      <c r="F105" t="n">
+        <v>646488066</v>
+      </c>
+      <c r="G105" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D106" t="n">
+        <v>80</v>
+      </c>
+      <c r="E106" t="n">
+        <v>831821378</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1790486389</v>
+      </c>
+      <c r="G106" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D107" t="n">
+        <v>5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2282</v>
+      </c>
+      <c r="F107" t="n">
+        <v>360</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.097561</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6.097561</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D109" t="n">
+        <v>80</v>
+      </c>
+      <c r="E109" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4410039153</v>
+      </c>
+      <c r="G109" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D110" t="n">
+        <v>80</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G110" t="n">
+        <v>97.560976</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D111" t="n">
+        <v>76</v>
+      </c>
+      <c r="E111" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F111" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G111" t="n">
+        <v>92.68292700000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C104" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D104" t="n">
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
         <v>76</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E112" t="n">
         <v>19690000</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F112" t="n">
         <v>109088024</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G112" t="n">
         <v>92.68292700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205427.203125</v>
+        <v>204957.3125</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.289993</v>
+        <v>201.839996</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>128.529999</v>
+        <v>130.240005</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>440.369995</v>
+        <v>439.339996</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9748</v>
+        <v>4.9916</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.601</v>
+        <v>5.5874</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7834.240234</v>
+        <v>7800.709961</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27662.966797</v>
+        <v>27498.011719</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51601.289062</v>
+        <v>51213.96875</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4191.299805</v>
+        <v>4135.399902</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>89.220001</v>
+        <v>88.779999</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.75</v>
+        <v>100.699997</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1295.75</v>
+        <v>1293.5</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>506.5</v>
+        <v>501.25</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>10.243213</v>
+        <v>9.991045</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>9.892433</v>
+        <v>9.647976</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>14.830696</v>
+        <v>16.358443</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5647</v>
+        <v>-1.794935</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.38409</v>
+        <v>-4.061195</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.007035</v>
+        <v>-5.237689</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>2.387757</v>
+        <v>1.949541</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>2.985386</v>
+        <v>2.371281</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.365728</v>
+        <v>0.6048750000000001</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.109862</v>
+        <v>-1.225316</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.327137</v>
+        <v>-1.813757</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.651114</v>
+        <v>-2.733509</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>0.212684</v>
+        <v>0.03867</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>1.148278</v>
+        <v>0.09984999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>7.75</v>
+        <v>0.024383</v>
       </c>
       <c r="F30" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="G30" t="n">
         <v>74.390244</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024342</v>
+        <v>0.024383</v>
       </c>
       <c r="F31" t="n">
         <v>0.050788</v>
@@ -1210,76 +1210,76 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024342</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
       <c r="G32" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1351,7 +1351,7 @@
         <v>5.643</v>
       </c>
       <c r="F37" t="n">
-        <v>4.9698</v>
+        <v>4.9935</v>
       </c>
       <c r="G37" t="n">
         <v>74.390244</v>
@@ -1376,7 +1376,7 @@
         <v>5.6424</v>
       </c>
       <c r="F38" t="n">
-        <v>4.9853</v>
+        <v>4.9929</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1651,7 +1651,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>-4.074582</v>
+        <v>-3.617132</v>
       </c>
       <c r="G49" t="n">
         <v>73.170732</v>
@@ -1676,7 +1676,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.764261</v>
+        <v>-3.617551</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1835,26 +1835,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3.983297</v>
       </c>
       <c r="G57" t="n">
-        <v>73.170732</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="58">
@@ -1873,7 +1873,7 @@
         <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>0.004914</v>
+        <v>0.004873</v>
       </c>
       <c r="F58" t="n">
         <v>-0.000457</v>
@@ -1898,7 +1898,7 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004914</v>
+        <v>0.004873</v>
       </c>
       <c r="F59" t="n">
         <v>-0.000457</v>
@@ -2017,19 +2017,19 @@
         <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E64" t="n">
         <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>34418070076</v>
       </c>
       <c r="G64" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="65">
@@ -2042,19 +2042,19 @@
         <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E65" t="n">
         <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>26677510096</v>
       </c>
       <c r="G65" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="66">
@@ -2067,19 +2067,19 @@
         <v>43861</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D66" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E66" t="n">
         <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>7740559980</v>
       </c>
       <c r="G66" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="67">
@@ -2092,19 +2092,19 @@
         <v>43861</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D67" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E67" t="n">
         <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>61095580172</v>
       </c>
       <c r="G67" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="68">
@@ -2117,19 +2117,19 @@
         <v>43861</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D68" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E68" t="n">
         <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>76342513744</v>
       </c>
       <c r="G68" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="69">
@@ -2142,19 +2142,19 @@
         <v>43861</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D69" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E69" t="n">
         <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>14665789542</v>
       </c>
       <c r="G69" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="70">
@@ -2167,19 +2167,19 @@
         <v>43861</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D70" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E70" t="n">
         <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>1611232587</v>
       </c>
       <c r="G70" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="71">
@@ -2192,19 +2192,19 @@
         <v>43861</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D71" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E71" t="n">
         <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>27463449</v>
       </c>
       <c r="G71" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="72">
@@ -2217,19 +2217,19 @@
         <v>43861</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D72" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E72" t="n">
         <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>28316206132</v>
       </c>
       <c r="G72" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="73">
@@ -2242,19 +2242,19 @@
         <v>43861</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E73" t="n">
         <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>753147930</v>
+        <v>809708916</v>
       </c>
       <c r="G73" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="74">
@@ -2267,19 +2267,19 @@
         <v>43861</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E74" t="n">
         <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>2221291720</v>
+        <v>2306235692</v>
       </c>
       <c r="G74" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="75">
@@ -2292,19 +2292,19 @@
         <v>43861</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
         <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>170442</v>
+        <v>144681</v>
       </c>
       <c r="G75" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
@@ -2317,19 +2317,19 @@
         <v>43861</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
         <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>143344</v>
+        <v>122543</v>
       </c>
       <c r="G76" t="n">
-        <v>96.341463</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
@@ -2342,19 +2342,19 @@
         <v>43861</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E77" t="n">
         <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>1292800592</v>
       </c>
       <c r="G77" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="78">
@@ -2367,19 +2367,19 @@
         <v>43861</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E78" t="n">
         <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>235659946</v>
       </c>
       <c r="G78" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="79">
@@ -2442,19 +2442,19 @@
         <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
         <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>967242706</v>
+        <v>950751177</v>
       </c>
       <c r="G81" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="82">
@@ -2467,19 +2467,19 @@
         <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E82" t="n">
         <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>162300453</v>
+        <v>156467198</v>
       </c>
       <c r="G82" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="83">
@@ -2492,19 +2492,19 @@
         <v>43861</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D83" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E83" t="n">
         <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>9868969</v>
+        <v>10523613</v>
       </c>
       <c r="G83" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="84">
@@ -2517,19 +2517,19 @@
         <v>43861</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D84" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E84" t="n">
         <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>942383</v>
+        <v>988603</v>
       </c>
       <c r="G84" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="85">
@@ -2542,19 +2542,19 @@
         <v>43861</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E85" t="n">
         <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>748163251</v>
+        <v>892280162</v>
       </c>
       <c r="G85" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="86">
@@ -2567,19 +2567,19 @@
         <v>43861</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E86" t="n">
         <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>1412673002</v>
+        <v>1801287673</v>
       </c>
       <c r="G86" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="87">
@@ -2592,19 +2592,19 @@
         <v>43861</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
         <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>1381516</v>
+        <v>1255725</v>
       </c>
       <c r="G87" t="n">
-        <v>85.365854</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="88">
@@ -2617,19 +2617,19 @@
         <v>43861</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E88" t="n">
         <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1452782</v>
+        <v>1333748</v>
       </c>
       <c r="G88" t="n">
-        <v>85.365854</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="89">
@@ -2642,19 +2642,19 @@
         <v>43861</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E89" t="n">
         <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>893582419</v>
+        <v>649437972</v>
       </c>
       <c r="G89" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="90">
@@ -2667,19 +2667,19 @@
         <v>43861</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E90" t="n">
         <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1438094595</v>
+        <v>942054629</v>
       </c>
       <c r="G90" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="91">
@@ -2742,19 +2742,19 @@
         <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E93" t="n">
         <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>1002656682</v>
+        <v>1228786726</v>
       </c>
       <c r="G93" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="94">
@@ -2767,19 +2767,19 @@
         <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E94" t="n">
         <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>4653100189</v>
+        <v>5207728793</v>
       </c>
       <c r="G94" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="95">
@@ -2792,19 +2792,19 @@
         <v>43861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D95" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E95" t="n">
         <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>33273820</v>
+        <v>37058160</v>
       </c>
       <c r="G95" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="96">
@@ -2817,19 +2817,19 @@
         <v>43861</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D96" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E96" t="n">
         <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>199281400</v>
+        <v>220704294</v>
       </c>
       <c r="G96" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="97">
@@ -2842,19 +2842,19 @@
         <v>43861</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D97" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E97" t="n">
         <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>1771842975</v>
       </c>
       <c r="G97" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="98">
@@ -2867,19 +2867,19 @@
         <v>43861</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D98" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E98" t="n">
         <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>31660490297</v>
       </c>
       <c r="G98" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="99">
@@ -2892,19 +2892,19 @@
         <v>43861</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E99" t="n">
         <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>5139747</v>
       </c>
       <c r="G99" t="n">
-        <v>80.48780499999999</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="100">
@@ -2917,19 +2917,19 @@
         <v>43861</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
         <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>61011592</v>
       </c>
       <c r="G100" t="n">
-        <v>80.48780499999999</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="101">
@@ -2942,19 +2942,19 @@
         <v>43861</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E101" t="n">
         <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6498868606</v>
       </c>
       <c r="G101" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="102">
@@ -2967,19 +2967,19 @@
         <v>43861</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E102" t="n">
         <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>11689652591</v>
       </c>
       <c r="G102" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="103">
@@ -2992,19 +2992,19 @@
         <v>43861</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D103" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E103" t="n">
         <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>631617247</v>
       </c>
       <c r="G103" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="104">
@@ -3017,19 +3017,19 @@
         <v>43861</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D104" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E104" t="n">
         <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>893774707</v>
       </c>
       <c r="G104" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="105">
@@ -3042,19 +3042,19 @@
         <v>43861</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E105" t="n">
         <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>646488066</v>
+        <v>755950210</v>
       </c>
       <c r="G105" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="106">
@@ -3067,19 +3067,19 @@
         <v>43861</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D106" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E106" t="n">
         <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>1790486389</v>
+        <v>1941525390</v>
       </c>
       <c r="G106" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="107">
@@ -3142,19 +3142,19 @@
         <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E109" t="n">
         <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>4410039153</v>
+        <v>3473089697</v>
       </c>
       <c r="G109" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="110">
@@ -3167,19 +3167,19 @@
         <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E110" t="n">
         <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>9808807495</v>
+        <v>7358383641</v>
       </c>
       <c r="G110" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="111">
@@ -3192,19 +3192,19 @@
         <v>43861</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E111" t="n">
         <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>44621019</v>
+        <v>51965570</v>
       </c>
       <c r="G111" t="n">
-        <v>92.68292700000001</v>
+        <v>93.902439</v>
       </c>
     </row>
     <row r="112">
@@ -3217,19 +3217,19 @@
         <v>43861</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D112" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E112" t="n">
         <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>109088024</v>
+        <v>117130000</v>
       </c>
       <c r="G112" t="n">
-        <v>92.68292700000001</v>
+        <v>93.902439</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204957.3125</v>
+        <v>205987.65625</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.839996</v>
+        <v>202.75</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>130.240005</v>
+        <v>133.270004</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.339996</v>
+        <v>438.910004</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9916</v>
+        <v>5.0122</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5874</v>
+        <v>5.6139</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7800.709961</v>
+        <v>7747.589844</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27498.011719</v>
+        <v>27173.046875</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51213.96875</v>
+        <v>51085.648438</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4135.399902</v>
+        <v>4147.5</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>88.779999</v>
+        <v>91.05999799999999</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.699997</v>
+        <v>103.629997</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1293.5</v>
+        <v>1288</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>501.25</v>
+        <v>500</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>9.991045</v>
+        <v>10.543982</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>9.647976</v>
+        <v>10.142328</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>16.358443</v>
+        <v>19.065491</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.794935</v>
+        <v>-1.89105</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.061195</v>
+        <v>-3.665265</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.237689</v>
+        <v>-4.788245</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.949541</v>
+        <v>1.2553</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>2.371281</v>
+        <v>1.161482</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6048750000000001</v>
+        <v>0.352802</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.225316</v>
+        <v>-0.936303</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.813757</v>
+        <v>0.707807</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.733509</v>
+        <v>0.09658899999999999</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03867</v>
+        <v>-0.386698</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09984999999999999</v>
+        <v>-0.149775</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>0.024383</v>
+        <v>7.75</v>
       </c>
       <c r="F30" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="G30" t="n">
         <v>74.390244</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024383</v>
+        <v>0.02443</v>
       </c>
       <c r="F31" t="n">
         <v>0.050788</v>
@@ -1210,107 +1210,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>1.25</v>
+        <v>0.02443</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.32</v>
+        <v>0.050788</v>
       </c>
       <c r="G32" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G33" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>97.48671</v>
+        <v>1.16</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
       <c r="G35" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>96.53041</v>
+        <v>97.48671</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
         <v>70.731707</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.643</v>
+        <v>96.53041</v>
       </c>
       <c r="F37" t="n">
-        <v>4.9935</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>74.390244</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F38" t="n">
-        <v>4.9929</v>
+        <v>5.0119</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F39" t="n">
-        <v>7397669</v>
+        <v>5.0113</v>
       </c>
       <c r="G39" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F40" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F41" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F42" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
         <v>71.95122000000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F46" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
         <v>71.95122000000001</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
       <c r="G47" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.617132</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.617551</v>
+        <v>-3.261982</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>-3.262359</v>
       </c>
       <c r="G51" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F54" t="n">
-        <v>0.777299</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
         <v>70.731707</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F55" t="n">
-        <v>4.223453</v>
+        <v>-2.628712</v>
       </c>
       <c r="G55" t="n">
-        <v>58.536585</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F56" t="n">
-        <v>3.348378</v>
+        <v>4.223453</v>
       </c>
       <c r="G56" t="n">
-        <v>59.756098</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>3.983297</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
-        <v>58.536585</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.004873</v>
+        <v>7.191214</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000457</v>
+        <v>3.983297</v>
       </c>
       <c r="G58" t="n">
-        <v>73.170732</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004873</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>0.004826</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
       <c r="G60" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03</v>
+        <v>0.004826</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
       <c r="G61" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.02</v>
+        <v>0.03</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>34418070076</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.02</v>
       </c>
       <c r="F65" t="n">
-        <v>26677510096</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7740559980</v>
+        <v>34418070076</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>61095580172</v>
+        <v>26677510096</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>76342513744</v>
+        <v>7740559980</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14665789542</v>
+        <v>61095580172</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1611232587</v>
+        <v>76342513744</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>27463449</v>
+        <v>14665789542</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>28316206132</v>
+        <v>1611232587</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>809708916</v>
+        <v>27463449</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2306235692</v>
+        <v>28316206132</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>144681</v>
+        <v>809708916</v>
       </c>
       <c r="G75" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>122543</v>
+        <v>2306235692</v>
       </c>
       <c r="G76" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1292800592</v>
+        <v>144681</v>
       </c>
       <c r="G77" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>235659946</v>
+        <v>122543</v>
       </c>
       <c r="G78" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1292800592</v>
       </c>
       <c r="G79" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>235659946</v>
       </c>
       <c r="G80" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>950751177</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>156467198</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>10523613</v>
+        <v>950751177</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>988603</v>
+        <v>156467198</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>892280162</v>
+        <v>10523613</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1801287673</v>
+        <v>988603</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1255725</v>
+        <v>892280162</v>
       </c>
       <c r="G87" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1333748</v>
+        <v>1801287673</v>
       </c>
       <c r="G88" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>649437972</v>
+        <v>1255725</v>
       </c>
       <c r="G89" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>942054629</v>
+        <v>1333748</v>
       </c>
       <c r="G90" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>649437972</v>
       </c>
       <c r="G91" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>942054629</v>
       </c>
       <c r="G92" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1228786726</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>5207728793</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>37058160</v>
+        <v>1228786726</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>220704294</v>
+        <v>5207728793</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>1771842975</v>
+        <v>37058160</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>31660490297</v>
+        <v>220704294</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>5139747</v>
+        <v>1771842975</v>
       </c>
       <c r="G99" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>61011592</v>
+        <v>31660490297</v>
       </c>
       <c r="G100" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>6498868606</v>
+        <v>5139747</v>
       </c>
       <c r="G101" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>11689652591</v>
+        <v>61011592</v>
       </c>
       <c r="G102" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>631617247</v>
+        <v>6498868606</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>893774707</v>
+        <v>11689652591</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>755950210</v>
+        <v>631617247</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1941525390</v>
+        <v>893774707</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>755950210</v>
       </c>
       <c r="G107" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1941525390</v>
       </c>
       <c r="G108" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>3473089697</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>7358383641</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>51965570</v>
+        <v>3473089697</v>
       </c>
       <c r="G111" t="n">
-        <v>93.902439</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D112" t="n">
+        <v>81</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D113" t="n">
+        <v>77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.902439</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D114" t="n">
         <v>77</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>117130000</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205987.65625</v>
+        <v>206768.96875</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.75</v>
+        <v>203.580002</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>133.270004</v>
+        <v>133.729996</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.910004</v>
+        <v>438.649994</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0122</v>
+        <v>5.0001</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6139</v>
+        <v>5.6081</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7747.589844</v>
+        <v>7758.700195</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27173.046875</v>
+        <v>27225.183594</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51085.648438</v>
+        <v>51122.460938</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4147.5</v>
+        <v>4157.899902</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.05999799999999</v>
+        <v>90.800003</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.629997</v>
+        <v>103.290001</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1288</v>
+        <v>1287.75</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>500</v>
+        <v>500.5</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>10.543982</v>
+        <v>10.963276</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>10.142328</v>
+        <v>10.59322</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>19.065491</v>
+        <v>19.476454</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.89105</v>
+        <v>-1.94917</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.665265</v>
+        <v>-3.897822</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.788245</v>
+        <v>-4.886617</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2553</v>
+        <v>1.400504</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.161482</v>
+        <v>1.35558</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.352802</v>
+        <v>0.425117</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.936303</v>
+        <v>-0.6879</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>0.707807</v>
+        <v>0.420266</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09658899999999999</v>
+        <v>-0.231815</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.386698</v>
+        <v>-0.406032</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.149775</v>
+        <v>-0.049925</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1210,107 +1210,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02443</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
       <c r="G32" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>70.731707</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.0119</v>
       </c>
       <c r="G37" t="n">
-        <v>70.731707</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0119</v>
+        <v>5.0113</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0113</v>
+        <v>7397669</v>
       </c>
       <c r="G39" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F40" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F41" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F42" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
         <v>71.95122000000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
       <c r="G46" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>367927</v>
+        <v>1.608989</v>
       </c>
       <c r="F47" t="n">
-        <v>362821</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>-3.261982</v>
       </c>
       <c r="G49" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.261982</v>
+        <v>-3.262359</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.262359</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,132 +1760,132 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
       <c r="G54" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.628712</v>
+        <v>4.223453</v>
       </c>
       <c r="G55" t="n">
-        <v>71.95122000000001</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>4.223453</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
-        <v>58.536585</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>3.983297</v>
       </c>
       <c r="G57" t="n">
-        <v>59.756098</v>
+        <v>58.536585</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>3.983297</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>58.536585</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.004826</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.004826</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.004826</v>
+        <v>0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000457</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>34418070076</v>
       </c>
       <c r="G64" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>1.02</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>26677510096</v>
       </c>
       <c r="G65" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>34418070076</v>
+        <v>7740559980</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>26677510096</v>
+        <v>61095580172</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7740559980</v>
+        <v>76342513744</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>61095580172</v>
+        <v>14665789542</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>76342513744</v>
+        <v>1611232587</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14665789542</v>
+        <v>27463449</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1611232587</v>
+        <v>28316206132</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>27463449</v>
+        <v>809708916</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>28316206132</v>
+        <v>2306235692</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>809708916</v>
+        <v>144681</v>
       </c>
       <c r="G75" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2306235692</v>
+        <v>122543</v>
       </c>
       <c r="G76" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>144681</v>
+        <v>1292800592</v>
       </c>
       <c r="G77" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>122543</v>
+        <v>235659946</v>
       </c>
       <c r="G78" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1292800592</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>235659946</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>950751177</v>
       </c>
       <c r="G81" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>156467198</v>
       </c>
       <c r="G82" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>950751177</v>
+        <v>10523613</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>156467198</v>
+        <v>988603</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>10523613</v>
+        <v>892280162</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>988603</v>
+        <v>1801287673</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>892280162</v>
+        <v>1255725</v>
       </c>
       <c r="G87" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1801287673</v>
+        <v>1333748</v>
       </c>
       <c r="G88" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1255725</v>
+        <v>649437972</v>
       </c>
       <c r="G89" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1333748</v>
+        <v>942054629</v>
       </c>
       <c r="G90" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>649437972</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>942054629</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1228786726</v>
       </c>
       <c r="G93" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>5207728793</v>
       </c>
       <c r="G94" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1228786726</v>
+        <v>37058160</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>5207728793</v>
+        <v>220704294</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>37058160</v>
+        <v>1771842975</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>220704294</v>
+        <v>31660490297</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>1771842975</v>
+        <v>5139747</v>
       </c>
       <c r="G99" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>31660490297</v>
+        <v>61011592</v>
       </c>
       <c r="G100" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>5139747</v>
+        <v>6498868606</v>
       </c>
       <c r="G101" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>61011592</v>
+        <v>11689652591</v>
       </c>
       <c r="G102" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>6498868606</v>
+        <v>631617247</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>11689652591</v>
+        <v>893774707</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>631617247</v>
+        <v>755950210</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>893774707</v>
+        <v>1941525390</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>755950210</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1941525390</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>3473089697</v>
       </c>
       <c r="G109" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>7358383641</v>
       </c>
       <c r="G110" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>3473089697</v>
+        <v>51965570</v>
       </c>
       <c r="G111" t="n">
-        <v>98.78048800000001</v>
+        <v>93.902439</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46295</v>
       </c>
       <c r="D112" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>7358383641</v>
+        <v>117130000</v>
       </c>
       <c r="G112" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D113" t="n">
-        <v>77</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>51965570</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.902439</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D114" t="n">
-        <v>77</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>117130000</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>206768.96875</v>
+        <v>208674.40625</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>203.580002</v>
+        <v>205.360001</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>133.729996</v>
+        <v>138.789993</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.649994</v>
+        <v>439.200012</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0001</v>
+        <v>4.9842</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6081</v>
+        <v>5.577</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7758.700195</v>
+        <v>7807.779785</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27225.183594</v>
+        <v>27350.091797</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51122.460938</v>
+        <v>51618.488281</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4157.899902</v>
+        <v>4210.899902</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.800003</v>
+        <v>91.480003</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.290001</v>
+        <v>104.099998</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1287.75</v>
+        <v>1274.5</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>500.5</v>
+        <v>472.5</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>10.963276</v>
+        <v>11.985836</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>10.59322</v>
+        <v>11.56019</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>19.476454</v>
+        <v>23.997135</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.94917</v>
+        <v>-1.826225</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.897822</v>
+        <v>-4.203424</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.886617</v>
+        <v>-5.41407</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.400504</v>
+        <v>2.041939</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.35558</v>
+        <v>1.820595</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.425117</v>
+        <v>1.399514</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6879</v>
+        <v>0.578014</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>0.420266</v>
+        <v>1.172313</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.231815</v>
+        <v>0.550565</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.406032</v>
+        <v>-1.430781</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.049925</v>
+        <v>-5.641538</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02443</v>
+        <v>0.024483</v>
       </c>
       <c r="F31" t="n">
         <v>0.050788</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>1.25</v>
+        <v>0.024483</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.32</v>
+        <v>0.050788</v>
       </c>
       <c r="G32" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
       <c r="G33" t="n">
         <v>73.170732</v>
@@ -1260,57 +1260,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>97.48671</v>
+        <v>1.16</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>0.82</v>
       </c>
       <c r="G35" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>96.53041</v>
+        <v>97.48671</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
         <v>70.731707</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.643</v>
+        <v>96.53041</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0119</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>74.390244</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0113</v>
+        <v>4.9892</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F39" t="n">
-        <v>7397669</v>
+        <v>4.9886</v>
       </c>
       <c r="G39" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F40" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F41" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F42" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
         <v>71.95122000000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,26 +1560,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F46" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1651,7 +1651,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.261982</v>
+        <v>-3.700129</v>
       </c>
       <c r="G49" t="n">
         <v>73.170732</v>
@@ -1676,7 +1676,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.262359</v>
+        <v>-3.700558</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
       <c r="G54" t="n">
-        <v>71.95122000000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>4.223453</v>
+        <v>3.348378</v>
       </c>
       <c r="G55" t="n">
-        <v>58.536585</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F56" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
       <c r="G56" t="n">
         <v>59.756098</v>
@@ -1835,32 +1835,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>3.983297</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>58.536585</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -1873,10 +1873,10 @@
         <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>0.004773</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
       <c r="G58" t="n">
         <v>73.170732</v>
@@ -1885,7 +1885,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,7 +1898,7 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004826</v>
+        <v>0.004773</v>
       </c>
       <c r="F59" t="n">
         <v>-0.000457</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>208674.40625</v>
+        <v>208473.4375</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.360001</v>
+        <v>205.149994</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>138.789993</v>
+        <v>138.770004</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.200012</v>
+        <v>439.23999</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9842</v>
+        <v>4.9872</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.577</v>
+        <v>5.5779</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7807.779785</v>
+        <v>7812.879883</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27350.091797</v>
+        <v>27376.107422</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51618.488281</v>
+        <v>51627.800781</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4210.899902</v>
+        <v>4214.100098</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.480003</v>
+        <v>91.199997</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.099998</v>
+        <v>103.879997</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1274.5</v>
+        <v>1273</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>472.5</v>
+        <v>470.25</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>11.985836</v>
+        <v>11.877985</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>11.56019</v>
+        <v>11.446106</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>23.997135</v>
+        <v>23.979276</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.826225</v>
+        <v>-1.817289</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.203424</v>
+        <v>-4.145768</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.41407</v>
+        <v>-5.398809</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>2.041939</v>
+        <v>2.108593</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.820595</v>
+        <v>1.917448</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.399514</v>
+        <v>1.417808</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.578014</v>
+        <v>0.654451</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>1.172313</v>
+        <v>0.86264</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>0.550565</v>
+        <v>0.338065</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.430781</v>
+        <v>-1.54679</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-5.641538</v>
+        <v>-6.090864</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
       <c r="G47" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.700129</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.700558</v>
+        <v>-3.700129</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>-3.700558</v>
       </c>
       <c r="G51" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>7.168596</v>
+        <v>2.436662</v>
       </c>
       <c r="F54" t="n">
-        <v>4.57612</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
-        <v>59.756098</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F55" t="n">
-        <v>3.348378</v>
+        <v>-2.628712</v>
       </c>
       <c r="G55" t="n">
-        <v>59.756098</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>7.191214</v>
+        <v>7.168596</v>
       </c>
       <c r="F56" t="n">
-        <v>4.293633</v>
+        <v>4.57612</v>
       </c>
       <c r="G56" t="n">
         <v>59.756098</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.004773</v>
+        <v>7.191214</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000457</v>
+        <v>4.293633</v>
       </c>
       <c r="G58" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004773</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>0.004773</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
       <c r="G60" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03</v>
+        <v>0.004773</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
       <c r="G61" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.02</v>
+        <v>0.03</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>34418070076</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.02</v>
       </c>
       <c r="F65" t="n">
-        <v>26677510096</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7740559980</v>
+        <v>34418070076</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>61095580172</v>
+        <v>26677510096</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>76342513744</v>
+        <v>7740559980</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14665789542</v>
+        <v>61095580172</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1611232587</v>
+        <v>76342513744</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>27463449</v>
+        <v>14665789542</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>28316206132</v>
+        <v>1611232587</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>809708916</v>
+        <v>27463449</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2306235692</v>
+        <v>28316206132</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>144681</v>
+        <v>809708916</v>
       </c>
       <c r="G75" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>122543</v>
+        <v>2306235692</v>
       </c>
       <c r="G76" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1292800592</v>
+        <v>144681</v>
       </c>
       <c r="G77" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>235659946</v>
+        <v>122543</v>
       </c>
       <c r="G78" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1292800592</v>
       </c>
       <c r="G79" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>235659946</v>
       </c>
       <c r="G80" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>950751177</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>156467198</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>10523613</v>
+        <v>950751177</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>988603</v>
+        <v>156467198</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>892280162</v>
+        <v>10523613</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1801287673</v>
+        <v>988603</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1255725</v>
+        <v>892280162</v>
       </c>
       <c r="G87" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1333748</v>
+        <v>1801287673</v>
       </c>
       <c r="G88" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>649437972</v>
+        <v>1255725</v>
       </c>
       <c r="G89" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>942054629</v>
+        <v>1333748</v>
       </c>
       <c r="G90" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>649437972</v>
       </c>
       <c r="G91" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>942054629</v>
       </c>
       <c r="G92" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1228786726</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>5207728793</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>37058160</v>
+        <v>1228786726</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>220704294</v>
+        <v>5207728793</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>1771842975</v>
+        <v>37058160</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>31660490297</v>
+        <v>220704294</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>5139747</v>
+        <v>1771842975</v>
       </c>
       <c r="G99" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>61011592</v>
+        <v>31660490297</v>
       </c>
       <c r="G100" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>6498868606</v>
+        <v>5139747</v>
       </c>
       <c r="G101" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>11689652591</v>
+        <v>61011592</v>
       </c>
       <c r="G102" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>631617247</v>
+        <v>6498868606</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>893774707</v>
+        <v>11689652591</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>755950210</v>
+        <v>631617247</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1941525390</v>
+        <v>893774707</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>755950210</v>
       </c>
       <c r="G107" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1941525390</v>
       </c>
       <c r="G108" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>3473089697</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>7358383641</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>51965570</v>
+        <v>3473089697</v>
       </c>
       <c r="G111" t="n">
-        <v>93.902439</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D112" t="n">
+        <v>81</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D113" t="n">
+        <v>77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.902439</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D114" t="n">
         <v>77</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>117130000</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>208473.4375</v>
+        <v>209067</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.149994</v>
+        <v>203.080002</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>138.770004</v>
+        <v>134.389999</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.23999</v>
+        <v>440.350006</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9872</v>
+        <v>4.9772</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5779</v>
+        <v>5.5828</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7812.879883</v>
+        <v>7811.540039</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27376.107422</v>
+        <v>27366.169922</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51627.800781</v>
+        <v>51654.949219</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4214.100098</v>
+        <v>4216.299805</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.199997</v>
+        <v>91.849998</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.879997</v>
+        <v>104.720001</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1273</v>
+        <v>1292</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>470.25</v>
+        <v>479.75</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>11.877985</v>
+        <v>12.196522</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>11.446106</v>
+        <v>10.321599</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>23.979276</v>
+        <v>20.066112</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.817289</v>
+        <v>-1.569168</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.145768</v>
+        <v>-4.337964</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.398809</v>
+        <v>-5.315706</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>2.108593</v>
+        <v>2.091082</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.917448</v>
+        <v>1.880452</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.417808</v>
+        <v>1.471138</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.654451</v>
+        <v>0.706991</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>0.86264</v>
+        <v>1.581509</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>0.338065</v>
+        <v>1.149428</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.54679</v>
+        <v>-0.07734000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.090864</v>
+        <v>-4.193709</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>203.080002</v>
+        <v>205.550003</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>134.389999</v>
+        <v>139.800003</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>440.350006</v>
+        <v>439.25</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9772</v>
+        <v>4.9918</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>10.321599</v>
+        <v>11.663408</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>20.066112</v>
+        <v>24.899493</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.569168</v>
+        <v>-1.815051</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.337964</v>
+        <v>-4.057355</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
       <c r="G46" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>367927</v>
+        <v>1.608989</v>
       </c>
       <c r="F47" t="n">
-        <v>362821</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>-3.700129</v>
       </c>
       <c r="G49" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.700129</v>
+        <v>-3.700558</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.700558</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
       <c r="G54" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
       <c r="G55" t="n">
-        <v>71.95122000000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>4.57612</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
         <v>59.756098</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
       <c r="G57" t="n">
         <v>59.756098</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>59.756098</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.004773</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.004773</v>
+        <v>0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
       <c r="G61" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>34418070076</v>
       </c>
       <c r="G64" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>1.02</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>26677510096</v>
       </c>
       <c r="G65" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>34418070076</v>
+        <v>7740559980</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>26677510096</v>
+        <v>61095580172</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7740559980</v>
+        <v>76342513744</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>61095580172</v>
+        <v>14665789542</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>76342513744</v>
+        <v>1611232587</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14665789542</v>
+        <v>27463449</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1611232587</v>
+        <v>28316206132</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>27463449</v>
+        <v>809708916</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>28316206132</v>
+        <v>2306235692</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>809708916</v>
+        <v>144681</v>
       </c>
       <c r="G75" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2306235692</v>
+        <v>122543</v>
       </c>
       <c r="G76" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>144681</v>
+        <v>1292800592</v>
       </c>
       <c r="G77" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>122543</v>
+        <v>235659946</v>
       </c>
       <c r="G78" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1292800592</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>235659946</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>950751177</v>
       </c>
       <c r="G81" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>156467198</v>
       </c>
       <c r="G82" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>950751177</v>
+        <v>10523613</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>156467198</v>
+        <v>988603</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>10523613</v>
+        <v>892280162</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>988603</v>
+        <v>1801287673</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>892280162</v>
+        <v>1255725</v>
       </c>
       <c r="G87" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1801287673</v>
+        <v>1333748</v>
       </c>
       <c r="G88" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1255725</v>
+        <v>649437972</v>
       </c>
       <c r="G89" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1333748</v>
+        <v>942054629</v>
       </c>
       <c r="G90" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>649437972</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>942054629</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1228786726</v>
       </c>
       <c r="G93" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>5207728793</v>
       </c>
       <c r="G94" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1228786726</v>
+        <v>37058160</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>5207728793</v>
+        <v>220704294</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>37058160</v>
+        <v>1771842975</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>220704294</v>
+        <v>31660490297</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>1771842975</v>
+        <v>5139747</v>
       </c>
       <c r="G99" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>31660490297</v>
+        <v>61011592</v>
       </c>
       <c r="G100" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>5139747</v>
+        <v>6498868606</v>
       </c>
       <c r="G101" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>61011592</v>
+        <v>11689652591</v>
       </c>
       <c r="G102" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>6498868606</v>
+        <v>631617247</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>11689652591</v>
+        <v>893774707</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>631617247</v>
+        <v>755950210</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>893774707</v>
+        <v>1941525390</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>755950210</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1941525390</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>3473089697</v>
       </c>
       <c r="G109" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>7358383641</v>
       </c>
       <c r="G110" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>3473089697</v>
+        <v>51965570</v>
       </c>
       <c r="G111" t="n">
-        <v>98.78048800000001</v>
+        <v>93.902439</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46295</v>
       </c>
       <c r="D112" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>7358383641</v>
+        <v>117130000</v>
       </c>
       <c r="G112" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D113" t="n">
-        <v>77</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>51965570</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.902439</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D114" t="n">
-        <v>77</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>117130000</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F46" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
       <c r="G47" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.700129</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.700558</v>
+        <v>-3.700129</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>-3.700558</v>
       </c>
       <c r="G51" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F55" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
       <c r="G55" t="n">
-        <v>59.756098</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F56" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
       <c r="G56" t="n">
         <v>59.756098</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
         <v>59.756098</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
       <c r="G58" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004773</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03</v>
+        <v>0.004773</v>
       </c>
       <c r="F61" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
       <c r="G61" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.02</v>
+        <v>0.03</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>34418070076</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.02</v>
       </c>
       <c r="F65" t="n">
-        <v>26677510096</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7740559980</v>
+        <v>34418070076</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>61095580172</v>
+        <v>26677510096</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>76342513744</v>
+        <v>7740559980</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14665789542</v>
+        <v>61095580172</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1611232587</v>
+        <v>76342513744</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>27463449</v>
+        <v>14665789542</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>28316206132</v>
+        <v>1611232587</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>809708916</v>
+        <v>27463449</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2306235692</v>
+        <v>28316206132</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>144681</v>
+        <v>809708916</v>
       </c>
       <c r="G75" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>122543</v>
+        <v>2306235692</v>
       </c>
       <c r="G76" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1292800592</v>
+        <v>144681</v>
       </c>
       <c r="G77" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>235659946</v>
+        <v>122543</v>
       </c>
       <c r="G78" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1292800592</v>
       </c>
       <c r="G79" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>235659946</v>
       </c>
       <c r="G80" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>950751177</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>156467198</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>10523613</v>
+        <v>950751177</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>988603</v>
+        <v>156467198</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>892280162</v>
+        <v>10523613</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1801287673</v>
+        <v>988603</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1255725</v>
+        <v>892280162</v>
       </c>
       <c r="G87" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1333748</v>
+        <v>1801287673</v>
       </c>
       <c r="G88" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>649437972</v>
+        <v>1255725</v>
       </c>
       <c r="G89" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>942054629</v>
+        <v>1333748</v>
       </c>
       <c r="G90" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>649437972</v>
       </c>
       <c r="G91" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>942054629</v>
       </c>
       <c r="G92" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1228786726</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>5207728793</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>37058160</v>
+        <v>1228786726</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>220704294</v>
+        <v>5207728793</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>1771842975</v>
+        <v>37058160</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>31660490297</v>
+        <v>220704294</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>5139747</v>
+        <v>1771842975</v>
       </c>
       <c r="G99" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>61011592</v>
+        <v>31660490297</v>
       </c>
       <c r="G100" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>6498868606</v>
+        <v>5139747</v>
       </c>
       <c r="G101" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>11689652591</v>
+        <v>61011592</v>
       </c>
       <c r="G102" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>631617247</v>
+        <v>6498868606</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>893774707</v>
+        <v>11689652591</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>755950210</v>
+        <v>631617247</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1941525390</v>
+        <v>893774707</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>755950210</v>
       </c>
       <c r="G107" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1941525390</v>
       </c>
       <c r="G108" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>3473089697</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>7358383641</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>51965570</v>
+        <v>3473089697</v>
       </c>
       <c r="G111" t="n">
-        <v>93.902439</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D112" t="n">
+        <v>81</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D113" t="n">
+        <v>77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.902439</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D114" t="n">
         <v>77</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>117130000</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9918</v>
+        <v>4.9863</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5828</v>
+        <v>5.5628</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7811.540039</v>
+        <v>7801.430176</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27366.169922</v>
+        <v>27238.013672</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51654.949219</v>
+        <v>51815.429688</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4216.299805</v>
+        <v>4188.399902</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.849998</v>
+        <v>93.55999799999999</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.720001</v>
+        <v>106.470001</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1292</v>
+        <v>1288.25</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>479.75</v>
+        <v>483.5</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.057355</v>
+        <v>-4.163062</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.315706</v>
+        <v>-5.654905</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>2.091082</v>
+        <v>1.958954</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.880452</v>
+        <v>1.403344</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.471138</v>
+        <v>1.786387</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.706991</v>
+        <v>0.040598</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>1.581509</v>
+        <v>3.472682</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>1.149428</v>
+        <v>2.839759</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.07734000000000001</v>
+        <v>-0.367363</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.193709</v>
+        <v>-3.444833</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="F31" t="n">
         <v>0.050788</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="F32" t="n">
         <v>0.050788</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.004773</v>
+        <v>0.004712</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000457</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.004773</v>
+        <v>0.004712</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000457</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7801.430176</v>
+        <v>7805.220215</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27238.013672</v>
+        <v>27254.84375</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51815.429688</v>
+        <v>51821.851562</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4188.399902</v>
+        <v>4192</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>93.55999799999999</v>
+        <v>93.540001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>106.470001</v>
+        <v>106.489998</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.958954</v>
+        <v>2.008487</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.403344</v>
+        <v>1.466</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.786387</v>
+        <v>1.799002</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.040598</v>
+        <v>0.126587</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>3.472682</v>
+        <v>3.450567</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>2.839759</v>
+        <v>2.859074</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>209067</v>
+        <v>206741.546875</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.550003</v>
+        <v>203.5</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>139.800003</v>
+        <v>135.210007</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.25</v>
+        <v>441.290009</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9863</v>
+        <v>5.0137</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5628</v>
+        <v>5.6095</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7805.220215</v>
+        <v>7797.970215</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27254.84375</v>
+        <v>27187.478516</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51821.851562</v>
+        <v>51644.039062</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4192</v>
+        <v>4177.399902</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>93.540001</v>
+        <v>94.290001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>106.489998</v>
+        <v>105.959999</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1288.25</v>
+        <v>1284</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>483.5</v>
+        <v>482.5</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>12.196522</v>
+        <v>10.94856</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>11.663408</v>
+        <v>10.54976</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>24.899493</v>
+        <v>20.798719</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.815051</v>
+        <v>-1.359051</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.163062</v>
+        <v>-3.636432</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.654905</v>
+        <v>-4.862873</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>2.008487</v>
+        <v>1.913735</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.466</v>
+        <v>1.215209</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.799002</v>
+        <v>1.449706</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.126587</v>
+        <v>-0.222139</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>3.450567</v>
+        <v>4.28003</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>2.859074</v>
+        <v>2.347146</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.367363</v>
+        <v>-0.696056</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.444833</v>
+        <v>-3.644533</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024544</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.050788</v>
+        <v>0.82</v>
       </c>
       <c r="G32" t="n">
-        <v>74.390244</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
         <v>73.170732</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
       <c r="G34" t="n">
         <v>73.170732</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="F35" t="n">
-        <v>0.82</v>
+        <v>109.91611</v>
       </c>
       <c r="G35" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
       <c r="G36" t="n">
         <v>70.731707</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>5.0096</v>
       </c>
       <c r="G37" t="n">
-        <v>70.731707</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F38" t="n">
-        <v>4.9892</v>
+        <v>5.009</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F39" t="n">
-        <v>4.9886</v>
+        <v>7397669</v>
       </c>
       <c r="G39" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F40" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F41" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F42" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
         <v>71.95122000000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
       <c r="G46" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>367927</v>
+        <v>1.608989</v>
       </c>
       <c r="F47" t="n">
-        <v>362821</v>
+        <v>-0.219358</v>
       </c>
       <c r="G47" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>-3.306375</v>
       </c>
       <c r="G49" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.700129</v>
+        <v>-3.306758</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.700558</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
       <c r="G54" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
       <c r="G55" t="n">
-        <v>71.95122000000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>4.57612</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
         <v>59.756098</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
       <c r="G57" t="n">
         <v>59.756098</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>59.756098</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.004712</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.004712</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.004712</v>
+        <v>0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000457</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>34418070076</v>
       </c>
       <c r="G64" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>1.02</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>26677510096</v>
       </c>
       <c r="G65" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>34418070076</v>
+        <v>7740559980</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>26677510096</v>
+        <v>61095580172</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7740559980</v>
+        <v>76342513744</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>61095580172</v>
+        <v>14665789542</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>76342513744</v>
+        <v>1611232587</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14665789542</v>
+        <v>27463449</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1611232587</v>
+        <v>28316206132</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>27463449</v>
+        <v>809708916</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>28316206132</v>
+        <v>2306235692</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>809708916</v>
+        <v>144681</v>
       </c>
       <c r="G75" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>2306235692</v>
+        <v>122543</v>
       </c>
       <c r="G76" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>144681</v>
+        <v>1292800592</v>
       </c>
       <c r="G77" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>122543</v>
+        <v>235659946</v>
       </c>
       <c r="G78" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1292800592</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>235659946</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>950751177</v>
       </c>
       <c r="G81" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>156467198</v>
       </c>
       <c r="G82" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>950751177</v>
+        <v>10523613</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>156467198</v>
+        <v>988603</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>10523613</v>
+        <v>892280162</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>988603</v>
+        <v>1801287673</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>892280162</v>
+        <v>1255725</v>
       </c>
       <c r="G87" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>1801287673</v>
+        <v>1333748</v>
       </c>
       <c r="G88" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1255725</v>
+        <v>649437972</v>
       </c>
       <c r="G89" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>1333748</v>
+        <v>942054629</v>
       </c>
       <c r="G90" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>649437972</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>942054629</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>1228786726</v>
       </c>
       <c r="G93" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>5207728793</v>
       </c>
       <c r="G94" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>1228786726</v>
+        <v>37058160</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>5207728793</v>
+        <v>220704294</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>37058160</v>
+        <v>1771842975</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>220704294</v>
+        <v>31660490297</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>1771842975</v>
+        <v>5139747</v>
       </c>
       <c r="G99" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>31660490297</v>
+        <v>61011592</v>
       </c>
       <c r="G100" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>5139747</v>
+        <v>6498868606</v>
       </c>
       <c r="G101" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>61011592</v>
+        <v>11689652591</v>
       </c>
       <c r="G102" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>6498868606</v>
+        <v>631617247</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>432290309</v>
       </c>
       <c r="F104" t="n">
-        <v>11689652591</v>
+        <v>893774707</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>207990371</v>
+        <v>281324952</v>
       </c>
       <c r="F105" t="n">
-        <v>631617247</v>
+        <v>755950210</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>432290309</v>
+        <v>831821378</v>
       </c>
       <c r="F106" t="n">
-        <v>893774707</v>
+        <v>1941525390</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>281324952</v>
+        <v>2282</v>
       </c>
       <c r="F107" t="n">
-        <v>755950210</v>
+        <v>360</v>
       </c>
       <c r="G107" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>831821378</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
-        <v>1941525390</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E109" t="n">
-        <v>2282</v>
+        <v>504774218</v>
       </c>
       <c r="F109" t="n">
-        <v>360</v>
+        <v>3473089697</v>
       </c>
       <c r="G109" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>1397018249</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>7358383641</v>
       </c>
       <c r="G110" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E111" t="n">
-        <v>504774218</v>
+        <v>6305340</v>
       </c>
       <c r="F111" t="n">
-        <v>3473089697</v>
+        <v>51965570</v>
       </c>
       <c r="G111" t="n">
-        <v>98.78048800000001</v>
+        <v>93.902439</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,65 +3220,15 @@
         <v>46295</v>
       </c>
       <c r="D112" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E112" t="n">
-        <v>1397018249</v>
+        <v>19690000</v>
       </c>
       <c r="F112" t="n">
-        <v>7358383641</v>
+        <v>117130000</v>
       </c>
       <c r="G112" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D113" t="n">
-        <v>77</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>51965570</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.902439</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D114" t="n">
-        <v>77</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>117130000</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>206741.546875</v>
+        <v>204498.546875</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>203.5</v>
+        <v>201.429993</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>135.210007</v>
+        <v>131.199997</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>441.290009</v>
+        <v>441.929993</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0137</v>
+        <v>5.0395</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6095</v>
+        <v>5.6045</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7797.970215</v>
+        <v>7748.819824</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27187.478516</v>
+        <v>26954.634766</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51644.039062</v>
+        <v>51627.679688</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4177.399902</v>
+        <v>4118.200195</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.290001</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.959999</v>
+        <v>105.910004</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>482.5</v>
+        <v>480</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>10.94856</v>
+        <v>9.744846000000001</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>10.54976</v>
+        <v>9.425245</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>20.798719</v>
+        <v>17.216114</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.359051</v>
+        <v>-1.215996</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.636432</v>
+        <v>-3.14055</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.862873</v>
+        <v>-4.947675</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.913735</v>
+        <v>1.271375</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>1.215209</v>
+        <v>0.348364</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.449706</v>
+        <v>1.41757</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.222139</v>
+        <v>-1.636133</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>4.28003</v>
+        <v>5.419157</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>2.347146</v>
+        <v>2.298855</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.696056</v>
+        <v>-1.160093</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.644533</v>
+        <v>-4.143784</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024544</v>
+        <v>0.024615</v>
       </c>
       <c r="F31" t="n">
         <v>0.050788</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>1.25</v>
+        <v>0.024615</v>
       </c>
       <c r="F32" t="n">
-        <v>0.82</v>
+        <v>0.050788</v>
       </c>
       <c r="G32" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
       <c r="G33" t="n">
         <v>73.170732</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
         <v>73.170732</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>97.48671</v>
+        <v>1.16</v>
       </c>
       <c r="F35" t="n">
-        <v>109.91611</v>
+        <v>0.82</v>
       </c>
       <c r="G35" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>96.53041</v>
+        <v>97.48671</v>
       </c>
       <c r="F36" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
       <c r="G36" t="n">
         <v>70.731707</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.643</v>
+        <v>96.53041</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0096</v>
+        <v>114.40189</v>
       </c>
       <c r="G37" t="n">
-        <v>74.390244</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F38" t="n">
-        <v>5.009</v>
+        <v>5.0096</v>
       </c>
       <c r="G38" t="n">
         <v>74.390244</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F39" t="n">
-        <v>7397669</v>
+        <v>5.009</v>
       </c>
       <c r="G39" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F40" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F41" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F42" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
         <v>71.95122000000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
         <v>71.95122000000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
         <v>71.95122000000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F45" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
         <v>71.95122000000001</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F46" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
       <c r="G46" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
       <c r="G47" t="n">
-        <v>69.51219500000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F48" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
       <c r="G48" t="n">
         <v>69.51219500000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.306375</v>
+        <v>4.057001</v>
       </c>
       <c r="G49" t="n">
-        <v>73.170732</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.306758</v>
+        <v>-3.306375</v>
       </c>
       <c r="G50" t="n">
         <v>73.170732</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480339</v>
+        <v>-3.306758</v>
       </c>
       <c r="G51" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F53" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
       <c r="G54" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F55" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
       <c r="G55" t="n">
-        <v>59.756098</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F56" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
       <c r="G56" t="n">
         <v>59.756098</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
       <c r="G57" t="n">
         <v>59.756098</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
       <c r="G58" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004712</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>73.170732</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>0.004641</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
       <c r="G60" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03</v>
+        <v>0.004641</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
       <c r="G61" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
         <v>70.731707</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.02</v>
+        <v>0.03</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
         <v>70.731707</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>34418070076</v>
+        <v>0.23</v>
       </c>
       <c r="G64" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.02</v>
       </c>
       <c r="F65" t="n">
-        <v>26677510096</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7740559980</v>
+        <v>34418070076</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>61095580172</v>
+        <v>26677510096</v>
       </c>
       <c r="G67" t="n">
         <v>98.78048800000001</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>76342513744</v>
+        <v>7740559980</v>
       </c>
       <c r="G68" t="n">
         <v>98.78048800000001</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14665789542</v>
+        <v>61095580172</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1611232587</v>
+        <v>76342513744</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>27463449</v>
+        <v>14665789542</v>
       </c>
       <c r="G71" t="n">
         <v>98.78048800000001</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>28316206132</v>
+        <v>1611232587</v>
       </c>
       <c r="G72" t="n">
         <v>98.78048800000001</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>395907378</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>809708916</v>
+        <v>27463449</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>1403790404</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>2306235692</v>
+        <v>28316206132</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75" t="n">
-        <v>42579</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>144681</v>
+        <v>809708916</v>
       </c>
       <c r="G75" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E76" t="n">
-        <v>41657</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>122543</v>
+        <v>2306235692</v>
       </c>
       <c r="G76" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1292800592</v>
+        <v>144681</v>
       </c>
       <c r="G77" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>235659946</v>
+        <v>122543</v>
       </c>
       <c r="G78" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1292800592</v>
       </c>
       <c r="G79" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>235659946</v>
       </c>
       <c r="G80" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>500185177</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>950751177</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>103909023</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>156467198</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>9788257</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>10523613</v>
+        <v>950751177</v>
       </c>
       <c r="G83" t="n">
         <v>98.78048800000001</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>1182973</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>988603</v>
+        <v>156467198</v>
       </c>
       <c r="G84" t="n">
         <v>98.78048800000001</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>488810441</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>892280162</v>
+        <v>10523613</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1351894846</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>1801287673</v>
+        <v>988603</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E87" t="n">
-        <v>23393</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>1255725</v>
+        <v>892280162</v>
       </c>
       <c r="G87" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E88" t="n">
-        <v>40720</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>1333748</v>
+        <v>1801287673</v>
       </c>
       <c r="G88" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E89" t="n">
-        <v>401663716</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>649437972</v>
+        <v>1255725</v>
       </c>
       <c r="G89" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,122 +2670,122 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E90" t="n">
-        <v>955961547</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>942054629</v>
+        <v>1333748</v>
       </c>
       <c r="G90" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D91" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E91" t="n">
-        <v>13124930</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>649437972</v>
       </c>
       <c r="G91" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E92" t="n">
-        <v>40054409</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>942054629</v>
       </c>
       <c r="G92" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>349915062</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>1228786726</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>2083530104</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>5207728793</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>26216991</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>37058160</v>
+        <v>1228786726</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>196178640</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>220704294</v>
+        <v>5207728793</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>1771842975</v>
+        <v>37058160</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>31660490297</v>
+        <v>220704294</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>5139747</v>
+        <v>1771842975</v>
       </c>
       <c r="G99" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>61011592</v>
+        <v>31660490297</v>
       </c>
       <c r="G100" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>6498868606</v>
+        <v>5139747</v>
       </c>
       <c r="G101" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>11689652591</v>
+        <v>61011592</v>
       </c>
       <c r="G102" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>631617247</v>
+        <v>6498868606</v>
       </c>
       <c r="G103" t="n">
         <v>98.78048800000001</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>81</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>893774707</v>
+        <v>11689652591</v>
       </c>
       <c r="G104" t="n">
         <v>98.78048800000001</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="E105" t="n">
-        <v>281324952</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>755950210</v>
+        <v>631617247</v>
       </c>
       <c r="G105" t="n">
         <v>98.78048800000001</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>831821378</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1941525390</v>
+        <v>893774707</v>
       </c>
       <c r="G106" t="n">
         <v>98.78048800000001</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E107" t="n">
-        <v>2282</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>360</v>
+        <v>755950210</v>
       </c>
       <c r="G107" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E108" t="n">
-        <v>2500</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1941525390</v>
       </c>
       <c r="G108" t="n">
-        <v>6.097561</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>504774218</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>3473089697</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1397018249</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>7358383641</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,40 +3195,90 @@
         <v>46295</v>
       </c>
       <c r="D111" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E111" t="n">
-        <v>6305340</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>51965570</v>
+        <v>3473089697</v>
       </c>
       <c r="G111" t="n">
-        <v>93.902439</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D112" t="n">
+        <v>81</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="G112" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D113" t="n">
+        <v>77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.902439</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D114" t="n">
         <v>77</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>19690000</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>117130000</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204498.546875</v>
+        <v>204599.5</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.429993</v>
+        <v>201.509995</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>131.199997</v>
+        <v>130.940002</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>441.929993</v>
+        <v>441.399994</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0395</v>
+        <v>5.0385</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6045</v>
+        <v>5.607</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7748.819824</v>
+        <v>7748.359863</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26954.634766</v>
+        <v>26941.662109</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51627.679688</v>
+        <v>51619.429688</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4118.200195</v>
+        <v>4125.299805</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.31999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.910004</v>
+        <v>105.650002</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1278</v>
+        <v>1278.25</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>480</v>
+        <v>479.75</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>9.744846000000001</v>
+        <v>9.799023</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>9.425245</v>
+        <v>9.468705</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>17.216114</v>
+        <v>16.983831</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.215996</v>
+        <v>-1.334466</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.14055</v>
+        <v>-3.159778</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.947675</v>
+        <v>-4.905274</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.271375</v>
+        <v>1.265364</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>0.348364</v>
+        <v>0.300068</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.41757</v>
+        <v>1.401364</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.636133</v>
+        <v>-1.466558</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>5.419157</v>
+        <v>4.987837</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>2.298855</v>
+        <v>2.047718</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.160093</v>
+        <v>-1.140758</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.143784</v>
+        <v>-4.193709</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204599.5</v>
+        <v>205512.375</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.509995</v>
+        <v>202.300003</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>130.940002</v>
+        <v>132.309998</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>441.399994</v>
+        <v>438.640015</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0385</v>
+        <v>5.0463</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.607</v>
+        <v>5.6621</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7748.359863</v>
+        <v>7697.810059</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26941.662109</v>
+        <v>26452.943359</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51619.429688</v>
+        <v>51953.851562</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4125.299805</v>
+        <v>4180.600098</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.93000000000001</v>
+        <v>95.040001</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.650002</v>
+        <v>105.209999</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1278.25</v>
+        <v>1274.75</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>479.75</v>
+        <v>480.25</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>9.799023</v>
+        <v>10.288921</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>9.468705</v>
+        <v>9.897871</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>16.983831</v>
+        <v>18.207806</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.334466</v>
+        <v>-1.951401</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.159778</v>
+        <v>-3.00986</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.905274</v>
+        <v>-3.970779</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>1.265364</v>
+        <v>0.604715</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>0.300068</v>
+        <v>-1.519364</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>1.401364</v>
+        <v>2.058303</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.466558</v>
+        <v>-0.145702</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>4.987837</v>
+        <v>5.109492</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>2.047718</v>
+        <v>1.622718</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.140758</v>
+        <v>-1.411446</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.193709</v>
+        <v>-4.093859</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1185,57 +1185,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.024615</v>
+        <v>1.25</v>
       </c>
       <c r="F31" t="n">
-        <v>0.050788</v>
+        <v>0.82</v>
       </c>
       <c r="G31" t="n">
-        <v>74.390244</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024615</v>
+        <v>0.64</v>
       </c>
       <c r="F32" t="n">
-        <v>0.050788</v>
+        <v>1.57</v>
       </c>
       <c r="G32" t="n">
-        <v>74.390244</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,7 +1248,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
         <v>0.82</v>
@@ -1260,157 +1260,157 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.64</v>
+        <v>97.48671</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>109.91611</v>
       </c>
       <c r="G34" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>1.16</v>
+        <v>5.6424</v>
       </c>
       <c r="F35" t="n">
-        <v>0.82</v>
+        <v>5.0435</v>
       </c>
       <c r="G35" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>97.48671</v>
+        <v>4511956</v>
       </c>
       <c r="F36" t="n">
-        <v>109.91611</v>
+        <v>7397669</v>
       </c>
       <c r="G36" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>96.53041</v>
+        <v>2601017</v>
       </c>
       <c r="F37" t="n">
-        <v>114.40189</v>
+        <v>4670170</v>
       </c>
       <c r="G37" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E38" t="n">
-        <v>5.643</v>
+        <v>2.33</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0096</v>
+        <v>5.04</v>
       </c>
       <c r="G38" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.6424</v>
+        <v>1.43</v>
       </c>
       <c r="F39" t="n">
-        <v>5.009</v>
+        <v>3.35</v>
       </c>
       <c r="G39" t="n">
-        <v>74.390244</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4511956</v>
+        <v>2.99</v>
       </c>
       <c r="F40" t="n">
-        <v>7397669</v>
+        <v>6.03</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1910940</v>
+        <v>22.89</v>
       </c>
       <c r="F41" t="n">
-        <v>2727499</v>
+        <v>32.26</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,232 +1460,232 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2601017</v>
+        <v>367927</v>
       </c>
       <c r="F42" t="n">
-        <v>4670170</v>
+        <v>362821</v>
       </c>
       <c r="G42" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E43" t="n">
-        <v>2.33</v>
+        <v>1.608989</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04</v>
+        <v>-0.219358</v>
       </c>
       <c r="G43" t="n">
-        <v>71.95122000000001</v>
+        <v>69.51219500000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>-0.4094</v>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>-2.640774</v>
       </c>
       <c r="G44" t="n">
-        <v>71.95122000000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>1.896096</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>0.480339</v>
       </c>
       <c r="G45" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" t="n">
-        <v>22.89</v>
+        <v>2.436662</v>
       </c>
       <c r="F46" t="n">
-        <v>32.26</v>
+        <v>0.799177</v>
       </c>
       <c r="G46" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" t="n">
-        <v>367927</v>
+        <v>-0.042128</v>
       </c>
       <c r="F47" t="n">
-        <v>362821</v>
+        <v>-2.628712</v>
       </c>
       <c r="G47" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E48" t="n">
-        <v>1.608989</v>
+        <v>7.168596</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.219358</v>
+        <v>4.57612</v>
       </c>
       <c r="G48" t="n">
-        <v>69.51219500000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E49" t="n">
-        <v>1.36989</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>4.057001</v>
+        <v>3.348378</v>
       </c>
       <c r="G49" t="n">
-        <v>69.51219500000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.409357</v>
+        <v>7.191214</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.306375</v>
+        <v>4.293633</v>
       </c>
       <c r="G50" t="n">
-        <v>73.170732</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -1698,10 +1698,10 @@
         <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4094</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.306758</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>73.170732</v>
@@ -1710,7 +1710,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.896096</v>
+        <v>0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>0.480339</v>
+        <v>0.16</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>1.160214</v>
+        <v>0.03</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.060934</v>
+        <v>0.03</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>2.436662</v>
+        <v>0.02</v>
       </c>
       <c r="F54" t="n">
-        <v>0.799177</v>
+        <v>0.23</v>
       </c>
       <c r="G54" t="n">
         <v>70.731707</v>
@@ -1785,282 +1785,282 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.042128</v>
+        <v>1.02</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.628712</v>
+        <v>0.2</v>
       </c>
       <c r="G55" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44834</v>
+        <v>43861</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="E56" t="n">
-        <v>7.168596</v>
+        <v>14429715267</v>
       </c>
       <c r="F56" t="n">
-        <v>4.57612</v>
+        <v>34418070076</v>
       </c>
       <c r="G56" t="n">
-        <v>59.756098</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44834</v>
+        <v>43861</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="E57" t="n">
-        <v>8.248760000000001</v>
+        <v>17190165488</v>
       </c>
       <c r="F57" t="n">
-        <v>3.348378</v>
+        <v>26677510096</v>
       </c>
       <c r="G57" t="n">
-        <v>59.756098</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44834</v>
+        <v>43861</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="E58" t="n">
-        <v>7.191214</v>
+        <v>-2760450221</v>
       </c>
       <c r="F58" t="n">
-        <v>4.293633</v>
+        <v>7740559980</v>
       </c>
       <c r="G58" t="n">
-        <v>59.756098</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>31619880755</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>61095580172</v>
       </c>
       <c r="G59" t="n">
-        <v>73.170732</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E60" t="n">
-        <v>0.004641</v>
+        <v>46718273016</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000457</v>
+        <v>76342513744</v>
       </c>
       <c r="G60" t="n">
-        <v>73.170732</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E61" t="n">
-        <v>0.004641</v>
+        <v>12206525099</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000457</v>
+        <v>14665789542</v>
       </c>
       <c r="G61" t="n">
-        <v>73.170732</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03</v>
+        <v>641249369</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>1611232587</v>
       </c>
       <c r="G62" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03</v>
+        <v>11309879</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03</v>
+        <v>27463449</v>
       </c>
       <c r="G63" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02</v>
+        <v>17842724736</v>
       </c>
       <c r="F64" t="n">
-        <v>0.23</v>
+        <v>28316206132</v>
       </c>
       <c r="G64" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44530</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>1.02</v>
+        <v>395907378</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>809708916</v>
       </c>
       <c r="G65" t="n">
-        <v>70.731707</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>14429715267</v>
+        <v>1403790404</v>
       </c>
       <c r="F66" t="n">
-        <v>34418070076</v>
+        <v>2306235692</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2095,22 +2095,22 @@
         <v>46295</v>
       </c>
       <c r="D67" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>17190165488</v>
+        <v>42579</v>
       </c>
       <c r="F67" t="n">
-        <v>26677510096</v>
+        <v>144681</v>
       </c>
       <c r="G67" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2120,22 +2120,22 @@
         <v>46295</v>
       </c>
       <c r="D68" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-2760450221</v>
+        <v>41657</v>
       </c>
       <c r="F68" t="n">
-        <v>7740559980</v>
+        <v>122543</v>
       </c>
       <c r="G68" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>31619880755</v>
+        <v>357877575</v>
       </c>
       <c r="F69" t="n">
-        <v>61095580172</v>
+        <v>1292800592</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>46718273016</v>
+        <v>163332129</v>
       </c>
       <c r="F70" t="n">
-        <v>76342513744</v>
+        <v>235659946</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,57 +2185,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D71" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E71" t="n">
-        <v>12206525099</v>
+        <v>31418</v>
       </c>
       <c r="F71" t="n">
-        <v>14665789542</v>
+        <v>6294</v>
       </c>
       <c r="G71" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D72" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E72" t="n">
-        <v>641249369</v>
+        <v>20000</v>
       </c>
       <c r="F72" t="n">
-        <v>1611232587</v>
+        <v>1560</v>
       </c>
       <c r="G72" t="n">
-        <v>98.78048800000001</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>11309879</v>
+        <v>500185177</v>
       </c>
       <c r="F73" t="n">
-        <v>27463449</v>
+        <v>950751177</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>17842724736</v>
+        <v>103909023</v>
       </c>
       <c r="F74" t="n">
-        <v>28316206132</v>
+        <v>156467198</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>81</v>
       </c>
       <c r="E75" t="n">
-        <v>395907378</v>
+        <v>9788257</v>
       </c>
       <c r="F75" t="n">
-        <v>809708916</v>
+        <v>10523613</v>
       </c>
       <c r="G75" t="n">
         <v>98.78048800000001</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>81</v>
       </c>
       <c r="E76" t="n">
-        <v>1403790404</v>
+        <v>1182973</v>
       </c>
       <c r="F76" t="n">
-        <v>2306235692</v>
+        <v>988603</v>
       </c>
       <c r="G76" t="n">
         <v>98.78048800000001</v>
@@ -2335,7 +2335,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46295</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E77" t="n">
-        <v>42579</v>
+        <v>488810441</v>
       </c>
       <c r="F77" t="n">
-        <v>144681</v>
+        <v>892280162</v>
       </c>
       <c r="G77" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,22 +2370,22 @@
         <v>46295</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E78" t="n">
-        <v>41657</v>
+        <v>1351894846</v>
       </c>
       <c r="F78" t="n">
-        <v>122543</v>
+        <v>1801287673</v>
       </c>
       <c r="G78" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -2395,22 +2395,22 @@
         <v>46295</v>
       </c>
       <c r="D79" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E79" t="n">
-        <v>357877575</v>
+        <v>23393</v>
       </c>
       <c r="F79" t="n">
-        <v>1292800592</v>
+        <v>1255725</v>
       </c>
       <c r="G79" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -2420,122 +2420,122 @@
         <v>46295</v>
       </c>
       <c r="D80" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E80" t="n">
-        <v>163332129</v>
+        <v>40720</v>
       </c>
       <c r="F80" t="n">
-        <v>235659946</v>
+        <v>1333748</v>
       </c>
       <c r="G80" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>31418</v>
+        <v>401663716</v>
       </c>
       <c r="F81" t="n">
-        <v>6294</v>
+        <v>649437972</v>
       </c>
       <c r="G81" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E82" t="n">
-        <v>20000</v>
+        <v>955961547</v>
       </c>
       <c r="F82" t="n">
-        <v>1560</v>
+        <v>942054629</v>
       </c>
       <c r="G82" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D83" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E83" t="n">
-        <v>500185177</v>
+        <v>13124930</v>
       </c>
       <c r="F83" t="n">
-        <v>950751177</v>
+        <v>60</v>
       </c>
       <c r="G83" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D84" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E84" t="n">
-        <v>103909023</v>
+        <v>40054409</v>
       </c>
       <c r="F84" t="n">
-        <v>156467198</v>
+        <v>24</v>
       </c>
       <c r="G84" t="n">
-        <v>98.78048800000001</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>9788257</v>
+        <v>349915062</v>
       </c>
       <c r="F85" t="n">
-        <v>10523613</v>
+        <v>1228786726</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>1182973</v>
+        <v>2083530104</v>
       </c>
       <c r="F86" t="n">
-        <v>988603</v>
+        <v>5207728793</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2598,10 +2598,10 @@
         <v>81</v>
       </c>
       <c r="E87" t="n">
-        <v>488810441</v>
+        <v>26216991</v>
       </c>
       <c r="F87" t="n">
-        <v>892280162</v>
+        <v>37058160</v>
       </c>
       <c r="G87" t="n">
         <v>98.78048800000001</v>
@@ -2610,7 +2610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2623,10 +2623,10 @@
         <v>81</v>
       </c>
       <c r="E88" t="n">
-        <v>1351894846</v>
+        <v>196178640</v>
       </c>
       <c r="F88" t="n">
-        <v>1801287673</v>
+        <v>220704294</v>
       </c>
       <c r="G88" t="n">
         <v>98.78048800000001</v>
@@ -2635,7 +2635,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46295</v>
       </c>
       <c r="D89" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E89" t="n">
-        <v>23393</v>
+        <v>1627139024</v>
       </c>
       <c r="F89" t="n">
-        <v>1255725</v>
+        <v>1771842975</v>
       </c>
       <c r="G89" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,22 +2670,22 @@
         <v>46295</v>
       </c>
       <c r="D90" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E90" t="n">
-        <v>40720</v>
+        <v>25418986258</v>
       </c>
       <c r="F90" t="n">
-        <v>1333748</v>
+        <v>31660490297</v>
       </c>
       <c r="G90" t="n">
-        <v>86.58536599999999</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2695,22 +2695,22 @@
         <v>46295</v>
       </c>
       <c r="D91" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E91" t="n">
-        <v>401663716</v>
+        <v>6207</v>
       </c>
       <c r="F91" t="n">
-        <v>649437972</v>
+        <v>5139747</v>
       </c>
       <c r="G91" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2720,72 +2720,72 @@
         <v>46295</v>
       </c>
       <c r="D92" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E92" t="n">
-        <v>955961547</v>
+        <v>7200</v>
       </c>
       <c r="F92" t="n">
-        <v>942054629</v>
+        <v>61011592</v>
       </c>
       <c r="G92" t="n">
-        <v>98.78048800000001</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E93" t="n">
-        <v>13124930</v>
+        <v>1707992437</v>
       </c>
       <c r="F93" t="n">
-        <v>60</v>
+        <v>6498868606</v>
       </c>
       <c r="G93" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E94" t="n">
-        <v>40054409</v>
+        <v>4221906804</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>11689652591</v>
       </c>
       <c r="G94" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>349915062</v>
+        <v>207990371</v>
       </c>
       <c r="F95" t="n">
-        <v>1228786726</v>
+        <v>631617247</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>2083530104</v>
+        <v>432290309</v>
       </c>
       <c r="F96" t="n">
-        <v>5207728793</v>
+        <v>893774707</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>26216991</v>
+        <v>281324952</v>
       </c>
       <c r="F97" t="n">
-        <v>37058160</v>
+        <v>755950210</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>196178640</v>
+        <v>831821378</v>
       </c>
       <c r="F98" t="n">
-        <v>220704294</v>
+        <v>1941525390</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,57 +2885,57 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>1627139024</v>
+        <v>2282</v>
       </c>
       <c r="F99" t="n">
-        <v>1771842975</v>
+        <v>360</v>
       </c>
       <c r="G99" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>25418986258</v>
+        <v>2500</v>
       </c>
       <c r="F100" t="n">
-        <v>31660490297</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>98.78048800000001</v>
+        <v>6.097561</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46295</v>
       </c>
       <c r="D101" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E101" t="n">
-        <v>6207</v>
+        <v>504774218</v>
       </c>
       <c r="F101" t="n">
-        <v>5139747</v>
+        <v>3473089697</v>
       </c>
       <c r="G101" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46295</v>
       </c>
       <c r="D102" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E102" t="n">
-        <v>7200</v>
+        <v>1397018249</v>
       </c>
       <c r="F102" t="n">
-        <v>61011592</v>
+        <v>7358383641</v>
       </c>
       <c r="G102" t="n">
-        <v>81.707317</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2995,22 +2995,22 @@
         <v>46295</v>
       </c>
       <c r="D103" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E103" t="n">
-        <v>1707992437</v>
+        <v>6305340</v>
       </c>
       <c r="F103" t="n">
-        <v>6498868606</v>
+        <v>51965570</v>
       </c>
       <c r="G103" t="n">
-        <v>98.78048800000001</v>
+        <v>93.902439</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3020,265 +3020,15 @@
         <v>46295</v>
       </c>
       <c r="D104" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E104" t="n">
-        <v>4221906804</v>
+        <v>19690000</v>
       </c>
       <c r="F104" t="n">
-        <v>11689652591</v>
+        <v>117130000</v>
       </c>
       <c r="G104" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C105" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D105" t="n">
-        <v>81</v>
-      </c>
-      <c r="E105" t="n">
-        <v>207990371</v>
-      </c>
-      <c r="F105" t="n">
-        <v>631617247</v>
-      </c>
-      <c r="G105" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D106" t="n">
-        <v>81</v>
-      </c>
-      <c r="E106" t="n">
-        <v>432290309</v>
-      </c>
-      <c r="F106" t="n">
-        <v>893774707</v>
-      </c>
-      <c r="G106" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D107" t="n">
-        <v>81</v>
-      </c>
-      <c r="E107" t="n">
-        <v>281324952</v>
-      </c>
-      <c r="F107" t="n">
-        <v>755950210</v>
-      </c>
-      <c r="G107" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C108" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D108" t="n">
-        <v>81</v>
-      </c>
-      <c r="E108" t="n">
-        <v>831821378</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1941525390</v>
-      </c>
-      <c r="G108" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>43890</v>
-      </c>
-      <c r="C109" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>2282</v>
-      </c>
-      <c r="F109" t="n">
-        <v>360</v>
-      </c>
-      <c r="G109" t="n">
-        <v>6.097561</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>43890</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D110" t="n">
-        <v>5</v>
-      </c>
-      <c r="E110" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>6.097561</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D111" t="n">
-        <v>81</v>
-      </c>
-      <c r="E111" t="n">
-        <v>504774218</v>
-      </c>
-      <c r="F111" t="n">
-        <v>3473089697</v>
-      </c>
-      <c r="G111" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D112" t="n">
-        <v>81</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1397018249</v>
-      </c>
-      <c r="F112" t="n">
-        <v>7358383641</v>
-      </c>
-      <c r="G112" t="n">
-        <v>98.78048800000001</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D113" t="n">
-        <v>77</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6305340</v>
-      </c>
-      <c r="F113" t="n">
-        <v>51965570</v>
-      </c>
-      <c r="G113" t="n">
-        <v>93.902439</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>43861</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D114" t="n">
-        <v>77</v>
-      </c>
-      <c r="E114" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>117130000</v>
-      </c>
-      <c r="G114" t="n">
         <v>93.902439</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205512.375</v>
+        <v>205726.09375</v>
       </c>
       <c r="G2" t="n">
         <v>74.390244</v>
@@ -501,7 +501,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.300003</v>
+        <v>202.639999</v>
       </c>
       <c r="G3" t="n">
         <v>74.390244</v>
@@ -526,7 +526,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>132.309998</v>
+        <v>131.389999</v>
       </c>
       <c r="G4" t="n">
         <v>74.390244</v>
@@ -551,7 +551,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.640015</v>
+        <v>443.209991</v>
       </c>
       <c r="G5" t="n">
         <v>74.390244</v>
@@ -576,7 +576,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0463</v>
+        <v>5.0767</v>
       </c>
       <c r="G6" t="n">
         <v>74.390244</v>
@@ -601,7 +601,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6621</v>
+        <v>5.7122</v>
       </c>
       <c r="G7" t="n">
         <v>74.390244</v>
@@ -626,7 +626,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7697.810059</v>
+        <v>7733.080078</v>
       </c>
       <c r="G8" t="n">
         <v>74.390244</v>
@@ -651,7 +651,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26452.943359</v>
+        <v>26499.583984</v>
       </c>
       <c r="G9" t="n">
         <v>74.390244</v>
@@ -676,7 +676,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51953.851562</v>
+        <v>52400.160156</v>
       </c>
       <c r="G10" t="n">
         <v>74.390244</v>
@@ -701,7 +701,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4180.600098</v>
+        <v>4207.799805</v>
       </c>
       <c r="G11" t="n">
         <v>74.390244</v>
@@ -726,7 +726,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.040001</v>
+        <v>95.589996</v>
       </c>
       <c r="G12" t="n">
         <v>74.390244</v>
@@ -751,7 +751,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.209999</v>
+        <v>105.459999</v>
       </c>
       <c r="G13" t="n">
         <v>74.390244</v>
@@ -776,7 +776,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1274.75</v>
+        <v>1253.75</v>
       </c>
       <c r="G14" t="n">
         <v>74.390244</v>
@@ -801,7 +801,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>480.25</v>
+        <v>473.75</v>
       </c>
       <c r="G15" t="n">
         <v>74.390244</v>
@@ -826,7 +826,7 @@
         <v>-1.532352</v>
       </c>
       <c r="F16" t="n">
-        <v>10.288921</v>
+        <v>10.403614</v>
       </c>
       <c r="G16" t="n">
         <v>73.170732</v>
@@ -851,7 +851,7 @@
         <v>-1.334271</v>
       </c>
       <c r="F17" t="n">
-        <v>9.897871</v>
+        <v>10.082571</v>
       </c>
       <c r="G17" t="n">
         <v>73.170732</v>
@@ -876,7 +876,7 @@
         <v>-2.158268</v>
       </c>
       <c r="F18" t="n">
-        <v>18.207806</v>
+        <v>17.385865</v>
       </c>
       <c r="G18" t="n">
         <v>73.170732</v>
@@ -901,7 +901,7 @@
         <v>-0.865729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.951401</v>
+        <v>-0.92988</v>
       </c>
       <c r="G19" t="n">
         <v>73.170732</v>
@@ -926,7 +926,7 @@
         <v>-0.783007</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.00986</v>
+        <v>-2.425565</v>
       </c>
       <c r="G20" t="n">
         <v>73.170732</v>
@@ -951,7 +951,7 @@
         <v>-4.10587</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.970779</v>
+        <v>-3.121077</v>
       </c>
       <c r="G21" t="n">
         <v>73.170732</v>
@@ -976,7 +976,7 @@
         <v>-0.833371</v>
       </c>
       <c r="F22" t="n">
-        <v>0.604715</v>
+        <v>1.065668</v>
       </c>
       <c r="G22" t="n">
         <v>73.170732</v>
@@ -1001,7 +1001,7 @@
         <v>0.25358</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.519364</v>
+        <v>-1.345727</v>
       </c>
       <c r="G23" t="n">
         <v>73.170732</v>
@@ -1026,7 +1026,7 @@
         <v>-3.729359</v>
       </c>
       <c r="F24" t="n">
-        <v>2.058303</v>
+        <v>2.935033</v>
       </c>
       <c r="G24" t="n">
         <v>73.170732</v>
@@ -1051,7 +1051,7 @@
         <v>-0.577389</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.145702</v>
+        <v>0.503968</v>
       </c>
       <c r="G25" t="n">
         <v>73.170732</v>
@@ -1076,7 +1076,7 @@
         <v>-20.808902</v>
       </c>
       <c r="F26" t="n">
-        <v>5.109492</v>
+        <v>5.71776</v>
       </c>
       <c r="G26" t="n">
         <v>73.170732</v>
@@ -1101,7 +1101,7 @@
         <v>-16.366435</v>
       </c>
       <c r="F27" t="n">
-        <v>1.622718</v>
+        <v>1.864194</v>
       </c>
       <c r="G27" t="n">
         <v>73.170732</v>
@@ -1126,7 +1126,7 @@
         <v>-1.497067</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.411446</v>
+        <v>-3.035576</v>
       </c>
       <c r="G28" t="n">
         <v>73.170732</v>
@@ -1151,7 +1151,7 @@
         <v>-0.219974</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.093859</v>
+        <v>-5.391912</v>
       </c>
       <c r="G29" t="n">
         <v>73.170732</v>
@@ -1185,57 +1185,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>1.25</v>
+        <v>0.024801</v>
       </c>
       <c r="F31" t="n">
-        <v>0.82</v>
+        <v>0.050788</v>
       </c>
       <c r="G31" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.64</v>
+        <v>0.024801</v>
       </c>
       <c r="F32" t="n">
-        <v>1.57</v>
+        <v>0.050788</v>
       </c>
       <c r="G32" t="n">
-        <v>73.170732</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,7 +1248,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
         <v>0.82</v>
@@ -1260,57 +1260,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>97.48671</v>
+        <v>0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>109.91611</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>5.6424</v>
+        <v>1.16</v>
       </c>
       <c r="F35" t="n">
-        <v>5.0435</v>
+        <v>0.82</v>
       </c>
       <c r="G35" t="n">
-        <v>74.390244</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>4511956</v>
+        <v>97.48845</v>
       </c>
       <c r="F36" t="n">
-        <v>7397669</v>
+        <v>110.40624</v>
       </c>
       <c r="G36" t="n">
         <v>71.95122000000001</v>
@@ -1335,7 +1335,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -1348,10 +1348,10 @@
         <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>2601017</v>
+        <v>96.53555</v>
       </c>
       <c r="F37" t="n">
-        <v>4670170</v>
+        <v>111.71919</v>
       </c>
       <c r="G37" t="n">
         <v>71.95122000000001</v>
@@ -1360,57 +1360,57 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>2.33</v>
+        <v>5.643</v>
       </c>
       <c r="F38" t="n">
-        <v>5.04</v>
+        <v>5.0521</v>
       </c>
       <c r="G38" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>1.43</v>
+        <v>5.6424</v>
       </c>
       <c r="F39" t="n">
-        <v>3.35</v>
+        <v>5.0515</v>
       </c>
       <c r="G39" t="n">
-        <v>71.95122000000001</v>
+        <v>74.390244</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>2.99</v>
+        <v>4511956</v>
       </c>
       <c r="F40" t="n">
-        <v>6.03</v>
+        <v>7397669</v>
       </c>
       <c r="G40" t="n">
         <v>71.95122000000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>22.89</v>
+        <v>1910940</v>
       </c>
       <c r="F41" t="n">
-        <v>32.26</v>
+        <v>2727499</v>
       </c>
       <c r="G41" t="n">
         <v>71.95122000000001</v>
@@ -1460,257 +1460,257 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>367927</v>
+        <v>2601017</v>
       </c>
       <c r="F42" t="n">
-        <v>362821</v>
+        <v>4670170</v>
       </c>
       <c r="G42" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D43" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.608989</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.219358</v>
+        <v>5.04</v>
       </c>
       <c r="G43" t="n">
-        <v>69.51219500000001</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.4094</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.640774</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
-        <v>73.170732</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>1.896096</v>
+        <v>22.89</v>
       </c>
       <c r="F45" t="n">
-        <v>0.480339</v>
+        <v>32.26</v>
       </c>
       <c r="G45" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D46" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>2.436662</v>
+        <v>367927</v>
       </c>
       <c r="F46" t="n">
-        <v>0.799177</v>
+        <v>362821</v>
       </c>
       <c r="G46" t="n">
-        <v>70.731707</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.042128</v>
+        <v>1.60818</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.628712</v>
+        <v>0.340229</v>
       </c>
       <c r="G47" t="n">
-        <v>71.95122000000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D48" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>7.168596</v>
+        <v>1.362679</v>
       </c>
       <c r="F48" t="n">
-        <v>4.57612</v>
+        <v>-2.420065</v>
       </c>
       <c r="G48" t="n">
-        <v>59.756098</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.409357</v>
       </c>
       <c r="F49" t="n">
-        <v>3.348378</v>
+        <v>-2.486055</v>
       </c>
       <c r="G49" t="n">
-        <v>59.756098</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D50" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>7.191214</v>
+        <v>-0.4094</v>
       </c>
       <c r="F50" t="n">
-        <v>4.293633</v>
+        <v>-2.486342</v>
       </c>
       <c r="G50" t="n">
-        <v>59.756098</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1.896096</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.480339</v>
       </c>
       <c r="G51" t="n">
-        <v>73.170732</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.03</v>
+        <v>1.160214</v>
       </c>
       <c r="F52" t="n">
-        <v>0.16</v>
+        <v>-0.060934</v>
       </c>
       <c r="G52" t="n">
         <v>70.731707</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.03</v>
+        <v>2.436662</v>
       </c>
       <c r="F53" t="n">
-        <v>0.03</v>
+        <v>0.799177</v>
       </c>
       <c r="G53" t="n">
         <v>70.731707</v>
@@ -1760,257 +1760,257 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02</v>
+        <v>-0.042128</v>
       </c>
       <c r="F54" t="n">
-        <v>0.23</v>
+        <v>-2.628712</v>
       </c>
       <c r="G54" t="n">
-        <v>70.731707</v>
+        <v>71.95122000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>1.02</v>
+        <v>7.168596</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2</v>
+        <v>4.57612</v>
       </c>
       <c r="G55" t="n">
-        <v>70.731707</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>43861</v>
+        <v>44834</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D56" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>14429715267</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>34418070076</v>
+        <v>3.348378</v>
       </c>
       <c r="G56" t="n">
-        <v>98.78048800000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>43861</v>
+        <v>44834</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D57" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>17190165488</v>
+        <v>7.191214</v>
       </c>
       <c r="F57" t="n">
-        <v>26677510096</v>
+        <v>4.293633</v>
       </c>
       <c r="G57" t="n">
-        <v>98.78048800000001</v>
+        <v>59.756098</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D58" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>-2760450221</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>7740559980</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>98.78048800000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D59" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>31619880755</v>
+        <v>0.004455</v>
       </c>
       <c r="F59" t="n">
-        <v>61095580172</v>
+        <v>-0.000457</v>
       </c>
       <c r="G59" t="n">
-        <v>98.78048800000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D60" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>46718273016</v>
+        <v>0.004455</v>
       </c>
       <c r="F60" t="n">
-        <v>76342513744</v>
+        <v>-0.000457</v>
       </c>
       <c r="G60" t="n">
-        <v>98.78048800000001</v>
+        <v>73.170732</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>12206525099</v>
+        <v>0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>14665789542</v>
+        <v>0.16</v>
       </c>
       <c r="G61" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D62" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>641249369</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>1611232587</v>
+        <v>0.03</v>
       </c>
       <c r="G62" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43861</v>
+        <v>44530</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D63" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>11309879</v>
+        <v>1.02</v>
       </c>
       <c r="F63" t="n">
-        <v>27463449</v>
+        <v>0.2</v>
       </c>
       <c r="G63" t="n">
-        <v>98.78048800000001</v>
+        <v>70.731707</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -2023,10 +2023,10 @@
         <v>81</v>
       </c>
       <c r="E64" t="n">
-        <v>17842724736</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>28316206132</v>
+        <v>34418070076</v>
       </c>
       <c r="G64" t="n">
         <v>98.78048800000001</v>
@@ -2035,7 +2035,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_fob</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -2048,10 +2048,10 @@
         <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>395907378</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>809708916</v>
+        <v>26677510096</v>
       </c>
       <c r="G65" t="n">
         <v>98.78048800000001</v>
@@ -2060,7 +2060,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_exp_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>1403790404</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>2306235692</v>
+        <v>7740559980</v>
       </c>
       <c r="G66" t="n">
         <v>98.78048800000001</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_fob</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2095,22 +2095,22 @@
         <v>46295</v>
       </c>
       <c r="D67" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E67" t="n">
-        <v>42579</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>144681</v>
+        <v>61095580172</v>
       </c>
       <c r="G67" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_acucares_cana_imp_kg</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2120,22 +2120,22 @@
         <v>46295</v>
       </c>
       <c r="D68" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E68" t="n">
-        <v>41657</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>122543</v>
+        <v>76342513744</v>
       </c>
       <c r="G68" t="n">
-        <v>97.560976</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_fob</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>357877575</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>1292800592</v>
+        <v>14665789542</v>
       </c>
       <c r="G69" t="n">
         <v>98.78048800000001</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_exp_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>163332129</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>235659946</v>
+        <v>1611232587</v>
       </c>
       <c r="G70" t="n">
         <v>98.78048800000001</v>
@@ -2185,57 +2185,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_fob</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D71" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E71" t="n">
-        <v>31418</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>6294</v>
+        <v>27463449</v>
       </c>
       <c r="G71" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_cafe_nao_torrado_imp_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D72" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>20000</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1560</v>
+        <v>28316206132</v>
       </c>
       <c r="G72" t="n">
-        <v>26.829268</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_fob</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>500185177</v>
+        <v>395907378</v>
       </c>
       <c r="F73" t="n">
-        <v>950751177</v>
+        <v>809708916</v>
       </c>
       <c r="G73" t="n">
         <v>98.78048800000001</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_exp_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>103909023</v>
+        <v>1403790404</v>
       </c>
       <c r="F74" t="n">
-        <v>156467198</v>
+        <v>2306235692</v>
       </c>
       <c r="G74" t="n">
         <v>98.78048800000001</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_fob</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2295,22 +2295,22 @@
         <v>46295</v>
       </c>
       <c r="D75" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>9788257</v>
+        <v>42579</v>
       </c>
       <c r="F75" t="n">
-        <v>10523613</v>
+        <v>144681</v>
       </c>
       <c r="G75" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_carne_bovina_congelada_imp_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2320,22 +2320,22 @@
         <v>46295</v>
       </c>
       <c r="D76" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1182973</v>
+        <v>41657</v>
       </c>
       <c r="F76" t="n">
-        <v>988603</v>
+        <v>122543</v>
       </c>
       <c r="G76" t="n">
-        <v>98.78048800000001</v>
+        <v>97.560976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2348,10 +2348,10 @@
         <v>81</v>
       </c>
       <c r="E77" t="n">
-        <v>488810441</v>
+        <v>357877575</v>
       </c>
       <c r="F77" t="n">
-        <v>892280162</v>
+        <v>1292800592</v>
       </c>
       <c r="G77" t="n">
         <v>98.78048800000001</v>
@@ -2360,7 +2360,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2373,10 +2373,10 @@
         <v>81</v>
       </c>
       <c r="E78" t="n">
-        <v>1351894846</v>
+        <v>163332129</v>
       </c>
       <c r="F78" t="n">
-        <v>1801287673</v>
+        <v>235659946</v>
       </c>
       <c r="G78" t="n">
         <v>98.78048800000001</v>
@@ -2385,57 +2385,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D79" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>23393</v>
+        <v>31418</v>
       </c>
       <c r="F79" t="n">
-        <v>1255725</v>
+        <v>6294</v>
       </c>
       <c r="G79" t="n">
-        <v>86.58536599999999</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
-        <v>40720</v>
+        <v>20000</v>
       </c>
       <c r="F80" t="n">
-        <v>1333748</v>
+        <v>1560</v>
       </c>
       <c r="G80" t="n">
-        <v>86.58536599999999</v>
+        <v>26.829268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_fob</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
@@ -2448,10 +2448,10 @@
         <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>401663716</v>
+        <v>500185177</v>
       </c>
       <c r="F81" t="n">
-        <v>649437972</v>
+        <v>950751177</v>
       </c>
       <c r="G81" t="n">
         <v>98.78048800000001</v>
@@ -2460,7 +2460,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_exp_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
@@ -2473,10 +2473,10 @@
         <v>81</v>
       </c>
       <c r="E82" t="n">
-        <v>955961547</v>
+        <v>103909023</v>
       </c>
       <c r="F82" t="n">
-        <v>942054629</v>
+        <v>156467198</v>
       </c>
       <c r="G82" t="n">
         <v>98.78048800000001</v>
@@ -2485,57 +2485,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_fob</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D83" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>13124930</v>
+        <v>9788257</v>
       </c>
       <c r="F83" t="n">
-        <v>60</v>
+        <v>10523613</v>
       </c>
       <c r="G83" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_fuel_oil_imp_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D84" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E84" t="n">
-        <v>40054409</v>
+        <v>1182973</v>
       </c>
       <c r="F84" t="n">
-        <v>24</v>
+        <v>988603</v>
       </c>
       <c r="G84" t="n">
-        <v>52.439024</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>349915062</v>
+        <v>488810441</v>
       </c>
       <c r="F85" t="n">
-        <v>1228786726</v>
+        <v>892280162</v>
       </c>
       <c r="G85" t="n">
         <v>98.78048800000001</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_exp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>2083530104</v>
+        <v>1351894846</v>
       </c>
       <c r="F86" t="n">
-        <v>5207728793</v>
+        <v>1801287673</v>
       </c>
       <c r="G86" t="n">
         <v>98.78048800000001</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_fob</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46295</v>
       </c>
       <c r="D87" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>26216991</v>
+        <v>23393</v>
       </c>
       <c r="F87" t="n">
-        <v>37058160</v>
+        <v>1255725</v>
       </c>
       <c r="G87" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_milho_em_grao_imp_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46295</v>
       </c>
       <c r="D88" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E88" t="n">
-        <v>196178640</v>
+        <v>40720</v>
       </c>
       <c r="F88" t="n">
-        <v>220704294</v>
+        <v>1333748</v>
       </c>
       <c r="G88" t="n">
-        <v>98.78048800000001</v>
+        <v>86.58536599999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2648,10 +2648,10 @@
         <v>81</v>
       </c>
       <c r="E89" t="n">
-        <v>1627139024</v>
+        <v>401663716</v>
       </c>
       <c r="F89" t="n">
-        <v>1771842975</v>
+        <v>649437972</v>
       </c>
       <c r="G89" t="n">
         <v>98.78048800000001</v>
@@ -2660,7 +2660,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2673,10 +2673,10 @@
         <v>81</v>
       </c>
       <c r="E90" t="n">
-        <v>25418986258</v>
+        <v>955961547</v>
       </c>
       <c r="F90" t="n">
-        <v>31660490297</v>
+        <v>942054629</v>
       </c>
       <c r="G90" t="n">
         <v>98.78048800000001</v>
@@ -2685,57 +2685,57 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D91" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E91" t="n">
-        <v>6207</v>
+        <v>13124930</v>
       </c>
       <c r="F91" t="n">
-        <v>5139747</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>81.707317</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E92" t="n">
-        <v>7200</v>
+        <v>40054409</v>
       </c>
       <c r="F92" t="n">
-        <v>61011592</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>81.707317</v>
+        <v>52.439024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
@@ -2748,10 +2748,10 @@
         <v>81</v>
       </c>
       <c r="E93" t="n">
-        <v>1707992437</v>
+        <v>349915062</v>
       </c>
       <c r="F93" t="n">
-        <v>6498868606</v>
+        <v>1228786726</v>
       </c>
       <c r="G93" t="n">
         <v>98.78048800000001</v>
@@ -2760,7 +2760,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -2773,10 +2773,10 @@
         <v>81</v>
       </c>
       <c r="E94" t="n">
-        <v>4221906804</v>
+        <v>2083530104</v>
       </c>
       <c r="F94" t="n">
-        <v>11689652591</v>
+        <v>5207728793</v>
       </c>
       <c r="G94" t="n">
         <v>98.78048800000001</v>
@@ -2785,7 +2785,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -2798,10 +2798,10 @@
         <v>81</v>
       </c>
       <c r="E95" t="n">
-        <v>207990371</v>
+        <v>26216991</v>
       </c>
       <c r="F95" t="n">
-        <v>631617247</v>
+        <v>37058160</v>
       </c>
       <c r="G95" t="n">
         <v>98.78048800000001</v>
@@ -2810,7 +2810,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -2823,10 +2823,10 @@
         <v>81</v>
       </c>
       <c r="E96" t="n">
-        <v>432290309</v>
+        <v>196178640</v>
       </c>
       <c r="F96" t="n">
-        <v>893774707</v>
+        <v>220704294</v>
       </c>
       <c r="G96" t="n">
         <v>98.78048800000001</v>
@@ -2835,7 +2835,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>81</v>
       </c>
       <c r="E97" t="n">
-        <v>281324952</v>
+        <v>1627139024</v>
       </c>
       <c r="F97" t="n">
-        <v>755950210</v>
+        <v>1771842975</v>
       </c>
       <c r="G97" t="n">
         <v>98.78048800000001</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>81</v>
       </c>
       <c r="E98" t="n">
-        <v>831821378</v>
+        <v>25418986258</v>
       </c>
       <c r="F98" t="n">
-        <v>1941525390</v>
+        <v>31660490297</v>
       </c>
       <c r="G98" t="n">
         <v>98.78048800000001</v>
@@ -2885,57 +2885,57 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="E99" t="n">
-        <v>2282</v>
+        <v>6207</v>
       </c>
       <c r="F99" t="n">
-        <v>360</v>
+        <v>5139747</v>
       </c>
       <c r="G99" t="n">
-        <v>6.097561</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>2500</v>
+        <v>7200</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>61011592</v>
       </c>
       <c r="G100" t="n">
-        <v>6.097561</v>
+        <v>81.707317</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2948,10 +2948,10 @@
         <v>81</v>
       </c>
       <c r="E101" t="n">
-        <v>504774218</v>
+        <v>1707992437</v>
       </c>
       <c r="F101" t="n">
-        <v>3473089697</v>
+        <v>6498868606</v>
       </c>
       <c r="G101" t="n">
         <v>98.78048800000001</v>
@@ -2960,7 +2960,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2973,10 +2973,10 @@
         <v>81</v>
       </c>
       <c r="E102" t="n">
-        <v>1397018249</v>
+        <v>4221906804</v>
       </c>
       <c r="F102" t="n">
-        <v>7358383641</v>
+        <v>11689652591</v>
       </c>
       <c r="G102" t="n">
         <v>98.78048800000001</v>
@@ -2985,7 +2985,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2995,40 +2995,240 @@
         <v>46295</v>
       </c>
       <c r="D103" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E103" t="n">
-        <v>6305340</v>
+        <v>207990371</v>
       </c>
       <c r="F103" t="n">
-        <v>51965570</v>
+        <v>631617247</v>
       </c>
       <c r="G103" t="n">
-        <v>93.902439</v>
+        <v>98.78048800000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D104" t="n">
+        <v>81</v>
+      </c>
+      <c r="E104" t="n">
+        <v>432290309</v>
+      </c>
+      <c r="F104" t="n">
+        <v>893774707</v>
+      </c>
+      <c r="G104" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D105" t="n">
+        <v>81</v>
+      </c>
+      <c r="E105" t="n">
+        <v>281324952</v>
+      </c>
+      <c r="F105" t="n">
+        <v>755950210</v>
+      </c>
+      <c r="G105" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D106" t="n">
+        <v>81</v>
+      </c>
+      <c r="E106" t="n">
+        <v>831821378</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1941525390</v>
+      </c>
+      <c r="G106" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D107" t="n">
+        <v>5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2282</v>
+      </c>
+      <c r="F107" t="n">
+        <v>360</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.097561</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6.097561</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D109" t="n">
+        <v>81</v>
+      </c>
+      <c r="E109" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3473089697</v>
+      </c>
+      <c r="G109" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D110" t="n">
+        <v>81</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F110" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="G110" t="n">
+        <v>98.78048800000001</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D111" t="n">
+        <v>77</v>
+      </c>
+      <c r="E111" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F111" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="G111" t="n">
+        <v>93.902439</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
-        <v